--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -521,12 +521,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>f942ac3d6c67fbe2</t>
+          <t>e187d7f52875f2cb</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 17:37 UTC</t>
+          <t>2026-05-06 17:46 UTC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -541,22 +541,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/openai-ra-mat-mo-hinh-gpt-moi-1234567.html</t>
+          <t>https://vnexpress.net/blue-origin-thu-nghiem-tau-do-bo-mat-trang-5070600.html</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>OpenAI ra mắt mô hình GPT mới</t>
+          <t>Blue Origin thử nghiệm tàu đổ bộ Mặt Trăng</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>OpenAI vừa công bố mô hình ngôn ngữ mới với khả năng vượt trội.</t>
+          <t>Tàu đổ bộ Mặt Trăng MK1 của công ty hàng không vũ trụ Blue Origin hoàn thành thử nghiệm trong buồng chân không nhiệt.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04 20:00 UTC</t>
+          <t>2026-05-06 17:00 UTC</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -580,12 +580,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>be74c0f8cd71c5b6</t>
+          <t>0bd99cffc576ec87</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 17:37 UTC</t>
+          <t>2026-05-06 17:46 UTC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -600,22 +600,22 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/momo-hop-tac-ngan-hang-x-7654321.html</t>
+          <t>https://vnexpress.net/cisco-muon-giai-quyet-diem-nghen-ha-tang-ai-tai-viet-nam-5070803.html</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>MoMo hợp tác với ngân hàng X</t>
+          <t>Cisco muốn giải quyết 'điểm nghẽn' hạ tầng AI tại Việt Nam</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>MoMo công bố hợp tác chiến lược.</t>
+          <t>Cisco cho biết đang góp phần thu hẹp khoảng trống hạ tầng AI của Việt Nam bằng loạt giải pháp thúc đẩy quá trình ứng dụng công nghệ này.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04 03:30 UTC</t>
+          <t>2026-05-06 14:24 UTC</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2bdcd86837aca9c9</t>
+          <t>c74a59ba6d34f04e</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 17:37 UTC</t>
+          <t>2026-05-06 17:46 UTC</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tin-rat-cu-0000001.html</t>
+          <t>https://vnexpress.net/viet-nam-an-do-chia-se-mo-hinh-phat-trien-cong-nghe-loi-5070774.html</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tin rất cũ</t>
+          <t>Việt Nam - Ấn Độ chia sẻ mô hình phát triển công nghệ lõi</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Bài viết cũ ngoài cửa sổ 7 ngày.</t>
+          <t>Làm việc với các viện công nghệ hàng đầu Ấn Độ, đoàn công tác Việt Nam tìm hiểu mô hình tự chủ đại học, cơ chế tài chính và cách thức xây dựng hệ sinh thái khởi nghiệp, phát triển công nghệ lõi.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2023-12-31 17:00 UTC</t>
+          <t>2026-05-06 12:03 UTC</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -690,6 +690,2779 @@
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>8a232a47596d2372</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/robot-hinh-nguoi-tiep-tuc-mat-kiem-soat-5070550.html</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Robot hình người tiếp tục 'mất kiểm soát'</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Khi biểu diễn tại một lễ hội ở Tân Cương, robot hình người bất ngờ có hành động khiến người xung quanh giật mình.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>7e96c0c331f0babd</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chip-dat-toc-do-500-gb-giay-5070492.html</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Chip đạt tốc độ 500 Gb/giây</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Chip sử dụng công nghệ Silicon-germanium do Đức phát triển đạt tốc độ 500 Gb/giây, được kỳ vọng giúp tăng hiệu suất AI, mạng và xử lý dữ liệu tốc độ cao.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:00 UTC</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1bfcfdbcee66d3de</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chu-tich-openai-noi-ve-su-bat-nhat-cua-elon-musk-5070412.html</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Chủ tịch OpenAI nói về sự 'bất nhất' của Elon Musk</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Greg Brockman, nhà đồng sáng lập kiêm Chủ tịch OpenAI, cho biết Elon Musk từng đề nghị làm CEO công ty và chuyển sang mô hình vì lợi nhuận nhưng bị từ chối.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 07:56 UTC</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>6ee0e0d429a3c823</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/loat-smartphone-tich-hop-ai-tam-gia-10-trieu-dong-5057401.html</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Loạt smartphone tích hợp AI tầm giá 10 triệu đồng</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Các smartphone trong phân khúc giá 10 triệu đồng từ Samsung, Xiaomi, Vivo, Oppo trang bị nhiều tính năng AI phục vụ đa dạng nhu cầu, đặt biệt là giới trẻ.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 07:00 UTC</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ad48d8ce5c204bc7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/viet-nam-xac-dinh-10-nhom-cong-nghe-chien-luoc-5070604.html</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Việt Nam xác định 10 nhóm công nghệ chiến lược</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Chính phủ ban hành quyết định về 10 nhóm công nghệ chiến lược và 30 sản phẩm công nghệ chiến lược mà Việt Nam ưu tiên phát triển.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 06:00 UTC</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>12a223f45c927751</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/thu-tuong-yeu-cau-triet-pha-website-phim-nhac-game-lau-5070399.html</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Thủ tướng yêu cầu triệt phá website phim, nhạc, game lậu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Thủ tướng yêu cầu mở đợt cao điểm xử lý xâm phạm sở hữu trí tuệ, triệt phá các website phim, âm nhạc, trò chơi điện tử, truyền hình lậu có lượng truy cập lớn.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 03:17 UTC</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>0ca039111acb9826</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/tham-vong-trung-tam-san-xuat-ban-dan-moi-cua-an-do-5069832.html</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Tham vọng 'trung tâm sản xuất bán dẫn mới' của Ấn Độ</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Thông qua Sứ mệnh Bán dẫn Ấn Độ (ISM) và thúc đẩy đầu tư, Ấn Độ đặt mục tiêu định vị thành trung tâm sản xuất bán dẫn mới của thế giới.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 03:00 UTC</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>1dccc6ed9f0e8793</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/nasa-cong-bo-hon-12-000-buc-anh-tu-nhiem-vu-artemis-ii-5070309.html</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>NASA công bố hơn 12.000 bức ảnh từ nhiệm vụ Artemis II</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>NASA chia sẻ 12.217 bức ảnh về phi hành đoàn Artemis II cùng các thiên thể trong chuyến bay vòng qua Mặt Trăng mang tính lịch sử đầu tháng 4.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 02:00 UTC</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>e44c35bf14478135</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chuoi-cung-ung-tai-chau-a-chiem-90-chi-phi-san-xuat-cua-nvidia-5069846.html</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Chuỗi cung ứng tại châu Á chiếm 90% chi phí sản xuất của Nvidia</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Sự bùng nổ của AI và robot đẩy chi phí sản xuất của Nvidia tại châu Á lên mức kỷ lục, trong khi cơn khát linh kiện khiến nhiều dòng chip cũ bị khai tử sớm.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 01:00 UTC</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>434a899f8742498d</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/find-x9-ultra-dien-thoai-zoom-quang-10x-gia-50-trieu-dong-5070359.html</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Find X9 Ultra - điện thoại zoom quang 10x giá 50 triệu đồng</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Oppo Find X9 Ultra trang bị cụm camera có thông số và khả năng chụp thuộc hàng tốt nhất hiện nay, nhưng giá khởi điểm 50 triệu đồng.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 23:23 UTC</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>fa8aa6b37b85134e</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/nu-game-thu-tu-che-can-phong-cpu-5069663.html</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Nữ game thủ tự chế 'căn phòng CPU'</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Soda Baka, reviewer công nghệ người Trung Quốc, tạo căn phòng với hình dáng CPU, đủ không gian cho một người có thể làm việc và chơi game bên trong.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 22:00 UTC</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>4552b761048a95ba</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ai-co-the-chan-doan-ca-cap-cuu-chinh-xac-hon-bac-si-5069845.html</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>AI có thể 'chẩn đoán ca cấp cứu chính xác hơn bác sĩ'</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Nghiên cứu từ Trường Y Harvard cho thấy AI có khả năng đưa ra chẩn đoán chính xác hơn những bác sĩ dày dạn kinh nghiệm trong các ca cấp cứu thực tế.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>dac24d9c8e687b15</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/iphone-17-chiem-ba-vi-tri-dau-bang-xep-hang-smartphone-ban-chay-5070010.html</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>iPhone 17 chiếm ba vị trí đầu bảng xếp hạng smartphone bán chạy</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Trong danh sách 10 smartphone ăn khách nhất quý I/2026, ba mẫu iPhone 17, 17 Pro Max và 17 Pro lần lượt chiếm ba vị trí đầu tiên.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 11:00 UTC</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>b21946135e8ea321</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/so-doanh-nghiep-bi-ma-doc-tong-tien-tang-bon-lan-do-ai-5070156.html</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Số doanh nghiệp bị mã độc tống tiền tăng bốn lần do AI</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Hơn 7.800 tổ chức và doanh nghiệp bị dính mã độc tống tiền (ransomware) trong năm 2025, tăng 389% so với 2024 do công cụ tấn công bằng AI trở nên phổ biến.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:00 UTC</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>4de17e18a65daff2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/phi-hanh-gia-ghi-hinh-cau-lua-tu-tram-iss-5070094.html</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Phi hành gia ghi hình cầu lửa từ trạm ISS</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Chris Williams, phi hành gia NASA sống trên Trạm Vũ trụ Quốc tế (ISS), chia sẻ video về vật thể rực sáng như cầu lửa lao qua khí quyển.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 08:00 UTC</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>e0172e6074e4263b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/intel-chuyen-giao-thiet-bi-san-xuat-chip-cho-viet-nam-5070075.html</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Intel chuyển giao thiết bị sản xuất chip cho Việt Nam</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 5/5, Intel cho biết hoàn tất bàn giao 31 thiết bị lắp ráp và kiểm định chip cho Khu Công nghệ cao TP HCM (SHTP) và Đại học Quốc gia Hà Nội.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 06:21 UTC</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>14b25b76f4642e56</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/xa-lo-xuyen-sa-mac-lon-nhat-trung-quoc-thanh-hanh-lang-xanh-5070046.html</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Xa lộ xuyên sa mạc lớn nhất Trung Quốc thành hành lang xanh</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Dự án năng lượng xanh dọc theo xa lộ sa mạc Tarim dài 522 km đạt cột mốc quan trọng khi sản xuất hơn 15 triệu kWh điện mặt trời.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 05:00 UTC</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>e1f0dc49fceab29b</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/de-xuat-lap-mang-luoi-chuyen-gia-ai-viet-toan-cau-5069743.html</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Đề xuất lập mạng lưới chuyên gia AI Việt toàn cầu</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Bộ Khoa học và Công nghệ đề xuất lập mạng lưới chuyên gia AI Việt trên toàn cầu, kết nối lực lượng trong và ngoài nước để giải các bài toán quốc gia.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 03:36 UTC</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>52959b0dd4dc44cd</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/musk-ep-chu-tich-openai-dan-xep-kien-tung-ngay-truoc-phien-toa-5069919.html</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Musk 'ép' Chủ tịch OpenAI dàn xếp kiện tụng ngay trước phiên tòa</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Trước phiên tòa ngày 28/4, Elon Musk gây áp lực, buộc nhà đồng sáng lập kiêm Chủ tịch OpenAI Greg Brockman dàn xếp hoặc thành "người bị ghét nhất nước Mỹ".</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 03:01 UTC</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>18968ff80d1d8e2e</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/thi-truong-it-viet-thieu-nguoi-gioi-du-nguoi-code-co-ban-5059102.html</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Thị trường IT Việt 'thiếu người giỏi, dư người code cơ bản'</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Lập trình viên mới vào nghề gặp khó khăn hơn khi xin việc do AI khiến các doanh nghiệp chuyển sang săn tìm nhân sự có tư duy, năng lực giải bài toán thực.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 02:00 UTC</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>87a0b80ecd4325dc</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/trung-quoc-gan-bat-kip-my-ve-hieu-nang-ai-5067916.html</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Trung Quốc gần bắt kịp Mỹ về hiệu năng AI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Các mô hình AI tốt nhất của Trung Quốc và Mỹ không còn cách biệt đáng kể về hiệu năng dù Mỹ vẫn sở hữu nhiều mô hình AI hàng đầu hơn.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>05c61b004a68a47f</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/nhieu-nguoi-bat-dau-bi-khoa-sim-vi-khong-xac-thuc-5067900.html</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Nhiều người bắt đầu bị khóa SIM vì không chính chủ, không xác thực</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Hai tuần kể từ khi Thông tư 08 về xác thực thông tin di động có hiệu lực, nhiều thuê bao bị khóa vì chưa thực hiện theo quy định.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 22:00 UTC</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>33f8e1a4a27e5898</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/viet-nam-don-mua-sao-bang-eta-aquarids-5069794.html</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Việt Nam đón mưa sao băng Eta Aquarids</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Mưa sao băng Eta Aquarids dự kiến đạt cực đại rạng sáng 6/5, có thể quan sát ở những nơi có điều kiện thời tiết thuận lợi tại Việt Nam.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>e114624ac65ed778</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ao-anh-mat-trang-chua-duoc-giai-ma-sau-hang-nghin-nam-5069631.html</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ảo ảnh Mặt Trăng chưa được giải mã sau hàng nghìn năm</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Con người thường thấy Mặt Trăng rất lớn khi mọc hoặc lặn, lớn hơn so với khi ở trên cao, nhưng cảm nhận về kích thước này không đúng.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 12:00 UTC</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>da7ef2a8d114aaba</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/google-dau-tu-vao-trung-tam-nghien-cuu-ai-o-viet-nam-5069650.html</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Google đầu tư vào trung tâm nghiên cứu AI ở Việt Nam</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Các nhóm nghiên cứu tại Saigon AI Hub được quyền truy cập sớm vào các công nghệ mới nhất của Google, được hỗ trợ kỹ thuật bởi chuyên gia DeepMind.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 07:54 UTC</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>517f007e23ee2770</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/bieu-do-the-hien-gia-chip-nho-tang-gan-thang-dung-5069426.html</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Biểu đồ thể hiện giá chip nhớ tăng gần thẳng đứng</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Tình trạng thiếu hụt RAM và ổ cứng SSD đang trở thành một "thảm họa" khi giá bán tăng 26% chỉ trong một tháng.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 05:00 UTC</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>feb3b00eed8051d5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/mot-cong-ty-bi-toa-an-ngan-sa-thai-nhan-vien-vi-ai-5069483.html</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Một công ty bị tòa án ngăn sa thải nhân viên vì AI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Tòa án Nhân dân Trung cấp Hàng Châu cuối tuần trước yêu cầu một công ty địa phương không được phép đuổi việc nhân viên chỉ vì AI.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 03:39 UTC</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>e19053b51422cca3</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/jensen-huang-thi-phan-phan-cung-ai-cua-nvidia-tai-trung-quoc-ve-0-5069427.html</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Jensen Huang: Thị phần phần cứng AI của Nvidia tại Trung Quốc về 0%</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>CEO Nvidia Jensen Huang cho biết chính sách hạn chế xuất khẩu của Mỹ đã phản tác dụng khi khiến họ mất hết thị phần và thúc đẩy Trung Quốc tự chủ công nghệ nhanh hơn.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 02:00 UTC</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>28ffb8cf941e9015</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/trai-nghiem-hieu-nang-macbook-neo-5069171.html</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Trải nghiệm hiệu năng MacBook Neo</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>MacBook Neo dùng tốt cho nhu cầu cơ bản, thao tác ổn với ảnh RAW trên Lightroom, video 4K ít hiệu ứng và đồ họa 2D, nhưng gặp vấn đề khi đa nhiệm với ứng dụng nặng, kỹ xảo phức tạp.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 00:00 UTC</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>54f3063899590ce4</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/tien-si-toan-goc-nga-bien-ai-thanh-co-may-in-tien-5068630.html</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiến sĩ toán gốc Nga biến AI thành 'cỗ máy in tiền'</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiến sĩ toán Alex Gerko nắm lợi thế trong ngành tài chính nhờ xây dựng hệ thống AI có khả năng phân tích lượng lớn dữ liệu từ nhiều năm trước.</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 22:00 UTC</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>487612c567af176c</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/nen-tang-ket-hop-tri-tue-nhan-tao-game-doat-giai-ai-cho-hoc-sinh-5067867.html</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Nền tảng kết hợp trí tuệ nhân tạo - game đoạt giải AI cho học sinh</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Heritage Guessr, AI kết hợp game hóa (gamification) giúp lan tỏa văn hóa Việt Nam của Neural Ninjas, vượt 15.000 đội thi để đoạt giải nhất AI Young Guru.</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 14:25 UTC</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>8aca1b1f1f934334</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/cong-ty-trung-quoc-dung-ai-tao-gan-500-phim-ngan-moi-ngay-5069291.html</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Công ty Trung Quốc dùng AI tạo gần 500 phim ngắn mỗi ngày</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Tại Trung Quốc, phim ngắn đang được tạo với tốc độ đáng kinh ngạc cùng chi phí thấp nhờ AI, với hàng trăm phim được sản xuất mỗi ngày.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 07:58 UTC</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>4c654c239627e5f0</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/mac-mini-mac-studio-chay-hang-vi-chay-duoc-mo-hinh-huan-luyen-ai-5069207.html</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Mac Mini, Mac Studio 'cháy hàng' vì chạy được mô hình huấn luyện AI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>CEO Apple Tim Cook cho biết Mac Mini đang được mua "nhanh hơn dự đoán" khi nguồn cung không đủ nhu cầu, chủ yếu phục vụ huấn luyện AI.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 07:00 UTC</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>db569b130a5ff342</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/trang-hoi-dap-truc-tuyen-ask-com-dong-cua-sau-30-nam-5069257.html</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Trang hỏi đáp trực tuyến Ask.com đóng cửa sau 30 năm</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Ask.com, công cụ tìm kiếm và dịch vụ hỏi đáp trực tuyến từng được nhiều người dùng ưa thích, tuyên bố ngừng hoạt động từ 1/5.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 04:38 UTC</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>42d7052d276a1047</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/robot-hinh-nguoi-trung-quoc-co-lop-da-18-000-diem-cam-bien-5069216.html</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Robot hình người Trung Quốc có lớp da 18.000 điểm cảm biến</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>KAI, robot hình người không mặt của Kinetix AI, sở hữu lớp da xúc giác chứa 18.000 điểm cảm biến, có thể giúp việc trong gia đình như gấp quần áo, lấy đồ từ máy rửa chén.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 02:00 UTC</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>a4ed6a95e12d16ab</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/nubia-neo-5-gt-smartphone-chuyen-game-co-quat-tan-nhiet-5069141.html</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Nubia Neo 5 GT - smartphone chuyên game có quạt tản nhiệt</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Nubia Neo 5 GT là điện thoại cho game thủ tầm trung hiếm hoi có quạt tản nhiệt, cùng màn hình OLED 144 Hz, nút bấm trigger và pin 6.210 mAh.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 01:33 UTC</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>720be6f005497aba</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/sam-altman-ai-giup-doi-vai-cua-nguoi-co-y-tuong-5069213.html</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Sam Altman: AI giúp 'đổi vai' của người có ý tưởng</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>CEO OpenAI Sam Altman cho rằng những người có ý tưởng nhưng yếu về kỹ thuật từng không được coi trọng, nhưng AI khiến vai trò của họ thay đổi.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03 00:35 UTC</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>08e56a62cfcd4c15</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/musk-noi-gi-trong-ba-ngay-lam-chung-tai-phien-toa-kien-openai-5068995.html</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Musk nói gì trong ba ngày làm chứng tại phiên tòa kiện OpenAI?</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Trong phiên xử vụ kiện OpenAI và CEO Sam Altman, Elon Musk đưa ra nhiều lập luận nhằm bảo vệ quan điểm công ty nên được duy trì như một tổ chức phi lợi nhuận.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 17:00 UTC</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>510b53d56f30c3ed</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/ai-bi-sa-thai-vi-chi-phi-cao-5068957.html</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>'AI bị sa thải' vì chi phí cao</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Trong khi nhiều công ty lấy lý do triển khai AI để cắt giảm nhân sự, vấn đề chi phí có thể dẫn đến tình huống ngược là "AI bị sa thải" để tuyển lại con người.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 08:00 UTC</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>f1b50cbe7d94b328</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/lau-nam-goc-bat-tay-voi-loat-cong-ty-ai-tru-anthropic-5069061.html</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Lầu Năm Góc bắt tay với loạt công ty AI, trừ Anthropic</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Bộ Quốc phòng Mỹ cho biết đã đạt thỏa thuận triển khai công nghệ của 7 công ty trí tuệ nhân tạo hàng đầu thế giới trong các mạng lưới bí mật.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 05:14 UTC</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>55f15eb390083225</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/trien-khai-5-nhiem-vu-nghien-cuu-ban-dan-viet-nam-nhat-ban-5068758.html</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Triển khai 5 nhiệm vụ nghiên cứu bán dẫn Việt Nam - Nhật Bản</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Bộ Khoa học và Công nghệ vừa phê duyệt 5 nhiệm vụ về vi mạch tích hợp 3D, vật liệu transistor độ linh động cao, cảm biến môi trường, chip AI SoC và linh kiện điện tử công suất, có sự hợp tác giữa các trường đại học Việt Nam và Nhật Bản.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 03:00 UTC</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>3b02c9fc76d80e2e</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/iphone-17-la-san-pham-thanh-cong-nhat-trong-lich-su-apple-5068997.html</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>iPhone 17 là sản phẩm thành công nhất trong lịch sử Apple</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Bất chấp khó khăn về chuỗi cung ứng, iPhone 17 xác lập kỷ lục khi trở thành thế hệ iPhone bán chạy nhất từ trước đến nay.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 02:15 UTC</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2c609a8633799a2d</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/samsung-va-apple-cung-len-tieng-ve-khung-hoang-chip-nho-5068993.html</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Samsung và Apple cùng lên tiếng về khủng hoảng chip nhớ</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Samsung và SK Hynix cho rằng tình trạng thiếu hụt chip nhớ vì cơn sốt AI sẽ kéo dài, trong khi Apple cũng dự báo chi phí bộ nhớ "tăng đáng kể" trong quý II/2026.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 00:35 UTC</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>b1f2579523704d9f</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/trung-quoc-phat-trien-cong-nghe-pin-sat-ben-16-nam-5068064.html</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Trung Quốc phát triển công nghệ pin sắt bền 16 năm</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Các nhà khoa học Trung Quốc chế tạo nguyên mẫu pin dòng chảy sắt với khả năng vượt qua hơn 6.000 chu kỳ sạc - xả mà không giảm dung lượng.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:00 UTC</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>cde8724513cfae14</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/elon-musk-canh-bao-kich-ban-ai-tro-thanh-ke-huy-diet-5068949.html</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Elon Musk cảnh báo kịch bản AI trở thành 'kẻ hủy diệt'</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Elon Musk nhiều lần nhắc đến kịch bản AI có thể thành "kẻ hủy diệt" khi làm chứng tại tòa trong vụ kiện nhằm vào OpenAI.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 12:18 UTC</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>fab2f123dfe914f6</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/mark-zuckerberg-ly-giai-nguyen-do-day-meta-vao-28-ngay-dia-nguc-5068854.html</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Mark Zuckerberg lý giải nguyên do đẩy Meta vào '28 ngày địa ngục'</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Lần đầu Mark Zuckerberg trực tiếp đề cập tới kế hoạch sa thải nhân sự là do chi tiêu dành cho AI tăng mạnh và không loại trừ sẽ tiếp tục cắt giảm.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 06:17 UTC</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>9c2f2f859023307a</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 17:46 UTC</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_sohoa</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/phat-hien-xu-ly-hon-500-bo-thiet-bi-kich-song-di-dong-5068650.html</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Phát hiện, xử lý hơn 500 bộ thiết bị kích sóng di động</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Cục Tần số vô tuyến điện cho biết, hơn 500 bộ thiết bị kích sóng di động do người dân tự ý lắp đặt đã bị phát hiện và xử lý từ năm 2023 đến nay.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 05:16 UTC</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>market_pulse</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>domestic</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>new</t>
         </is>
@@ -733,7 +3506,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:14 UTC</t>
+          <t>2026-05-06 18:19 UTC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:14 UTC</t>
+          <t>2026-05-06 18:19 UTC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:14 UTC</t>
+          <t>2026-05-06 18:19 UTC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:14 UTC</t>
+          <t>2026-05-06 18:19 UTC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-06 18:14 UTC</t>
+          <t>2026-05-06 18:19 UTC</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">

--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V108"/>
+  <dimension ref="A1:V107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -578,17 +578,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/policy/article/3353315/china-clears-tencents-ximalaya-acquisition-strict-bans-exclusive-deals-fee-hikes?utm_source=rss_feed</t>
+          <t>https://momo.vn/tin-tuc/tin-tuc-su-kien/tham-gia-vong-song-khoe-nhan-qua-co-tri-gia-den-8707</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -616,12 +616,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -629,24 +629,32 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Tencent Holdings has secured conditional approval to acquire online audio platform Ximalaya after a nearly year-long review by China’s antitrust watchdog, a move set to expand the Shenzhen-based tech giant’s footprint in China’s digital content ecosystem. The State Administration for Market Regulati</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ Sự Kiện · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Làm nhiệm vụ đơn giản, nhận lượt quay và trúng quà có giá trị cao tại Vòng Sống Khỏe. Xem chi tiết ngay! Thời gian áp dụng: Từ 18/05/2026 đến hết ngày 30/09/202</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
     </row>
@@ -656,17 +664,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/25901</t>
+          <t>https://www.scmp.com/tech/policy/article/3353315/china-clears-tencents-ximalaya-acquisition-strict-bans-exclusive-deals-fee-hikes?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -684,18 +692,22 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -703,20 +715,24 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Tencent Holdings has secured conditional approval to acquire online audio platform Ximalaya after a nearly year-long review by China’s antitrust watchdog, a move set to expand the Shenzhen-based tech giant’s footprint in China’s digital content ecosystem. The State Administration for Market Regulati</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="V3" s="2" t="inlineStr"/>
     </row>
@@ -726,17 +742,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/khuyen-mai/ban-moi-nhap-ma-chonmomo-co-qua-500000d-giam-8225</t>
+          <t>https://banhang.shopee.vn/edu/article/25901</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bạn mới nhập mã CHONMOMO: Có quà 500.000đ giảm nhiều dịch vụ, thêm tiền thưởng đến 1 triệu</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -754,10 +770,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Bạn mới nhập mã CHONMOMO: Có quà 500.000đ giảm nhiều dịch vụ, thêm tiền thưởng đến 1 triệu</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -765,7 +785,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>MoMo</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -773,24 +793,20 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Bạn mới nhập mã CHONMOMO: Có quà 500.000đ giảm nhiều dịch vụ, thêm tiền thưởng đến 1 triệu</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bạn mới nhập mã CHONMOMO: Có quà 500.000đ giảm nhiều dịch vụ, thêm tiền thưởng đến 1 triệu Khuyến mãi · 01/04/2026 · 12.2K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Chọn MoMo - chọn linh hoạt chi tiêu: Nhận ngay bộ thẻ quà 500.000đ giảm mọi dịch vụ &amp; lì xì đến 1 triệu khi </t>
-        </is>
-      </c>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
     </row>
@@ -800,17 +816,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/thong-tin-khuyen-mai-cua-chuong-trinh-grabfood-van-deal-mastximum-giam-50/</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>THÔNG TIN KHUYẾN MẠI CỦA CHƯƠNG TRÌNH GRABFOOD VẠN DEAL MASTXIMUM GIẢM 50%</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -828,22 +844,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>THÔNG TIN KHUYẾN MẠI CỦA CHƯƠNG TRÌNH GRABFOOD VẠN DEAL MASTXIMUM GIẢM 50%</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Trong nước</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -851,24 +867,24 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>THÔNG TIN KHUYẾN MẠI CỦA CHƯƠNG TRÌNH GRABFOOD VẠN DEAL MASTXIMUM GIẢM 50%</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Ba Tháng Năm 12th, 2026 THÔNG TIN KHUYẾN MẠI CỦA CHƯƠNG TRÌNH GRABFOOD VẠN DEAL MASTXIMUM GIẢM 50% 🔊 Xin thông báo mùa hè nóng kỷ lục chỉ còn là cái tên: GrabFood giới thiệu biệt đội Mátximum nóng tới đâu cũng có vạn deal món mát nhất – giảm “maximum”! 🧋 Biệt đội mát dịu dàng buitruonglinh mang </t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="U5" s="2" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="V5" s="2" t="inlineStr"/>
     </row>
@@ -878,22 +894,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>https://merchant.grab.com/vn-vn/blog/traicaysachanvatvoduyninh</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>grab_merchant_vn</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4 - Strategic shift</t>
+          <t>3 - Market signal</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -906,22 +922,18 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Trong nước</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -929,24 +941,24 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t xml:space="preserve">Hơn 21 năm gắn bó với nghề kinh doanh mỹ phẩm theo mô hình truyền thống, chị Ngọc Diệp đã trải qua những ngày thử thách và biến động bởi đại dịch Covid-19. Từ việc phải tạm đóng cửa hàng mỹ phẩm và trăn trở giải quyết bài toán xoay vốn, hiện tại chị Diệp đã sở hữu cửa hàng online hoạt động ổn định, </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
     </row>
@@ -956,12 +968,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/traicaysachanvatvoduyninh</t>
+          <t>https://merchant.grab.com/vn-vn/blog/dealhoidonkhachmoi</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -984,7 +996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
@@ -1003,12 +1015,12 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hơn 21 năm gắn bó với nghề kinh doanh mỹ phẩm theo mô hình truyền thống, chị Ngọc Diệp đã trải qua những ngày thử thách và biến động bởi đại dịch Covid-19. Từ việc phải tạm đóng cửa hàng mỹ phẩm và trăn trở giải quyết bài toán xoay vốn, hiện tại chị Diệp đã sở hữu cửa hàng online hoạt động ổn định, </t>
+          <t>Quý Đối tác thân mến, 🤗 Đối tác mong muốn thu hút thêm nhiều Người dùng mới đến nhà hàng trải nghiệm món ngon ? 🤗 Đối tác đang tìm kiếm chiến dịch marketing với ngân sách tối ưu để tiếp cận Người dùng mới ? Mời Đối tác tham gia chương trình “Deal Hời Đón Khách Mới” - giải pháp giúp thu hút và mở rộn</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1030,12 +1042,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/dealhoidonkhachmoi</t>
+          <t>https://merchant.grab.com/vn-vn/blog/gfin-vc-hoan01thanglaivay</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1058,7 +1070,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1077,12 +1089,12 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Quý Đối tác thân mến, 🤗 Đối tác mong muốn thu hút thêm nhiều Người dùng mới đến nhà hàng trải nghiệm món ngon ? 🤗 Đối tác đang tìm kiếm chiến dịch marketing với ngân sách tối ưu để tiếp cận Người dùng mới ? Mời Đối tác tham gia chương trình “Deal Hời Đón Khách Mới” - giải pháp giúp thu hút và mở rộn</t>
+          <t>Quý Đối tác thân mến, Công ty TNHH GFIN Việt Nam (“GFIN”) mang đến cho các Đối tác Tài xế, Đối tác Thương nhân chương trình Hoàn tiền lãi 01 tháng cho các khoản vay tín chấp với thương hiệu TIN VAY của VietCredit (“TIN VAY”). TIN VAY hoàn tiền lãi trung bình 01 tháng trực tiếp vào khoản vay: Giá trị</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1969,7 +1981,11 @@
           <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1990,7 +2006,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng Khuyến mãi · 15/05/2026 · 2.3K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Lễ hội Pháo hoa Quốc tế Đà Nẵng (DIFF) 2026 chính thức quay trở lại, hứa hẹn biến bầu trời sông Hàn thành một kiệt tác nghệ thuật đầy mê h</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng Khuyến mãi · 15/05/2026 · 2.5K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Lễ hội Pháo hoa Quốc tế Đà Nẵng (DIFF) 2026 chính thức quay trở lại, hứa hẹn biến bầu trời sông Hàn thành một kiệt tác nghệ thuật đầy mê h</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2031,7 +2047,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -2045,7 +2061,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2129,7 +2145,11 @@
           <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2554,12 +2574,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/17468</t>
+          <t>https://banhang.shopee.vn/edu/article/25329</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2582,10 +2602,14 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2601,7 +2625,7 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr"/>
@@ -2624,12 +2648,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27364</t>
+          <t>https://banhang.shopee.vn/edu/article/27540</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tỷ lệ sản phẩm bật kênh Hỏa Tốc đối với Shopee Mall/Shop Yêu Thích+</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2643,7 +2667,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -2652,10 +2676,14 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Tỷ lệ sản phẩm bật kênh Hỏa Tốc đối với Shopee Mall/Shop Yêu Thích+</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2671,11 +2699,15 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Tỷ lệ sản phẩm bật kênh Hỏa Tốc đối với Shopee Mall/Shop Yêu Thích+</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="n">
         <v>3</v>
@@ -2694,12 +2726,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27540</t>
+          <t>https://banhang.shopee.vn/edu/article/17468</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2713,7 +2745,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2722,12 +2754,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2745,15 +2777,11 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="n">
         <v>3</v>
@@ -4176,12 +4204,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
+          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -4204,7 +4232,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -4227,12 +4255,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
+          <t>Tài liệu tòa án cho thấy Sam Altman có cổ phần hơn hai tỷ USD tại hàng loạt công ty đang bắt tay với OpenAI.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -4254,17 +4282,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
+          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4282,12 +4310,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4305,12 +4333,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
+          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -4332,12 +4360,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
+          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4360,7 +4388,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -4383,12 +4411,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
+          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -4410,12 +4438,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4438,7 +4466,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -4461,12 +4489,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
+          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -4488,17 +4516,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>grab_inside</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4516,18 +4544,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
@@ -4535,24 +4567,24 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
+          <t>Vietnam Airlines dự kiến lỗ trong quý II, khiến lợi nhuận nửa đầu năm 2026 xuống mức âm dù quý I vừa lãi kỷ lục hơn 4.500 tỷ.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
     </row>
@@ -4562,12 +4594,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
+          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4590,7 +4622,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -4609,7 +4641,7 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -4636,12 +4668,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
+          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4664,7 +4696,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -4683,7 +4715,7 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -4710,17 +4742,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
+          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>grab_inside</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4738,22 +4770,18 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+          <t>Tracing our impact</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
@@ -4761,24 +4789,24 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
+          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V56" s="2" t="inlineStr"/>
     </row>
@@ -4788,12 +4816,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
+          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -4816,7 +4844,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -4839,12 +4867,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
+          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -4866,12 +4894,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
+          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4894,7 +4922,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -4917,12 +4945,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
+          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
@@ -4944,12 +4972,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/running-codex-safely/</t>
+          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4972,12 +5000,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -4995,12 +5023,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
+          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
@@ -5022,17 +5050,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/ai-poised-to-tilt-job-market-leverage-toward-older-workers</t>
+          <t>https://openai.com/index/running-codex-safely/</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5050,12 +5078,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -5073,12 +5101,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>When it comes to job cuts, older workers are often disproportionately affected. But a new survey of chief executive officers suggests this won’t be a given as companies adopt artificial intelligence.</t>
+          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
@@ -5100,12 +5128,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/-the-oppenheimer-of-the-ai-era-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/ai-poised-to-tilt-job-market-leverage-toward-older-workers</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5128,7 +5156,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -5151,12 +5179,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>What drives the tech titans behind the AI arms race? For some, it's the thrill of scientific discovery; for others, it's the pursuit of profit.  Through the story of DeepMind co-founder Demis Hassabis and other AI leaders, author Sebastian Mallaby explores how motivations ranging from scientific cur</t>
+          <t>When it comes to job cuts, older workers are often disproportionately affected. But a new survey of chief executive officers suggests this won’t be a given as companies adopt artificial intelligence.</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -5178,12 +5206,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/elon-musk-says-he-isn-t-selling-his-spacex-shares-as-ipo-looms</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/-the-oppenheimer-of-the-ai-era-video</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5206,7 +5234,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -5229,12 +5257,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk said he is not selling any SpaceX shares, with the company reported to be preparing to file publicly for its long-awaited IPO as soon as next week.</t>
+          <t>What drives the tech titans behind the AI arms race? For some, it's the thrill of scientific discovery; for others, it's the pursuit of profit.  Through the story of DeepMind co-founder Demis Hassabis and other AI leaders, author Sebastian Mallaby explores how motivations ranging from scientific cur</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -5256,12 +5284,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/how-agentic-commerce-will-reshape-the-internet-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/elon-musk-says-he-isn-t-selling-his-spacex-shares-as-ipo-looms</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5284,7 +5312,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -5307,12 +5335,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The internet is made for shopping. For years, the main inputs for e-commerce transactions involved targeted ads, algorithmic recommendations, SEO, and lots of mindless scrolling. But agentic commerce might represent a sea change for e-commerce: With the rise of AI agents doing shopping on behalf of </t>
+          <t>Elon Musk said he is not selling any SpaceX shares, with the company reported to be preparing to file publicly for its long-awaited IPO as soon as next week.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -5334,12 +5362,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/snap-youtube-settle-school-social-media-suit-ahead-of-trial</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/how-agentic-commerce-will-reshape-the-internet-video</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5362,12 +5390,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5385,12 +5413,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Snap Inc., Google’s YouTube and ByteDance Ltd.’s TikTok reached agreements to settle the first lawsuit headed to trial over claims that addiction to top social media platforms has disrupted learning and pushed public schools to spend massive sums fighting a mental health crisis, according to court f</t>
+          <t xml:space="preserve">The internet is made for shopping. For years, the main inputs for e-commerce transactions involved targeted ads, algorithmic recommendations, SEO, and lots of mindless scrolling. But agentic commerce might represent a sea change for e-commerce: With the rise of AI agents doing shopping on behalf of </t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -5412,12 +5440,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/korea-bond-yields-may-extend-gains-on-chips-boom-analysts-say</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/snap-youtube-settle-school-social-media-suit-ahead-of-trial</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5440,12 +5468,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -5463,12 +5491,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>South Korea’s bonds are set to extend this year’s rout as a semiconductor boom supercharges the nation’s economic growth and adds to inflationary pressures, analysts say.</t>
+          <t>Snap Inc., Google’s YouTube and ByteDance Ltd.’s TikTok reached agreements to settle the first lawsuit headed to trial over claims that addiction to top social media platforms has disrupted learning and pushed public schools to spend massive sums fighting a mental health crisis, according to court f</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -5490,12 +5518,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/forbright-files-for-ipo-pitching-middle-market-digital-banking</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/korea-bond-yields-may-extend-gains-on-chips-boom-analysts-say</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
+          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -5518,12 +5546,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
+          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -5541,12 +5569,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
+          <t>Korea Bond Yields Seen Gaining on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Forbright Inc., a financial services platform that focuses on middle-market lending and digital consumer banking, filed for an initial public offering showing growing deposits.</t>
+          <t>South Korea’s bonds are set to extend this year’s rout as a semiconductor boom supercharges the nation’s economic growth and adds to inflationary pressures, analysts say.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -5568,12 +5596,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/us-is-starting-to-see-heavy-job-losses-in-roles-exposed-to-ai</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/forbright-files-for-ipo-pitching-middle-market-digital-banking</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
+          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -5596,7 +5624,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
+          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -5619,12 +5647,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
+          <t>Forbright Files for IPO Pitching Middle Market, Digital Banking</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Several US occupations expected to be impacted by artificial intelligence saw heavy job losses for a second year in 2025, led by customer service representatives and certain types of secretaries and salespeople.</t>
+          <t>Forbright Inc., a financial services platform that focuses on middle-market lending and digital consumer banking, filed for an initial public offering showing growing deposits.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -5646,17 +5674,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/us-is-starting-to-see-heavy-job-losses-in-roles-exposed-to-ai</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5674,12 +5702,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -5697,12 +5725,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>US Is Starting to See Heavy Job Losses in Roles Exposed to AI</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
+          <t>Several US occupations expected to be impacted by artificial intelligence saw heavy job losses for a second year in 2025, led by customer service representatives and certain types of secretaries and salespeople.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -5724,12 +5752,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
+          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -5752,7 +5780,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -5775,12 +5803,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chatting with AI has quickly become a critical part of how people get information and ask important questions. These questions can be deeply sensitive or personal, like health issues, loan details, or career advice. Today, we’re launching Incognito Chat with Meta AI on WhatsApp and the Meta AI app, </t>
+          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -5802,12 +5830,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
+          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing a Completely Private Way to Chat With AI</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -5830,12 +5858,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing a Completely Private Way to Chat With AI</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -5853,12 +5881,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing a Completely Private Way to Chat With AI</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
+          <t xml:space="preserve">Chatting with AI has quickly become a critical part of how people get information and ask important questions. These questions can be deeply sensitive or personal, like health issues, loan details, or career advice. Today, we’re launching Incognito Chat with Meta AI on WhatsApp and the Meta AI app, </t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -5880,12 +5908,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
+          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -5908,12 +5936,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -5931,12 +5959,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
+          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -5958,12 +5986,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
+          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -5986,12 +6014,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6009,12 +6037,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
+          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -6036,17 +6064,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
+          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6064,12 +6092,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -6087,12 +6115,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
+          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -6114,12 +6142,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6142,12 +6170,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6165,12 +6193,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
+          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -6192,17 +6220,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6220,7 +6248,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -6243,12 +6271,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
+          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -6270,12 +6298,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
+          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6298,7 +6326,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -6321,12 +6349,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
+          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -6348,12 +6376,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
+          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -6376,12 +6404,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -6399,12 +6427,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
+          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -6426,12 +6454,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
+          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6454,7 +6482,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -6477,12 +6505,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
+          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -6504,12 +6532,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
+          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6532,7 +6560,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -6555,12 +6583,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
+          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -6582,12 +6610,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
+          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6610,12 +6638,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6633,12 +6661,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
+          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -6660,12 +6688,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
+          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6688,7 +6716,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -6711,12 +6739,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
+          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -6738,12 +6766,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
+          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6766,7 +6794,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -6789,12 +6817,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
+          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -6816,12 +6844,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
+          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6844,7 +6872,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -6867,12 +6895,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
+          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -6894,12 +6922,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
+          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6922,7 +6950,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -6945,12 +6973,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
+          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -6972,12 +7000,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
+          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -7000,12 +7028,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -7023,12 +7051,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
+          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -7050,12 +7078,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/11/tiktok-launches-an-ad-free-subscription-plan-in-the-uk/</t>
+          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TikTok launches an ad-free subscription plan in the UK</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -7078,7 +7106,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>TikTok launches an ad-free subscription plan in the UK</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -7101,12 +7129,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>TikTok launches an ad-free subscription plan in the UK</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Users who sign up for the plan won’t see ads on TikTok, and their data won’t be used for advertising purposes.</t>
+          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -7128,17 +7156,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
+          <t>https://techcrunch.com/2026/05/11/tiktok-launches-an-ad-free-subscription-plan-in-the-uk/</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>TikTok launches an ad-free subscription plan in the UK</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7156,12 +7184,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>TikTok launches an ad-free subscription plan in the UK</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -7179,12 +7207,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>TikTok launches an ad-free subscription plan in the UK</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
+          <t>Users who sign up for the plan won’t see ads on TikTok, and their data won’t be used for advertising purposes.</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -7206,12 +7234,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
+          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -7234,12 +7262,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7257,12 +7285,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
+          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -7284,12 +7312,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
+          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7312,7 +7340,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -7335,12 +7363,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
+          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
@@ -7362,12 +7390,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
+          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7390,7 +7418,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -7413,12 +7441,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
+          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -7440,12 +7468,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
+          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -7468,12 +7496,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -7491,12 +7519,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
+          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -7518,12 +7546,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
+          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -7546,7 +7574,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -7569,12 +7597,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
+          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -7596,12 +7624,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/cisco-cuts-nearly-4000-jobs-to-spend-more-on-ai-reports-record-quarterly-revenue/</t>
+          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -7624,7 +7652,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -7647,12 +7675,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>This is Cisco's latest layoff in recent years, while the company's chief executive touts record revenue and growth.</t>
+          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -7674,12 +7702,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/who-decides-what-ai-tells-you-campbell-brown-once-metas-news-chief-has-thoughts/</t>
+          <t>https://techcrunch.com/2026/05/14/cisco-cuts-nearly-4000-jobs-to-spend-more-on-ai-reports-record-quarterly-revenue/</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Who decides what AI tells you? Campbell Brown, once Meta’s news chief, has thoughts</t>
+          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7702,7 +7730,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Who decides what AI tells you? Campbell Brown, once Meta’s news chief, has thoughts</t>
+          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -7725,12 +7753,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Who decides what AI tells you? Campbell Brown, once Meta’s news chief, has thoughts</t>
+          <t>Cisco cuts nearly 4,000 jobs to spend more on AI, reports ‘record quarterly revenue’</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>"The conversation is sort of happening in Silicon Valley around one thing, and a totally different conversation is happening among consumers," Campbell Brown said at StrictlyVC.</t>
+          <t>This is Cisco's latest layoff in recent years, while the company's chief executive touts record revenue and growth.</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -8532,17 +8560,17 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://baotintuc.vn/video/quan-ly-via-he-minh-bach-hon-nho-cong-nghe-20260517221259840.htm</t>
+          <t>https://www.bloomberg.com/news/newsletters/2026-05-17/ios-27-siri-app-to-have-auto-deleting-chats-siri-may-be-a-beta-genmoji-mp9udydr</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Quản lý vỉa hè minh bạch hơn nhờ công nghệ</t>
+          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>baotintuc_money</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -8560,7 +8588,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Quản lý vỉa hè minh bạch hơn nhờ công nghệ</t>
+          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -8583,28 +8611,24 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Quản lý vỉa hè minh bạch hơn nhờ công nghệ</t>
+          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 15/5, phường An Đông (TP Hồ Chí Minh) triển khai ứng dụng đăng ký và thanh toán trực tuyến sử dụng tạm thời lòng đường, vỉa hè bằng mã QR. Mô hình này giúp người dân giảm thủ tục đi lại, tăng tính minh bạch trong quản lý và là bước thử nghiệm đáng chú ý trong chuyển đổi số đô thị tại cơ sở.</t>
-        </is>
-      </c>
-      <c r="Q105" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
+          <t>Also: A Genmoji upgrade is coming in iOS 27.</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr"/>
       <c r="S105" s="2" t="n">
         <v>2.6</v>
       </c>
       <c r="T105" s="2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U105" s="2" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="V105" s="2" t="inlineStr"/>
     </row>
@@ -8614,17 +8638,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/newsletters/2026-05-17/ios-27-siri-app-to-have-auto-deleting-chats-siri-may-be-a-beta-genmoji-mp9udydr</t>
+          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8642,12 +8666,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -8665,12 +8689,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Apple’s New ChatGPT-Like Siri App Will Have Auto-Deleting Chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Also: A Genmoji upgrade is coming in iOS 27.</t>
+          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
@@ -8692,22 +8716,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>3 - Market signal</t>
+          <t>2 - Minor signal</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -8720,12 +8744,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8735,7 +8759,7 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr"/>
@@ -8743,104 +8767,26 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
+          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr"/>
       <c r="S107" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U107" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>2.52</v>
-      </c>
       <c r="V107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>scmp_tech</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>2 - Minor signal</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Market Pulse</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>Trung quốc</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr"/>
-      <c r="R108" s="2" t="inlineStr"/>
-      <c r="S108" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U108" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V108" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
@@ -8854,7 +8800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10394,27 +10340,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://baotintuc.vn/the-gioi/campuchia-duoc-xep-hang-dung-dau-the-gioi-ve-moi-truong-tu-nhien-nam-2026-20260517215852473.htm</t>
+          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>baotintuc_money</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Campuchia được xếp hạng đứng đầu thế giới về môi trường tự nhiên năm 2026</t>
+          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_724433ffce566d5f</t>
+          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -10425,27 +10371,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://baotintuc.vn/van-de-quan-tam/canh-bao-nguy-co-lu-quet-sat-lo-dat-o-5-tinh-bac-bo-va-trung-bo-20260517213104470.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-giai-phap-nguon-nen-cho-lo-trinh-nang-luong-quoc-gia-ben-vung.htm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>baotintuc_money</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cảnh báo nguy cơ lũ quét, sạt lở đất ở 5 tỉnh Bắc Bộ và Trung Bộ</t>
+          <t>Điện hạt nhân quy mô nhỏ: Giải pháp “nguồn nền” cho lộ trình năng lượng quốc gia bền vững</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_20331d3bb6f2fe8b</t>
+          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -10456,7 +10402,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-tu-giai-phap-tiem-nang-den-thi-truong-ty-usd.htm</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10466,12 +10412,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
+          <t>Điện hạt nhân quy mô nhỏ: Từ giải pháp tiềm năng đến thị trường tỷ USD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10487,7 +10433,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-giai-phap-nguon-nen-cho-lo-trinh-nang-luong-quoc-gia-ben-vung.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10497,7 +10443,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ: Giải pháp “nguồn nền” cho lộ trình năng lượng quốc gia bền vững</t>
+          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10507,7 +10453,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_66f393fea931b3bb</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -10518,7 +10464,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-tu-giai-phap-tiem-nang-den-thi-truong-ty-usd.htm</t>
+          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10528,17 +10474,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ: Từ giải pháp tiềm năng đến thị trường tỷ USD</t>
+          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_33371aef61a2861a</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -10549,7 +10495,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
+          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10559,17 +10505,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
+          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_66f393fea931b3bb</t>
+          <t>DUPLICATE_OF_fc44824132db1c02</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -10580,7 +10526,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
+          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10590,7 +10536,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
+          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -10600,7 +10546,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_33371aef61a2861a</t>
+          <t>DUPLICATE_OF_bd1eda655234ed35</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -10611,7 +10557,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10621,17 +10567,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
+          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_fc44824132db1c02</t>
+          <t>DUPLICATE_OF_20331d3bb6f2fe8b</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -10642,7 +10588,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
+          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10652,17 +10598,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
+          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_bd1eda655234ed35</t>
+          <t>DUPLICATE_OF_3150ccb709b5f656</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -10673,7 +10619,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
+          <t>https://vneconomy.vn/techconnect/vien-truong-vinatom-phat-trien-dien-hat-nhan-an-toan-la-so-mot-khong-co-ngoai-le.htm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10683,17 +10629,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
+          <t>Viện trưởng VINATOM: "Phát triển điện hạt nhân, an toàn là số một, không có ngoại lệ"</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_20331d3bb6f2fe8b</t>
+          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -10704,7 +10650,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
+          <t>https://vneconomy.vn/techconnect/cmc-tai-cau-truc-khoi-cong-nghe-va-giai-phap-thuc-day-muc-tieu-chuyen-doi-ai.htm</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10714,17 +10660,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
+          <t>CMC tái cấu trúc Khối Công nghệ và Giải pháp, thúc đẩy mục tiêu chuyển đổi AI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3150ccb709b5f656</t>
+          <t>DUPLICATE_OF_33371aef61a2861a</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -10735,7 +10681,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/vien-truong-vinatom-phat-trien-dien-hat-nhan-an-toan-la-so-mot-khong-co-ngoai-le.htm</t>
+          <t>https://vneconomy.vn/techconnect/them-giai-phap-ai-make-in-vietnam-dat-chuan-quoc-te-ve-chong-gia-mao-khuon-mat.htm</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10745,17 +10691,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Viện trưởng VINATOM: "Phát triển điện hạt nhân, an toàn là số một, không có ngoại lệ"</t>
+          <t>Thêm giải pháp AI "Make in Vietnam" đạt chuẩn quốc tế về chống giả mạo khuôn mặt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_fc44824132db1c02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -10766,22 +10712,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cmc-tai-cau-truc-khoi-cong-nghe-va-giai-phap-thuc-day-muc-tieu-chuyen-doi-ai.htm</t>
+          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vneconomy_lifestyle</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CMC tái cấu trúc Khối Công nghệ và Giải pháp, thúc đẩy mục tiêu chuyển đổi AI</t>
+          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10797,27 +10743,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/them-giai-phap-ai-make-in-vietnam-dat-chuan-quoc-te-ve-chong-gia-mao-khuon-mat.htm</t>
+          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vneconomy_lifestyle</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thêm giải pháp AI "Make in Vietnam" đạt chuẩn quốc tế về chống giả mạo khuôn mặt</t>
+          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_fc44824132db1c02</t>
+          <t>DUPLICATE_OF_25d6aed75f4f125f</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -10828,27 +10774,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
+          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>vneconomy_lifestyle</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
+          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_33371aef61a2861a</t>
+          <t>DUPLICATE_OF_518231b28978900a</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -10859,27 +10805,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
+          <t>https://vneconomy.vn/techconnect/dich-vu-cong-chinh-quyen-2-cap-nguoi-dan-van-phai-di-nhieu-cua-thay-vi-mot-cua.htm</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>vneconomy_lifestyle</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
+          <t>Dịch vụ công chính quyền 2 cấp: Người dân vẫn phải đi “nhiều cửa” thay vì “một cửa”</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_25d6aed75f4f125f</t>
+          <t>DUPLICATE_OF_0243da4a465c350b</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -10890,27 +10836,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
+          <t>https://www.grab.com/vn/blog/uu-dai-ngan-hang-acb/</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>grab_vn_blog</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>Ưu đãi ngân hàng ACB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_518231b28978900a</t>
+          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -10921,27 +10863,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dich-vu-cong-chinh-quyen-2-cap-nguoi-dan-van-phai-di-nhieu-cua-thay-vi-mot-cua.htm</t>
+          <t>https://www.grab.com/vn/blog/uu-dai-ngan-hang-hd-bank/</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>grab_vn_blog</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dịch vụ công chính quyền 2 cấp: Người dân vẫn phải đi “nhiều cửa” thay vì “một cửa”</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>Ưu đãi ngân hàng HD Bank</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_0243da4a465c350b</t>
+          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -10952,7 +10890,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/uu-dai-ngan-hang-acb/</t>
+          <t>https://www.grab.com/vn/blog/thong-tin-khuyen-mai-cua-chuong-trinh-grabfood-van-deal-mastximum-giam-50/</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10962,13 +10900,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ưu đãi ngân hàng ACB</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>THÔNG TIN KHUYẾN MẠI CỦA CHƯƠNG TRÌNH GRABFOOD VẠN DEAL MASTXIMUM GIẢM 50%</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
+          <t>DUPLICATE_OF_1566e1c9c20215f6</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -10979,23 +10921,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/uu-dai-ngan-hang-hd-bank/</t>
+          <t>https://banhang.shopee.vn/edu/article/21087</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ưu đãi ngân hàng HD Bank</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>TỔNG HỢP CÁC MỨC PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
+          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -11006,27 +10952,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/uu-dai-ngan-hang-tpbank/</t>
+          <t>https://vnexpress.net/50-nguoi-lai-xe-may-o-viet-nam-thuong-xuyen-dung-ung-dung-chi-duong-5072524.html</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ưu đãi ngân hàng TPBank</t>
+          <t>50% người lái xe máy ở Việt Nam thường xuyên dùng ứng dụng chỉ đường</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
+          <t>DUPLICATE_OF_8576657079afb8be</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -11037,27 +10983,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
+          <t>https://banhang.shopee.vn/edu/article/27541</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_a953e393438407c7</t>
+          <t>DUPLICATE_OF_8dd169053649c0d3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -11068,27 +11014,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/tin-tuc-su-kien/tham-gia-vong-song-khoe-nhan-qua-co-tri-gia-den-8707</t>
+          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>zalopay_news</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
+          <t>Tin tức</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_a953e393438407c7</t>
+          <t>DUPLICATE_OF_a7169d7312fe0349</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -11099,27 +11041,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
+          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>luatvietnam_chinhsach</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -11130,23 +11068,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/21087</t>
+          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TỔNG HỢP CÁC MỨC PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -11157,23 +11095,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/25329</t>
+          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -11184,27 +11122,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27541</t>
+          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -11215,27 +11149,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
+          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3a8cf1ca92908565</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -11246,27 +11176,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
+          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6c378659e2a97449</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -11277,23 +11203,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27358</t>
+          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] Thông báo phát hành Chứng từ khấu trừ thuế 2025 đối với hoạt động kinh doanh trên Shopee</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -11304,23 +11230,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/16440</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hướng dẫn quay video màn hình khi Người Bán cần Shopee hỗ trợ</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>China’s Energy Boom Could Give It the AI Edge</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3a8cf1ca92908565</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -11331,23 +11261,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/26981</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] Cập nhật địa chỉ theo đơn vị hành chính mới</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -11358,23 +11292,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27284</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[Mới] Shopee Chat: Danh sách sản phẩm Người mua quan tâm và tính năng Mời đặt hàng</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -11385,23 +11323,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/26506</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[MỚI] Cập nhật trang Tất Cả Sản Phẩm trên Kênh Người Bán</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -11412,23 +11354,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/26654</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[MỚI] Công cụ Tối ưu sản phẩm bởi AI trên Shopee</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6c378659e2a97449</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -11439,23 +11385,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>zalopay_news</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tin tức</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_a7169d7312fe0349</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -11466,23 +11416,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/spacex-shareholders-approve-5-for-1-split-of-common-stock</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>SpaceX Holders Sign Off on 5-for-1 Stock Split Ahead of IPO</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -11493,23 +11447,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-15/the-close-5-15-2026-video</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Global Bond Selloff Deepens as Oil Prices Rise | The Close 5/15/2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -11520,23 +11478,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/arm-holdings-said-to-face-us-antitrust-probe-over-chip-tech</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Arm Holdings to Face US Antitrust Probe Over Chip Tech</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -11547,23 +11509,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/trump-xi-summit-yields-warm-rhetoric-few-takeaways-on-trade-and-iran</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>From Trade to Taiwan, What the Trump-Xi Summit Did (and Didn’t) Accomplish</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -11574,23 +11540,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-15/sheila-bair-on-finding-a-good-workplace-video</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Sheila Bair on Finding a Good Workplace</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -11601,23 +11571,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-15/figure-ceo-says-humanoid-robot-test-had-no-outside-aid-video</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Figure CEO Says No Teleoperation in Their Humanoid Robot Testing</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -11628,23 +11602,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-15/figma-jumps-as-results-ease-ai-disruption-concerns-video</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Figma Jumps as Results Ease AI Disruption Concerns</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -11655,7 +11633,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-15/us-chip-sector-needs-more-talent-says-semi-video</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11665,12 +11643,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>China’s Energy Boom Could Give It the AI Edge</t>
+          <t>US Chip Sector Needs More Talent, Says SEMI</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -11686,17 +11664,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
+          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>luatvietnam_chinhsach</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
+          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11717,22 +11695,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
+          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
+          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11748,22 +11726,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
+          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_wechat</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
+          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11779,22 +11757,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
+          <t>China ramps up building a national computing power network as AI token demand surges</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11810,22 +11788,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
+          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11841,22 +11819,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/spacex-shareholders-approve-5-for-1-split-of-common-stock</t>
+          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SpaceX Holders Sign Off on 5-for-1 Stock Split Ahead of IPO</t>
+          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11872,22 +11850,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/the-close-5-15-2026-video</t>
+          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Global Bond Selloff Deepens as Oil Prices Rise | The Close 5/15/2026</t>
+          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11903,22 +11881,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/arm-holdings-said-to-face-us-antitrust-probe-over-chip-tech</t>
+          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Arm Holdings to Face US Antitrust Probe Over Chip Tech</t>
+          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11934,22 +11912,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/trump-xi-summit-yields-warm-rhetoric-few-takeaways-on-trade-and-iran</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>From Trade to Taiwan, What the Trump-Xi Summit Did (and Didn’t) Accomplish</t>
+          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11965,27 +11943,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/sheila-bair-on-finding-a-good-workplace-video</t>
+          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sheila Bair on Finding a Good Workplace</t>
+          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_HEALTHCARE</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -11996,22 +11974,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/figure-ceo-says-humanoid-robot-test-had-no-outside-aid-video</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Figure CEO Says No Teleoperation in Their Humanoid Robot Testing</t>
+          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -12027,22 +12005,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/figma-jumps-as-results-ease-ai-disruption-concerns-video</t>
+          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Figma Jumps as Results Ease AI Disruption Concerns</t>
+          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -12058,22 +12036,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/us-chip-sector-needs-more-talent-says-semi-video</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US Chip Sector Needs More Talent, Says SEMI</t>
+          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12089,22 +12067,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-15/cerebras-ceo-worth-3-2-billion-after-year-s-largest-ipo-video</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cerebras CEO Is Worth $3.2 Billion After Year’s Largest IPO</t>
+          <t>China ranks third in global index for AI competitiveness in life sciences</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -12120,22 +12098,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-14/fermi-reworks-board-rules-to-thwart-ex-ceo-s-push-to-remake-firm</t>
+          <t>https://www.scmp.com/business/china-evs/article/3353028/chinese-6-seat-electric-suvs-stand-out-amid-weak-domestic-sales-says-morgan-stanley?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fermi Alters Rules to Foil Ex-CEO Push to Remake Board</t>
+          <t>Chinese 6-seat electric SUVs to stand out amid weak domestic sales, Morgan Stanley says</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -12151,17 +12129,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/newsletters/2026-05-15/meet-atari-s-tycoon-ceo-who-is-aiming-for-a-retro-gaming-revival</t>
+          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atari’s Tycoon CEO Is Aiming for a New Retro Revival</t>
+          <t>Osaurus brings both local and cloud AI models to your Mac</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -12182,17 +12160,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
+          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
+          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -12213,22 +12191,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
+          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>scmp_wechat</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
+          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12244,22 +12222,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>China ramps up building a national computing power network as AI token demand surges</t>
+          <t>Indigo brings the open social web to one app</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12275,22 +12253,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/17/if-youre-giving-a-commencement-speech-in-2026-maybe-dont-mention-ai/</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
+          <t>If you’re giving a commencement speech in 2026, maybe don’t mention AI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12306,22 +12284,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/17/techcrunch-mobility-the-ai-skills-arms-race-is-coming-for-automotive/</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
+          <t>TechCrunch Mobility: The AI skills arms race is coming for automotive</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12337,22 +12315,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
+          <t>The haves and have nots of the AI gold rush</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12368,22 +12346,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
+          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12399,22 +12377,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
+          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12430,27 +12408,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
+          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>T3_HEALTHCARE</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -12461,22 +12439,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
+          <t>What happens when AI starts building itself?</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12492,22 +12470,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
+          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12523,22 +12501,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
+          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
+          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12554,22 +12532,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
+          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>China ranks third in global index for AI competitiveness in life sciences</t>
+          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12585,22 +12563,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-evs/article/3353028/chinese-6-seat-electric-suvs-stand-out-amid-weak-domestic-sales-says-morgan-stanley?utm_source=rss_feed</t>
+          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chinese 6-seat electric SUVs to stand out amid weak domestic sales, Morgan Stanley says</t>
+          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12616,22 +12594,22 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
+          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Osaurus brings both local and cloud AI models to your Mac</t>
+          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12647,22 +12625,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
+          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
+          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12678,22 +12656,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
+          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
+          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12709,22 +12687,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
+          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Indigo brings the open social web to one app</t>
+          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12740,22 +12718,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The haves and have nots of the AI gold rush</t>
+          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12771,22 +12749,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
+          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
+          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12802,22 +12780,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
+          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
+          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12833,22 +12811,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
+          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
+          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12864,22 +12842,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
+          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>What happens when AI starts building itself?</t>
+          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12895,22 +12873,22 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
+          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
+          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12926,22 +12904,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/wirestock-raises-23m-to-supply-multi-modal-data-to-ai-labs/</t>
+          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Wirestock raises $23M to supply creative multimodal data to AI labs</t>
+          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12957,17 +12935,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
+          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
+          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -12988,17 +12966,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
+          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
+          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -13019,22 +12997,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
+          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
+          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -13050,22 +13028,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
+          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
+          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -13081,22 +13059,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
+          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
+          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -13112,22 +13090,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
+          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
+          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -13143,22 +13121,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
+          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
+          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -13174,22 +13152,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
+          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
+          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13205,22 +13183,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
+          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
+          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13236,22 +13214,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13267,17 +13245,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
+          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
+          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -13298,7 +13276,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
+          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13308,12 +13286,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
+          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13329,7 +13307,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
+          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13339,12 +13317,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
+          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13360,7 +13338,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
+          <t>https://vnexpress.net/cong-ty-trung-quoc-ra-mat-robot-cho-nguoi-co-the-bien-hinh-5073389.html</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13370,12 +13348,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
+          <t>Công ty Trung Quốc ra mắt robot chở người có thể biến hình</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13391,22 +13369,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
+          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
+          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13422,7 +13400,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
+          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13432,12 +13410,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
+          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13453,7 +13431,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
+          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13463,12 +13441,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
+          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13484,7 +13462,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
+          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13494,12 +13472,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
+          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13515,7 +13493,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
+          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13525,12 +13503,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
+          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -13546,7 +13524,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
+          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13556,12 +13534,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
+          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -13577,7 +13555,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
+          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13587,7 +13565,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
+          <t>Vai trò của sách trong thời AI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13608,7 +13586,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/50-nguoi-lai-xe-may-o-viet-nam-thuong-xuyen-dung-ung-dung-chi-duong-5072524.html</t>
+          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13618,12 +13596,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>50% người lái xe máy ở Việt Nam thường xuyên dùng ứng dụng chỉ đường</t>
+          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13639,22 +13617,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>https://vnexpress.net/thu-nghiem-uav-cho-nong-nghiep-tai-dien-bien-5073530.html</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Thử nghiệm UAV cho nông nghiệp tại Điện Biên</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13670,22 +13648,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
+          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
+          <t>Giá vàng được dự báo giảm tiếp tuần sau</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13701,22 +13679,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
+          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
+          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13732,22 +13710,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
+          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
+          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13763,22 +13741,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-trung-quoc-ra-mat-robot-cho-nguoi-co-the-bien-hinh-5073389.html</t>
+          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Công ty Trung Quốc ra mắt robot chở người có thể biến hình</t>
+          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -13794,22 +13772,22 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
+          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
+          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -13825,22 +13803,22 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
+          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13856,22 +13834,22 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
+          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
+          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13887,22 +13865,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
+          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
+          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -13918,22 +13896,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
+          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
+          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -13949,22 +13927,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
+          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
+          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -13980,27 +13958,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
+          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Vai trò của sách trong thời AI</t>
+          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_SPORTS</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -14011,22 +13989,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
+          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
+          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14042,22 +14020,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-nghiem-uav-cho-nong-nghiep-tai-dien-bien-5073530.html</t>
+          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Thử nghiệm UAV cho nông nghiệp tại Điện Biên</t>
+          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14073,7 +14051,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
+          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14083,12 +14061,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Giá vàng được dự báo giảm tiếp tuần sau</t>
+          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -14104,7 +14082,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14114,12 +14092,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -14135,7 +14113,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14145,12 +14123,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -14166,7 +14144,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14176,12 +14154,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -14197,7 +14175,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
+          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14207,7 +14185,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
+          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -14228,7 +14206,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
+          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14238,7 +14216,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
+          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -14259,7 +14237,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
+          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14269,12 +14247,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
+          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -14290,7 +14268,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14300,12 +14278,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -14321,7 +14299,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14331,12 +14309,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -14352,7 +14330,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
+          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14362,12 +14340,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
+          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -14383,7 +14361,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
+          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14393,17 +14371,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
+          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>T3_SPORTS</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -14414,7 +14392,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
+          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14424,12 +14402,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
+          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -14445,7 +14423,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14455,12 +14433,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -14476,7 +14454,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14486,12 +14464,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -14507,7 +14485,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14517,12 +14495,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -14538,22 +14516,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14569,22 +14547,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -14600,22 +14578,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
+          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
+          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14625,626 +14603,6 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Giá xăng, dầu cùng giảm</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>vnexpress_kinhdoanh</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/thoi-su/ket-thuc-hoat-dong-va-giai-the-quy-ho-tro-phu-nu-ngheo-20260517221023442.htm</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Kết thúc hoạt động và giải thể Quỹ Hỗ trợ Phụ nữ nghèo</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/doanh-nghiep-san-pham-dich-vu/dai-hoi-dong-co-dong-tnh-chuyen-tu-tang-quy-mo-sang-toi-uu-hieu-qua-20260517215926287.htm</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Đại hội đồng cổ đông TNH: Chuyển từ tăng quy mô sang tối ưu hiệu quả</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/thoi-su/70-cong-nghe-cao-duoc-uu-tien-dau-tu-phat-trien-20260517220906187.htm</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>70 công nghệ cao được ưu tiên đầu tư phát triển</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/giao-duc/israel-cam-hoc-sinh-trung-hoc-co-so-su-dung-dien-thoai-trong-truong-hoc-20260517220053420.htm</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Israel cấm học sinh trung học cơ sở sử dụng điện thoại trong trường học</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/nguoi-viet-4-phuong/chuan-hoa-ky-thi-nang-luc-tieng-viet-dau-moc-dua-tieng-viet-bay-xa-20260517214954324.htm</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Chuẩn hóa kỳ thi năng lực tiếng Việt – Dấu mốc đưa tiếng Việt bay xa</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/van-hoa/khai-mac-cuoc-thi-tai-nang-dien-vien-cai-luong-toan-quoc-2026-20260517212532233.htm</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Khai mạc Cuộc thi Tài năng diễn viên cải lương toàn quốc 2026</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>https://baotintuc.vn/the-gioi/my-sa-thai-hang-tram-nhan-vien-ngoai-giao-giua-luc-doi-mat-nhieu-khung-hoang-20260517205553441.htm</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>baotintuc_money</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Mỹ sa thải hàng trăm nhân viên ngoại giao giữa lúc đối mặt nhiều khủng hoảng</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>vneconomy_techconnect</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>vneconomy_techconnect</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>vneconomy_techconnect</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>NO_KEYWORD</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="b">
         <v>0</v>
       </c>
     </row>
@@ -15318,12 +14676,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15332,13 +14690,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15348,12 +14706,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -15362,13 +14720,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -15378,12 +14736,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -15408,12 +14766,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15438,12 +14796,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15468,12 +14826,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15498,12 +14856,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15528,12 +14886,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15542,10 +14900,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -15558,12 +14916,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15572,10 +14930,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
@@ -15588,12 +14946,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15618,12 +14976,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15648,12 +15006,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15678,12 +15036,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15708,12 +15066,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15722,13 +15080,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -15738,12 +15096,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -15768,12 +15126,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -15798,12 +15156,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -15828,12 +15186,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -15858,12 +15216,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15872,13 +15230,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -15888,12 +15246,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15905,25 +15263,25 @@
         <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15948,12 +15306,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15978,12 +15336,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -16008,12 +15366,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -16038,12 +15396,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -16068,12 +15426,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16098,12 +15456,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -16128,12 +15486,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -16158,12 +15516,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -16188,12 +15546,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16218,12 +15576,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16235,10 +15593,10 @@
         <v>50</v>
       </c>
       <c r="E32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -16248,12 +15606,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16278,12 +15636,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16308,12 +15666,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16338,12 +15696,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16368,12 +15726,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-17T15:37:21.392307+00:00</t>
+          <t>2026-05-17T17:20:49.761303+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-17T15:43:05.096468+00:00</t>
+          <t>2026-05-17T17:26:37.583100+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">

--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:V109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -898,17 +898,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
+          <t>https://blog.whatsapp.com/helping-billions-ring-in-the-new-year-on-whatsapp</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Helping billions ring in the New Year on WhatsApp</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -926,22 +926,18 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>Helping billions ring in the New Year on WhatsApp</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Trong nước</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -949,24 +945,24 @@
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+          <t>Helping billions ring in the New Year on WhatsApp</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
+          <t xml:space="preserve">New Year’s is our biggest day at WhatsApp, with each year breaking new records for how people text and call their friends and loved ones. On a regular day, we support over 100 billion messages and 2 billion calls - but the twenty four hours when the world welcomes a New Year always tops our charts. </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>3.42</v>
+        <v>3.52</v>
       </c>
       <c r="V6" s="2" t="inlineStr"/>
     </row>
@@ -976,26 +972,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/traicaysachanvatvoduyninh</t>
+          <t>https://vnexpress.net/thu-giu-loat-hang-gia-o-saigon-square-cho-ben-thanh-5074046.html</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>grab_merchant_vn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3 - Market signal</t>
+          <t>4 - Strategic shift</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1004,18 +1000,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Trong nước</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -1023,24 +1023,24 @@
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
+          <t>Thu giữ loạt hàng giả ở Saigon Square, chợ Bến Thành</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hơn 21 năm gắn bó với nghề kinh doanh mỹ phẩm theo mô hình truyền thống, chị Ngọc Diệp đã trải qua những ngày thử thách và biến động bởi đại dịch Covid-19. Từ việc phải tạm đóng cửa hàng mỹ phẩm và trăn trở giải quyết bài toán xoay vốn, hiện tại chị Diệp đã sở hữu cửa hàng online hoạt động ổn định, </t>
+          <t>Quản lý thị trường TP HCM vừa kiểm tra đột xuất Saigon Square và chợ Bến Thành thu giữ nhiều hàng giả, không rõ nguồn gốc và xử phạt hơn nửa tỷ đồng.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="U7" s="2" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="V7" s="2" t="inlineStr"/>
     </row>
@@ -1050,17 +1050,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/dealhoidonkhachmoi</t>
+          <t>https://blog.whatsapp.com/introducing-incognito-chat-with-meta-ai-a-completely-private-way-to-chat-with-ai</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
+          <t>Introducing Incognito Chat with Meta AI: A completely private way to chat with AI</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>grab_merchant_vn</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,14 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
+          <t>Introducing Incognito Chat with Meta AI: A completely private way to chat with AI</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -1097,12 +1101,12 @@
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
+          <t>Introducing Incognito Chat with Meta AI: A completely private way to chat with AI</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Quý Đối tác thân mến, 🤗 Đối tác mong muốn thu hút thêm nhiều Người dùng mới đến nhà hàng trải nghiệm món ngon ? 🤗 Đối tác đang tìm kiếm chiến dịch marketing với ngân sách tối ưu để tiếp cận Người dùng mới ? Mời Đối tác tham gia chương trình “Deal Hời Đón Khách Mới” - giải pháp giúp thu hút và mở rộn</t>
+          <t>Chatting with AI has quickly become a critical part of how people get information and ask important questions. And many of these questions can be deeply sensitive, or include situations where people are including private financial, personal, health or work data with their questions. Ten years ago we</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -1124,12 +1128,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/gfin-vc-hoan01thanglaivay</t>
+          <t>https://merchant.grab.com/vn-vn/blog/traicaysachanvatvoduyninh</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1152,7 +1156,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1171,12 +1175,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
+          <t>GrabMart | Đảm việc nhà - Giỏi kinh doanh nhờ nắm bắt xu hướng bán hàng qua ứng dụng</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Quý Đối tác thân mến, Công ty TNHH GFIN Việt Nam (“GFIN”) mang đến cho các Đối tác Tài xế, Đối tác Thương nhân chương trình Hoàn tiền lãi 01 tháng cho các khoản vay tín chấp với thương hiệu TIN VAY của VietCredit (“TIN VAY”). TIN VAY hoàn tiền lãi trung bình 01 tháng trực tiếp vào khoản vay: Giá trị</t>
+          <t xml:space="preserve">Hơn 21 năm gắn bó với nghề kinh doanh mỹ phẩm theo mô hình truyền thống, chị Ngọc Diệp đã trải qua những ngày thử thách và biến động bởi đại dịch Covid-19. Từ việc phải tạm đóng cửa hàng mỹ phẩm và trăn trở giải quyết bài toán xoay vốn, hiện tại chị Diệp đã sở hữu cửa hàng online hoạt động ổn định, </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1198,12 +1202,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/grabmart-bikiptangtruongdoanhthu-saurieng</t>
+          <t>https://merchant.grab.com/vn-vn/blog/dealhoidonkhachmoi</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1245,12 +1249,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
+          <t>Grab | Giải pháp tăng trưởng Người dùng mới (dành cho dịch vụ Đi Ăn Nhà Hàng)</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quý Đối tác Thương nhân ơi, Mùa hè gõ cửa - cũng là lúc sầu riêng vào mùa, thơm lừng và cực kỳ hút khách . Nhu cầu tìm kiếm “sầu riêng” dự kiến tăng nhanh trên Grabmart. Đây chính là thời điểm vàng để Đối tác bứt phá doanh thu ! 🔥 Nắm bắt thời điểm vàng– lên kệ ngay hôm nay để đón đầu nhu cầu Người </t>
+          <t>Quý Đối tác thân mến, 🤗 Đối tác mong muốn thu hút thêm nhiều Người dùng mới đến nhà hàng trải nghiệm món ngon ? 🤗 Đối tác đang tìm kiếm chiến dịch marketing với ngân sách tối ưu để tiếp cận Người dùng mới ? Mời Đối tác tham gia chương trình “Deal Hời Đón Khách Mới” - giải pháp giúp thu hút và mở rộn</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1272,12 +1276,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/traicay2026</t>
+          <t>https://merchant.grab.com/vn-vn/blog/gfin-vc-hoan01thanglaivay</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1319,12 +1323,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
+          <t>GFIN x VIETCREDIT | Chương trình hoàn tiền 01 tháng lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Quý Đối tác GrabMart thân mến, 🥑🥑 Mùa hè đến, trái cây chín rộ! Nhằm đồng hành và hỗ trợ Đối tác gia tăng cơ hội doanh thu trong mùa trái cây, GrabMart triển khai 02 chương trình mang đến các quyền lợi hấp dẫn dành cho Đối tác: Tặng mã freeship và đồng tài trợ ưu đãi giảm giá . Thể lệ các chương trì</t>
+          <t>Quý Đối tác thân mến, Công ty TNHH GFIN Việt Nam (“GFIN”) mang đến cho các Đối tác Tài xế, Đối tác Thương nhân chương trình Hoàn tiền lãi 01 tháng cho các khoản vay tín chấp với thương hiệu TIN VAY của VietCredit (“TIN VAY”). TIN VAY hoàn tiền lãi trung bình 01 tháng trực tiếp vào khoản vay: Giá trị</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1346,12 +1350,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://merchant.grab.com/vn-vn/blog/capnhatcachtinhdiemdanhgiasao2026</t>
+          <t>https://merchant.grab.com/vn-vn/blog/grabmart-bikiptangtruongdoanhthu-saurieng</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
+          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1365,7 +1369,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1374,14 +1378,10 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
+          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1397,19 +1397,15 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
+          <t>GrabMart | Bí kíp tăng trưởng doanh thu sầu riêng</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quý Đối tác thân mến, Khi kinh doanh trên nền tảng số, điểm đánh giá sao từ Người dùng là một trong những yếu tố quan trọng để thu hút thêm đơn hàng và xây dựng uy tín của Cửa hàng. Để đảm bảo sự công bằng, minh bạch giữa các Cửa hàng, đồng thời khuyến khích tất cả Đối tác không ngừng nâng cao chất </t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Quý Đối tác Thương nhân ơi, Mùa hè gõ cửa - cũng là lúc sầu riêng vào mùa, thơm lừng và cực kỳ hút khách . Nhu cầu tìm kiếm “sầu riêng” dự kiến tăng nhanh trên Grabmart. Đây chính là thời điểm vàng để Đối tác bứt phá doanh thu ! 🔥 Nắm bắt thời điểm vàng– lên kệ ngay hôm nay để đón đầu nhu cầu Người </t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="n">
         <v>3</v>
@@ -1428,17 +1424,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/grab-community?page=1</t>
+          <t>https://merchant.grab.com/vn-vn/blog/traicay2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>grab_merchant_vn</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1456,7 +1452,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -1475,12 +1471,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>GrabMart | Các chương trình ưu đãi dành cho ngành hàng trái cây tươi mùa hè 2026</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
+          <t>Quý Đối tác GrabMart thân mến, 🥑🥑 Mùa hè đến, trái cây chín rộ! Nhằm đồng hành và hỗ trợ Đối tác gia tăng cơ hội doanh thu trong mùa trái cây, GrabMart triển khai 02 chương trình mang đến các quyền lợi hấp dẫn dành cho Đối tác: Tặng mã freeship và đồng tài trợ ưu đãi giảm giá . Thể lệ các chương trì</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1502,17 +1498,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driven-by-tech?page=1</t>
+          <t>https://merchant.grab.com/vn-vn/blog/capnhatcachtinhdiemdanhgiasao2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
+          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>grab_merchant_vn</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1521,7 +1517,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1530,10 +1526,14 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1549,15 +1549,19 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
+          <t>Grab | Cập nhật cách tính điểm đánh giá sao Cửa hàng</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Quý Đối tác thân mến, Khi kinh doanh trên nền tảng số, điểm đánh giá sao từ Người dùng là một trong những yếu tố quan trọng để thu hút thêm đơn hàng và xây dựng uy tín của Cửa hàng. Để đảm bảo sự công bằng, minh bạch giữa các Cửa hàng, đồng thời khuyến khích tất cả Đối tác không ngừng nâng cao chất </t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="n">
         <v>3</v>
@@ -1576,12 +1580,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/pulse-of-vietnam?page=1</t>
+          <t>https://www.grab.com/vn/blog/grab-community?page=1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
+          <t>Community</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1604,7 +1608,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
+          <t>Community</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1623,7 +1627,7 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
+          <t>Community</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1650,12 +1654,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/thong-bao-trien-khai-dich-vu-grabcar-plus-grabbike-plus-tai-mot-so-tinh-thanh/</t>
+          <t>https://www.grab.com/vn/blog/driven-by-tech?page=1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+          <t>Driven by Tech</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1669,7 +1673,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1678,14 +1682,10 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
+          <t>Driven by Tech</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1701,19 +1701,15 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+          <t>Driven by Tech</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Thứ Tư Tháng Năm 13th, 2026 Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành Bạn thân mến, Nhằm đáp ứng nhu cầu di chuyển đa dạng của hành khách, Grab chính thức triển khai dịch vụ GrabCar, GrabCar Plus và GrabBike Plus tại một số tỉnh thành từ ngày 14/05/2026. Thông ti</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
+          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="n">
         <v>3</v>
@@ -1732,12 +1728,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/thu-thach-cua-tin/</t>
+          <t>https://www.grab.com/vn/blog/pulse-of-vietnam?page=1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
+          <t>Pulse of Vietnam</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1751,7 +1747,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1760,14 +1756,10 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>Pulse of Vietnam</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1783,12 +1775,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
+          <t>Pulse of Vietnam</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Ba Tháng Năm 12th, 2026 Thử thách của Tín Các bạn sinh viên ơi! Grab chính thức khởi động Thử thách “Bản đồ bung sức mùa thi cùng Grab” với nhiều phần quà vô cùng hấp dẫn trong tháng 05 tới đây. Hãy cùng Grab khám phá thể lệ chi tiết của Thử thách này nhé! 🏁 THÔNG TIN TỔNG QUAN VỀ THỬ THÁCH Tên </t>
+          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1810,12 +1802,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/bike/ugc-quantotbung/</t>
+          <t>https://www.grab.com/vn/blog/thong-bao-trien-khai-dich-vu-grabcar-plus-grabbike-plus-tai-mot-so-tinh-thanh/</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1838,12 +1830,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1861,15 +1853,19 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu Tháng Năm 15th, 2026 Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO” Quý Đối tác thân mến, Mùa nắng nóng cao điểm đã đến, những cung đường dường như dài hơn và oi ả hơn. Thế nhưng, giữa cái nắng gắt ấy, sự tử tế vẫn luôn hiện hữu qua những ly nước mát lạnh miễn </t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Thứ Tư Tháng Năm 13th, 2026 Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành Bạn thân mến, Nhằm đáp ứng nhu cầu di chuyển đa dạng của hành khách, Grab chính thức triển khai dịch vụ GrabCar, GrabCar Plus và GrabBike Plus tại một số tỉnh thành từ ngày 14/05/2026. Thông ti</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="n">
         <v>3</v>
@@ -1888,17 +1884,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/thong-bao/moi-lan-thanh-toan-hoa-don-them-mam-xanh-duoc-8709</t>
+          <t>https://www.grab.com/vn/blog/thu-thach-cua-tin/</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
+          <t>Thử thách của Tín</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>grab_vn_blog</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1916,7 +1912,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
+          <t>Thử thách của Tín</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1931,7 +1927,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>MoMo</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1939,12 +1935,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
+          <t>Thử thách của Tín</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ Thông báo · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Thay vì chỉ là những giao dịch thanh toán thông thường, giờ đây với Green Hub - Góp hóa đơn trồng rừng trên MoMo, mỗi hóa đơn bạn chi trả đều mang lại giá trị đó</t>
+          <t xml:space="preserve">Thứ Ba Tháng Năm 12th, 2026 Thử thách của Tín Các bạn sinh viên ơi! Grab chính thức khởi động Thử thách “Bản đồ bung sức mùa thi cùng Grab” với nhiều phần quà vô cùng hấp dẫn trong tháng 05 tới đây. Hãy cùng Grab khám phá thể lệ chi tiết của Thử thách này nhé! 🏁 THÔNG TIN TỔNG QUAN VỀ THỬ THÁCH Tên </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -1966,17 +1962,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/tin-tuc/tin-tuc-su-kien</t>
+          <t>https://www.grab.com/vn/blog/driver/bike/ugc-quantotbung/</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
+          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>zalopay_news</t>
+          <t>grab_vn_blog</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1994,10 +1990,14 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -2013,12 +2013,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
+          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
+          <t xml:space="preserve">Thứ Sáu Tháng Năm 15th, 2026 Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO” Quý Đối tác thân mến, Mùa nắng nóng cao điểm đã đến, những cung đường dường như dài hơn và oi ả hơn. Thế nhưng, giữa cái nắng gắt ấy, sự tử tế vẫn luôn hiện hữu qua những ly nước mát lạnh miễn </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -2040,17 +2040,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/dac-biet</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/combo-du-lich-sieu-hoi-don-chao-le-hoi-phao-hoa-8718</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -2068,10 +2068,14 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2079,7 +2083,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -2087,12 +2091,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng Khuyến mãi · 15/05/2026 · 2.7K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Lễ hội Pháo hoa Quốc tế Đà Nẵng (DIFF) 2026 chính thức quay trở lại, hứa hẹn biến bầu trời sông Hàn thành một kiệt tác nghệ thuật đầy mê h</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -2114,17 +2118,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353594/chinese-foundries-smic-hua-hong-forecast-second-quarter-growth-amid-ai-boom?utm_source=rss_feed</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/155-315-hoan-den-8686d-khi-tu-chuyen-2k-tu-ngan-8717</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2142,22 +2146,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
@@ -2165,24 +2169,32 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>China’s leading semiconductor foundries, Semiconductor Manufacturing International Corporation (SMIC) and Hua Hong Semiconductor, expect their second-quarter sales to rise amid a dynamic global market defined by surging artificial intelligence demand and a memory supply crunch, while Hua Hong said i</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr"/>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN Khuyến mãi · 15/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn MoMo thưởng đến 8.686Đ cho bạn khi thực hiện giao dịch tự chuyển 2K từ app Ngân hàng đến SĐT MoMo của chính mình. Thời gian diễn r</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
       <c r="S22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" s="2" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T22" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U22" s="2" t="n">
-        <v>3.36</v>
       </c>
       <c r="V22" s="2" t="inlineStr"/>
     </row>
@@ -2192,17 +2204,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353451/alibaba-ai-revenue-logs-triple-digit-growth-11th-quarter-amid-strategic-reshuffle?utm_source=rss_feed</t>
+          <t>https://momo.vn/tin-tuc/thong-bao/moi-lan-thanh-toan-hoa-don-them-mam-xanh-duoc-8709</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2220,22 +2232,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
@@ -2243,24 +2255,24 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding expects its annualised recurring revenue from AI models and applications to hit 30 billion yuan (US$4.42 billion) by the year’s end, as the company ramps up its AI commitment. AI products are projected to generate more than 50 per cent of Alibaba’s cloud-computing revenue withi</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ Thông báo · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Thay vì chỉ là những giao dịch thanh toán thông thường, giờ đây với Green Hub - Góp hóa đơn trồng rừng trên MoMo, mỗi hóa đơn bạn chi trả đều mang lại giá trị đó</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" s="2" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T23" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>3.36</v>
       </c>
       <c r="V23" s="2" t="inlineStr"/>
     </row>
@@ -2270,17 +2282,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353214/kuaishou-stock-surges-reports-kling-ai-unit-spin?utm_source=rss_feed</t>
+          <t>https://blog.whatsapp.com/new-feature-roundup-free-up-space-multiple-accounts-cross-platform-transfer-and-more</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2289,7 +2301,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -2298,22 +2310,18 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
@@ -2321,24 +2329,24 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou Technology’s shares jumped as much as 10 per cent on Tuesday morning after reports that the Chinese short-video platform was raising new funding for its Kling AI unit at a valuation of US$20 billion. Kuaishou – often seen as a rival to ByteDance-owned Douyin in China – plans to spin off its</t>
+          <t xml:space="preserve">Over time, our chats become a record of the moments that matter: conversations with family, laughs with friends, the photos and videos we couldn't stop sharing. To help you make the most of all of it, we're rolling out new ways to make WhatsApp even easier to use — whether you're staying organized, </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" s="2" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T24" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U24" s="2" t="n">
-        <v>3.36</v>
       </c>
       <c r="V24" s="2" t="inlineStr"/>
     </row>
@@ -2348,17 +2356,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/25329</t>
+          <t>https://blog.whatsapp.com/whatsapps-latest-privacy-protection-strict-account-settings</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2367,7 +2375,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -2376,14 +2384,10 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2391,7 +2395,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
@@ -2399,20 +2403,24 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>At WhatsApp, we think you should be able to have a private conversation online, just like you would in-person. We will always defend that right to privacy for everyone, starting with default end-to-end encryption. But we also know that a few of our users – like journalists or public-facing figures –</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V25" s="2" t="inlineStr"/>
     </row>
@@ -2422,17 +2430,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27540</t>
+          <t>https://blog.whatsapp.com/level-up-your-whatsapp-group-chats-with-new-member-tags-text-stickers-and-more</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2450,14 +2458,10 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2465,7 +2469,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
@@ -2473,24 +2477,24 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>It’s a new year and a great time for some upgrades to your group chats. Group chats on WhatsApp make it easier to stay connected with the people in your life no matter what device they own – whether it’s sharing New Year’s resolutions, preparing for that special celebration you have coming up, or pl</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V26" s="2" t="inlineStr"/>
     </row>
@@ -2500,17 +2504,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/17468</t>
+          <t>https://blog.whatsapp.com/reintroducing-about-an-improved-way-to-share-what-youre-up-to</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2519,7 +2523,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -2528,14 +2532,10 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
@@ -2551,20 +2551,24 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>For those of you that have used WhatsApp from the very start, you’ll remember About was our first feature. Even before we brought the world private and secure messaging, we made it simple for you to quickly share what’s up in your life. Today we're reintroducing and improving About, making it more v</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="n">
         <v>3</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V27" s="2" t="inlineStr"/>
     </row>
@@ -2574,17 +2578,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353797/ai-agents-face-trust-issues-high-risk-industrial-sectors-experts?utm_source=rss_feed</t>
+          <t>https://zalopay.vn/tin-tuc/tin-tuc-su-kien</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>zalopay_news</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2593,7 +2597,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -2602,22 +2606,18 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
+          <t>Tin tức</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
@@ -2625,24 +2625,24 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>China’s industrial sectors are racing to integrate artificial intelligence to boost efficiency, bolstered by state support, but experts warn that critical vertical markets – such as healthcare and aerospace – may be too “high risk” for the shift towards autonomous agents. Hailed as the driver of a “</t>
+          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" s="2" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" s="2" t="n">
-        <v>3.24</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
     </row>
@@ -2652,17 +2652,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353764/trump-xi-weigh-ai-guardrails-nvidia-chip-exports-hang-balance?utm_source=rss_feed</t>
+          <t>https://zalopay.vn/khuyen-mai/dac-biet</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -2680,22 +2680,18 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
@@ -2703,24 +2699,24 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>US President Donald Trump and Chinese officials discussed artificial intelligence “guardrails” and Nvidia’s H200 chips during his just-ended state visit to Beijing. Speaking to reporters on Air Force One during his return flight, Trump said the two sides “talked about possibly working together for g</t>
+          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" s="2" t="n">
         <v>3.4</v>
-      </c>
-      <c r="T29" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" s="2" t="n">
-        <v>3.24</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
     </row>
@@ -2730,12 +2726,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353747/chinas-tech-companies-are-looking-rewrite-e-commerce-playbook-ai-agents?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353594/chinese-foundries-smic-hua-hong-forecast-second-quarter-growth-amid-ai-boom?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2758,12 +2754,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2781,12 +2777,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>For years, online shopping in China has followed a rigid, tedious ritual: typing precise keywords, squinting at endless rows of listings, and falling into a rabbit hole of product comparisons. But for a man surnamed Liu, a 30-something finance professional based in Hong Kong, that experience has rec</t>
+          <t>China’s leading semiconductor foundries, Semiconductor Manufacturing International Corporation (SMIC) and Hua Hong Semiconductor, expect their second-quarter sales to rise amid a dynamic global market defined by surging artificial intelligence demand and a memory supply crunch, while Hua Hong said i</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -2795,10 +2791,10 @@
         <v>3.4</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
@@ -2808,12 +2804,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353715/panic-over-capacity-crunch-mature-node-chips-drives-orders-chinese-foundries?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353451/alibaba-ai-revenue-logs-triple-digit-growth-11th-quarter-amid-strategic-reshuffle?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2836,12 +2832,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2859,12 +2855,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>The global AI boom is driving orders back to Chinese foundries as overseas rivals shift production towards high-margin AI chips and high-bandwidth memory, creating a shortage in mature-node semiconductors, according to the head of China’s top contract chipmaker. “AI demand has directly pushed power-</t>
+          <t>Alibaba Group Holding expects its annualised recurring revenue from AI models and applications to hit 30 billion yuan (US$4.42 billion) by the year’s end, as the company ramps up its AI commitment. AI products are projected to generate more than 50 per cent of Alibaba’s cloud-computing revenue withi</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -2873,10 +2869,10 @@
         <v>3.4</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
     </row>
@@ -2886,12 +2882,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353310/how-bytedance-plans-turn-openclaw-craze-profitable-ai-business?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353214/kuaishou-stock-surges-reports-kling-ai-unit-spin?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2914,12 +2910,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2937,12 +2933,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>ByteDance’s Volcano Engine, the cloud unit that released an OpenClaw-based cloud agent tool ArkClaw, is betting that the next phase of artificial intelligence will hinge on cheaper tokens, higher inference efficiency and longer context windows. “Agent-related token consumption still accounts for a s</t>
+          <t>Kuaishou Technology’s shares jumped as much as 10 per cent on Tuesday morning after reports that the Chinese short-video platform was raising new funding for its Kling AI unit at a valuation of US$20 billion. Kuaishou – often seen as a rival to ByteDance-owned Douyin in China – plans to spin off its</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -2951,10 +2947,10 @@
         <v>3.4</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
     </row>
@@ -2964,17 +2960,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353188/chinese-chip-pioneer-calls-focus-pragmatic-breakthroughs-over-chasing-2nm-hype?utm_source=rss_feed</t>
+          <t>https://banhang.shopee.vn/edu/article/25329</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2992,22 +2988,22 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
@@ -3015,24 +3011,20 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>The founder of China’s largest contract chipmaker has urged the country’s semiconductor industry to pursue breakthroughs in niche markets such as mature chips, citing their importance for “supply chain security”. Richard Chang Rugin, 78, former CEO of Semiconductor Manufacturing International Corp (</t>
-        </is>
-      </c>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="V33" s="2" t="inlineStr"/>
     </row>
@@ -3042,17 +3034,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353132/alibaba-taps-chinas-chat-buy-trend-qwen-ai-and-taobao-integration?utm_source=rss_feed</t>
+          <t>https://banhang.shopee.vn/edu/article/27540</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3061,7 +3053,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -3070,22 +3062,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
@@ -3093,24 +3085,24 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Alibaba Group Holding is integrating its flagship AI assistant Qwen into its biggest e-commerce platforms, betting that the future of online shopping lies in fluid conversations rather than rigid search terms. Using the Qwen app, shoppers are able to find, compare and purchase products from Taobao a</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="V34" s="2" t="inlineStr"/>
     </row>
@@ -3120,17 +3112,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/google-adds-gemini-powered-dictation-to-gboard-which-could-be-bad-news-for-dictation-startups/</t>
+          <t>https://banhang.shopee.vn/edu/article/17468</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3148,7 +3140,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3158,12 +3150,12 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
@@ -3171,24 +3163,20 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Google's transcription feature will initially launch with Samsung Galaxy and Google Pixel phones.</t>
-        </is>
-      </c>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
     </row>
@@ -3198,17 +3186,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/altman-bi-to-noi-doi-musk-bi-che-mat-tri-nho-chon-loc-5074265.html</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353797/ai-agents-face-trust-issues-high-risk-industrial-sectors-experts?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3226,12 +3214,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3241,7 +3229,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
@@ -3249,21 +3237,21 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Luật sư của Elon Musk công kích uy tín của Sam Altman, trong khi phía OpenAI đặt nghi vấn về các hành động của Musk.</t>
+          <t>China’s industrial sectors are racing to integrate artificial intelligence to boost efficiency, bolstered by state support, but experts warn that critical vertical markets – such as healthcare and aerospace – may be too “high risk” for the shift towards autonomous agents. Hailed as the driver of a “</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U36" s="2" t="n">
         <v>3.24</v>
@@ -3276,17 +3264,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/loat-thong-tin-duoc-ong-chu-chatgpt-he-lo-trong-phien-toa-5073321.html</t>
+          <t>https://www.scmp.com/tech/article/3353764/trump-xi-weigh-ai-guardrails-nvidia-chip-exports-hang-balance?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -3304,12 +3292,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3319,7 +3307,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
@@ -3327,21 +3315,21 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Trong phiên tòa đang diễn ra giữa Elon Musk và OpenAI, Sam Altman nhận xét Musk "đáng sợ", nhưng bị luật sư chất vấn về tính trung thực.</t>
+          <t>US President Donald Trump and Chinese officials discussed artificial intelligence “guardrails” and Nvidia’s H200 chips during his just-ended state visit to Beijing. Speaking to reporters on Air Force One during his return flight, Trump said the two sides “talked about possibly working together for g</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U37" s="2" t="n">
         <v>3.24</v>
@@ -3354,17 +3342,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/pershing-square-has-taken-new-stake-in-microsoft-ackman-says</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353747/chinas-tech-companies-are-looking-rewrite-e-commerce-playbook-ai-agents?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3382,7 +3370,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3397,7 +3385,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
@@ -3405,24 +3393,24 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Bill Ackman’s Pershing Square has built a $2.1 billion stake in Microsoft Corp., taking advantage of a decline in the company’s share price to invest in a business that he said is stronger and more resilient than investors think.</t>
+          <t>For years, online shopping in China has followed a rigid, tedious ritual: typing precise keywords, squinting at endless rows of listings, and falling into a rabbit hole of product comparisons. But for a man surnamed Liu, a 30-something finance professional based in Hong Kong, that experience has rec</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V38" s="2" t="inlineStr"/>
     </row>
@@ -3432,17 +3420,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/meta-at-the-cannes-film-festival-2026/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353715/panic-over-capacity-crunch-mature-node-chips-drives-orders-chinese-foundries?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -3460,12 +3448,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3475,7 +3463,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
@@ -3483,24 +3471,24 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Meta is proud to be an Official Partner of the Festival de Cannes in a new multi-year strategic partnership. It’s a natural fit: for decades, Cannes has defined how we see the world through the frame—and today, our platforms are where that view is shared with the world. With more than 3.5 billion pe</t>
+          <t>The global AI boom is driving orders back to Chinese foundries as overseas rivals shift production towards high-margin AI chips and high-bandwidth memory, creating a shortage in mature-node semiconductors, according to the head of China’s top contract chipmaker. “AI demand has directly pushed power-</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V39" s="2" t="inlineStr"/>
     </row>
@@ -3510,12 +3498,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353576/ex-meta-chinese-star-researcher-joins-race-self-improving-ai-us46b-start?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353310/how-bytedance-plans-turn-openclaw-craze-profitable-ai-business?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3538,12 +3526,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3553,7 +3541,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
@@ -3561,24 +3549,24 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>A star Chinese researcher laid off by Facebook owner Meta Platforms has co-founded a start-up focused on self-improving artificial intelligence systems, joining a wave of US and Chinese firms developing models capable of autonomously refining their own code and reasoning. Tian Yuandong, former resea</t>
+          <t>ByteDance’s Volcano Engine, the cloud unit that released an OpenClaw-based cloud agent tool ArkClaw, is betting that the next phase of artificial intelligence will hinge on cheaper tokens, higher inference efficiency and longer context windows. “Agent-related token consumption still accounts for a s</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr"/>
       <c r="S40" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V40" s="2" t="inlineStr"/>
     </row>
@@ -3588,12 +3576,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353291/jdcom-swings-back-profitability-first-quarter-though-profits-tumble-53?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353188/chinese-chip-pioneer-calls-focus-pragmatic-breakthroughs-over-chasing-2nm-hype?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3616,12 +3604,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -3631,7 +3619,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
@@ -3639,24 +3627,24 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chinese online shopping giant JD.com reported a 53.2 per cent year-on-year decline in first-quarter profit to 5.1 billion yuan (US$750.2 million) due to protracted competition on the e-commerce and food delivery fronts. The company was able to swing back to profitability after posting a loss in the </t>
+          <t>The founder of China’s largest contract chipmaker has urged the country’s semiconductor industry to pursue breakthroughs in niche markets such as mature chips, citing their importance for “supply chain security”. Richard Chang Rugin, 78, former CEO of Semiconductor Manufacturing International Corp (</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
       <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V41" s="2" t="inlineStr"/>
     </row>
@@ -3666,17 +3654,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/cerebras-raises-5-5b-kicking-off-2026s-ipo-season-with-a-bang/</t>
+          <t>https://www.scmp.com/tech/article/3353132/alibaba-taps-chinas-chat-buy-trend-qwen-ai-and-taobao-integration?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3694,12 +3682,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3709,7 +3697,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -3717,24 +3705,24 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>A year ago, it looked like this day would never happen for Cerebras.</t>
+          <t>Alibaba Group Holding is integrating its flagship AI assistant Qwen into its biggest e-commerce platforms, betting that the future of online shopping lies in fluid conversations rather than rigid search terms. Using the Qwen app, shoppers are able to find, compare and purchase products from Taobao a</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V42" s="2" t="inlineStr"/>
     </row>
@@ -3744,17 +3732,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/startup-my-duoc-dinh-gia-gan-100-ty-usd-nho-chip-ai-bang-cai-dia-5074683.html</t>
+          <t>https://techcrunch.com/2026/05/12/google-adds-gemini-powered-dictation-to-gboard-which-could-be-bad-news-for-dictation-startups/</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3772,12 +3760,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3795,24 +3783,24 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Cerebras, doanh nghiệp được đánh giá là đối thủ của Nvidia, thu hút sự chú ý với mẫu chip AI có kích thước bằng chiếc đĩa.</t>
+          <t>Google's transcription feature will initially launch with Samsung Galaxy and Google Pixel phones.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr"/>
       <c r="S43" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
     </row>
@@ -3822,12 +3810,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/giam-doc-anthropic-ai-viet-90-ma-cua-cong-ty-5073942.html</t>
+          <t>https://vnexpress.net/altman-bi-to-noi-doi-musk-bi-che-mat-tri-nho-chon-loc-5074265.html</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3850,12 +3838,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3873,24 +3861,24 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Krishna Rao, Giám đốc tài chính của Anthropic, cho biết AI Claude đang thay đổi cách nhân viên văn phòng làm việc mỗi ngày.</t>
+          <t>Luật sư của Elon Musk công kích uy tín của Sam Altman, trong khi phía OpenAI đặt nghi vấn về các hành động của Musk.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V44" s="2" t="inlineStr"/>
     </row>
@@ -3900,12 +3888,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sony-a7-r-vi-may-anh-cam-bien-xep-chong-gia-114-trieu-dong-5074084.html</t>
+          <t>https://vnexpress.net/loat-thong-tin-duoc-ong-chu-chatgpt-he-lo-trong-phien-toa-5073321.html</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3928,12 +3916,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3951,24 +3939,24 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI trang bị cảm biến xếp chồng (full stack) 67 megapixel, chip AI thế hệ mới, khả năng quay video 8K và giá 114 triệu đồng.</t>
+          <t>Trong phiên tòa đang diễn ra giữa Elon Musk và OpenAI, Sam Altman nhận xét Musk "đáng sợ", nhưng bị luật sư chất vấn về tính trung thực.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
     </row>
@@ -3978,17 +3966,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/pershing-square-has-taken-new-stake-in-microsoft-ackman-says</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4006,12 +3994,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4029,12 +4017,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Tài liệu tòa án cho thấy Sam Altman có cổ phần hơn hai tỷ USD tại hàng loạt công ty đang bắt tay với OpenAI.</t>
+          <t>Bill Ackman’s Pershing Square has built a $2.1 billion stake in Microsoft Corp., taking advantage of a decline in the company’s share price to invest in a business that he said is stronger and more resilient than investors think.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4056,17 +4044,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
+          <t>https://about.fb.com/news/2026/05/meta-at-the-cannes-film-festival-2026/</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4084,12 +4072,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4107,12 +4095,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
+          <t>Meta is proud to be an Official Partner of the Festival de Cannes in a new multi-year strategic partnership. It’s a natural fit: for decades, Cannes has defined how we see the world through the frame—and today, our platforms are where that view is shared with the world. With more than 3.5 billion pe</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -4134,17 +4122,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353576/ex-meta-chinese-star-researcher-joins-race-self-improving-ai-us46b-start?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4162,12 +4150,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4185,12 +4173,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
+          <t>A star Chinese researcher laid off by Facebook owner Meta Platforms has co-founded a start-up focused on self-improving artificial intelligence systems, joining a wave of US and Chinese firms developing models capable of autonomously refining their own code and reasoning. Tian Yuandong, former resea</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -4212,17 +4200,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353291/jdcom-swings-back-profitability-first-quarter-though-profits-tumble-53?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4240,12 +4228,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -4263,12 +4251,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
+          <t xml:space="preserve">Chinese online shopping giant JD.com reported a 53.2 per cent year-on-year decline in first-quarter profit to 5.1 billion yuan (US$750.2 million) due to protracted competition on the e-commerce and food delivery fronts. The company was able to swing back to profitability after posting a loss in the </t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -4290,17 +4278,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
+          <t>https://techcrunch.com/2026/05/14/cerebras-raises-5-5b-kicking-off-2026s-ipo-season-with-a-bang/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>grab_inside</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4309,7 +4297,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -4318,18 +4306,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
@@ -4337,24 +4329,24 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
+          <t>A year ago, it looked like this day would never happen for Cerebras.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V50" s="2" t="inlineStr"/>
     </row>
@@ -4364,17 +4356,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
+          <t>https://vnexpress.net/startup-my-duoc-dinh-gia-gan-100-ty-usd-nho-chip-ai-bang-cai-dia-5074683.html</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>grab_inside</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4383,7 +4375,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -4392,18 +4384,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr"/>
@@ -4411,24 +4407,24 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
+          <t>Cerebras, doanh nghiệp được đánh giá là đối thủ của Nvidia, thu hút sự chú ý với mẫu chip AI có kích thước bằng chiếc đĩa.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V51" s="2" t="inlineStr"/>
     </row>
@@ -4438,17 +4434,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
+          <t>https://vnexpress.net/giam-doc-anthropic-ai-viet-90-ma-cua-cong-ty-5073942.html</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>grab_inside</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -4457,7 +4453,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -4466,18 +4462,22 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
@@ -4485,24 +4485,24 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
+          <t>Krishna Rao, Giám đốc tài chính của Anthropic, cho biết AI Claude đang thay đổi cách nhân viên văn phòng làm việc mỗi ngày.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V52" s="2" t="inlineStr"/>
     </row>
@@ -4512,17 +4512,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
+          <t>https://vnexpress.net/sony-a7-r-vi-may-anh-cam-bien-xep-chong-gia-114-trieu-dong-5074084.html</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
+          <t>Sony A7 R VI trang bị cảm biến xếp chồng (full stack) 67 megapixel, chip AI thế hệ mới, khả năng quay video 8K và giá 114 triệu đồng.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         <v>2.6</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V53" s="2" t="inlineStr"/>
     </row>
@@ -4590,17 +4590,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
+          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
+          <t>Tài liệu tòa án cho thấy Sam Altman có cổ phần hơn hai tỷ USD tại hàng loạt công ty đang bắt tay với OpenAI.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -4655,10 +4655,10 @@
         <v>2.6</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V54" s="2" t="inlineStr"/>
     </row>
@@ -4668,17 +4668,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
+          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
+          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -4733,10 +4733,10 @@
         <v>2.6</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V55" s="2" t="inlineStr"/>
     </row>
@@ -4746,17 +4746,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/running-codex-safely/</t>
+          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
+          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
         <v>2.6</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U56" s="2" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V56" s="2" t="inlineStr"/>
     </row>
@@ -4824,17 +4824,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/newsletters/2026-05-17/youtube-and-netflix-are-starting-to-sound-a-lot-like-normal-tv</t>
+          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>YouTube is pitching advertisers on a new slate of shows -- just like a TV network.</t>
+          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
@@ -4889,10 +4889,10 @@
         <v>2.6</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
     </row>
@@ -4902,17 +4902,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/korea-bond-yields-may-extend-gains-on-chips-boom-analysts-say</t>
+          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>grab_inside</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -4930,22 +4930,18 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
+          <t>AI in action</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr"/>
@@ -4953,24 +4949,24 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>South Korea’s bonds are set to extend this year’s rout as a semiconductor boom supercharges the nation’s economic growth and adds to inflationary pressures, analysts say.</t>
+          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr"/>
       <c r="R58" s="2" t="inlineStr"/>
       <c r="S58" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V58" s="2" t="inlineStr"/>
     </row>
@@ -4980,17 +4976,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/ai-poised-to-tilt-job-market-leverage-toward-older-workers</t>
+          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>grab_inside</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4999,7 +4995,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -5008,22 +5004,18 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
+          <t>Product innovation</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr"/>
@@ -5031,24 +5023,24 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>When it comes to job cuts, older workers are often disproportionately affected. But a new survey of chief executive officers suggests this won’t be a given as companies adopt artificial intelligence.</t>
+          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U59" s="2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V59" s="2" t="inlineStr"/>
     </row>
@@ -5058,17 +5050,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/-the-oppenheimer-of-the-ai-era-video</t>
+          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>grab_inside</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5077,7 +5069,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -5086,22 +5078,18 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
+          <t>Tracing our impact</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr"/>
@@ -5109,24 +5097,24 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>‘The Oppenheimer’ of the AI Era</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>What drives the tech titans behind the AI arms race? For some, it's the thrill of scientific discovery; for others, it's the pursuit of profit.  Through the story of DeepMind co-founder Demis Hassabis and other AI leaders, author Sebastian Mallaby explores how motivations ranging from scientific cur</t>
+          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T60" s="2" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
     </row>
@@ -5136,17 +5124,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/elon-musk-says-he-isn-t-selling-his-spacex-shares-as-ipo-looms</t>
+          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -5164,12 +5152,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -5187,12 +5175,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk said he is not selling any SpaceX shares, with the company reported to be preparing to file publicly for its long-awaited IPO as soon as next week.</t>
+          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -5214,17 +5202,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/how-agentic-commerce-will-reshape-the-internet-video</t>
+          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5242,12 +5230,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -5265,12 +5253,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">The internet is made for shopping. For years, the main inputs for e-commerce transactions involved targeted ads, algorithmic recommendations, SEO, and lots of mindless scrolling. But agentic commerce might represent a sea change for e-commerce: With the rise of AI agents doing shopping on behalf of </t>
+          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -5292,17 +5280,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/snap-youtube-settle-school-social-media-suit-ahead-of-trial</t>
+          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -5320,12 +5308,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5343,12 +5331,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Snap Inc., Google’s YouTube and ByteDance Ltd.’s TikTok reached agreements to settle the first lawsuit headed to trial over claims that addiction to top social media platforms has disrupted learning and pushed public schools to spend massive sums fighting a mental health crisis, according to court f</t>
+          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -5370,17 +5358,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
+          <t>https://openai.com/index/running-codex-safely/</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5398,12 +5386,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5421,12 +5409,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
+          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -5448,17 +5436,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
+          <t>https://www.bloomberg.com/news/newsletters/2026-05-17/youtube-and-netflix-are-starting-to-sound-a-lot-like-normal-tv</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -5476,12 +5464,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -5499,12 +5487,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>YouTube and Netflix Are Starting to Sound a Lot Like Normal TV</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chatting with AI has quickly become a critical part of how people get information and ask important questions. These questions can be deeply sensitive or personal, like health issues, loan details, or career advice. Today, we’re launching Incognito Chat with Meta AI on WhatsApp and the Meta AI app, </t>
+          <t>YouTube is pitching advertisers on a new slate of shows -- just like a TV network.</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr"/>
@@ -5526,17 +5514,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/korea-bond-yields-may-extend-gains-on-chips-boom-analysts-say</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -5554,12 +5542,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -5577,12 +5565,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>South Korean Bond Yields Set to Rise on Chips Boom, Analysts Say</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
+          <t>South Korea’s bonds are set to extend this year’s rout as a semiconductor boom supercharges the nation’s economic growth and adds to inflationary pressures, analysts say.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr"/>
@@ -5604,17 +5592,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/ai-poised-to-tilt-job-market-leverage-toward-older-workers</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -5632,12 +5620,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -5655,12 +5643,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>AI Poised to Tilt Job Market Leverage Toward Older Workers</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
+          <t>When it comes to job cuts, older workers are often disproportionately affected. But a new survey of chief executive officers suggests this won’t be a given as companies adopt artificial intelligence.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr"/>
@@ -5682,17 +5670,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/-the-oppenheimer-of-the-ai-era-video</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -5710,12 +5698,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -5733,12 +5721,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>‘The Oppenheimer’ of the AI Era</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
+          <t>What drives the tech titans behind the AI arms race? For some, it's the thrill of scientific discovery; for others, it's the pursuit of profit.  Through the story of DeepMind co-founder Demis Hassabis and other AI leaders, author Sebastian Mallaby explores how motivations ranging from scientific cur</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr"/>
@@ -5760,17 +5748,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/elon-musk-says-he-isn-t-selling-his-spacex-shares-as-ipo-looms</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5788,12 +5776,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -5811,12 +5799,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Elon Musk Says He Isn’t Selling His SpaceX Shares as IPO Looms</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
+          <t>Elon Musk said he is not selling any SpaceX shares, with the company reported to be preparing to file publicly for its long-awaited IPO as soon as next week.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr"/>
@@ -5838,17 +5826,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/how-agentic-commerce-will-reshape-the-internet-video</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -5866,12 +5854,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -5889,12 +5877,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Stripe's John Collison on How Agentic Commerce Will Reshape the Internet | Odd Lots</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
+          <t xml:space="preserve">The internet is made for shopping. For years, the main inputs for e-commerce transactions involved targeted ads, algorithmic recommendations, SEO, and lots of mindless scrolling. But agentic commerce might represent a sea change for e-commerce: With the rise of AI agents doing shopping on behalf of </t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -5916,17 +5904,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/snap-youtube-settle-school-social-media-suit-ahead-of-trial</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5944,12 +5932,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -5967,12 +5955,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
+          <t>Snap Inc., Google’s YouTube and ByteDance Ltd.’s TikTok reached agreements to settle the first lawsuit headed to trial over claims that addiction to top social media platforms has disrupted learning and pushed public schools to spend massive sums fighting a mental health crisis, according to court f</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -5994,17 +5982,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
+          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6022,12 +6010,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6045,12 +6033,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
+          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -6072,17 +6060,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
+          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -6100,12 +6088,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -6123,12 +6111,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
+          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -6150,17 +6138,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
+          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6178,12 +6166,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6201,12 +6189,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
+          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -6228,17 +6216,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
+          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6256,7 +6244,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -6279,12 +6267,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
+          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -6306,17 +6294,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -6334,12 +6322,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -6357,12 +6345,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
+          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -6384,17 +6372,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6412,12 +6400,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -6435,12 +6423,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
+          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -6462,12 +6450,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
+          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6490,12 +6478,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -6513,12 +6501,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
+          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -6540,12 +6528,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
+          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6568,12 +6556,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -6591,12 +6579,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
+          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -6618,12 +6606,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
+          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6646,12 +6634,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -6669,12 +6657,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
+          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -6696,12 +6684,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
+          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6724,12 +6712,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -6747,12 +6735,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
+          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -6774,17 +6762,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/why-trust-is-a-big-question-at-the-elon-musk-openai-trial/</t>
+          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -6802,12 +6790,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6825,12 +6813,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>A big theme in the trial’s final days was whether OpenAI CEO Sam Altman is trustworthy.</t>
+          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -6852,17 +6840,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
+          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -6880,12 +6868,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -6903,12 +6891,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
+          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -6930,17 +6918,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
+          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -6958,12 +6946,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -6981,12 +6969,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
+          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -7008,17 +6996,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
+          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -7036,12 +7024,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -7059,12 +7047,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
+          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -7086,17 +7074,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
+          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -7114,12 +7102,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -7137,12 +7125,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
+          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -7164,17 +7152,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
+          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -7192,12 +7180,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -7215,12 +7203,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
+          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -7242,17 +7230,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
+          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7270,12 +7258,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7293,12 +7281,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
+          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -7320,17 +7308,17 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phien-toa-ty-phu-dau-ty-phu-giua-musk-va-altman-5074631.html</t>
+          <t>https://techcrunch.com/2026/05/17/why-trust-is-a-big-question-at-the-elon-musk-openai-trial/</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -7348,7 +7336,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -7371,12 +7359,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>Sau ba tuần tranh tụng, bên cạnh những thông tin chưa từng xuất hiện, phiên tòa giữa Elon Musk với Sam Altman và OpenAI còn phô trương sự giàu có.</t>
+          <t>A big theme in the trial’s final days was whether OpenAI CEO Sam Altman is trustworthy.</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
@@ -7398,17 +7386,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ai-mythos-cua-anthropic-co-the-be-khoa-may-mac-5074524.html</t>
+          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -7426,7 +7414,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -7449,12 +7437,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>Các nhà nghiên cứu bảo mật cảnh báo Calude Mythos của Anthropic đã có thể vượt qua hệ thống bảo mật của macOS theo cách chưa từng đạt được trước đây.</t>
+          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -7476,17 +7464,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/loat-tinh-nang-moi-tren-android-17-5073388.html</t>
+          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -7504,7 +7492,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -7527,12 +7515,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>Google giới thiệu hệ điều hành Android 17 tập trung vào Gemini và hướng tới chấm dứt tình trạng cuộn màn hình tiêu cực.</t>
+          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -7554,17 +7542,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nhung-dan-loa-tien-ty-tai-plase-show-2026-5074425.html</t>
+          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -7582,7 +7570,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -7605,12 +7593,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Triển lãm thiết bị biểu diễn chuyên nghiệp Plase Show 2026 tăng quy mô trở lại, nổi bật với 14 dàn loa treo (line-array) giữa trời, gấp đôi năm ngoái.</t>
+          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -7632,17 +7620,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cac-startup-viet-tim-duong-sang-thi-truong-nhat-ban-5074085.html</t>
+          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -7660,7 +7648,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -7683,12 +7671,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>Bên cạnh gọi vốn trong nước, nhiều startup Việt đang tìm cơ hội hợp tác, thử nghiệm sản phẩm và mở rộng sang thị trường Nhật Bản.</t>
+          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -7710,17 +7698,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cac-chuyen-gia-quoc-te-ban-ve-tuong-lai-ai-tai-tp-hcm-5073633.html</t>
+          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -7738,7 +7726,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -7761,12 +7749,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>Sự kiện GStar 2026, diễn ra cuối tháng 5 tại TP HCM, quy tụ nhiều chuyên gia từ Google, Qualcomm... cùng bàn về hướng phát triển định hình tương lai AI.</t>
+          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -7788,17 +7776,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sieu-hacker-ai-khien-loat-ngan-hang-my-voi-sua-loi-bao-mat-5073574.html</t>
+          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7816,7 +7804,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -7839,12 +7827,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>Các ngân hàng Mỹ đang gấp rút khắc phục những điểm yếu hệ thống IT do Mythos, công cụ AI được mệnh danh "siêu hacker" của Anthropic, phát hiện.</t>
+          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
@@ -7866,12 +7854,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/grok-cua-elon-musk-mat-dan-vi-the-trong-cuoc-dua-ai-5073523.html</t>
+          <t>https://vnexpress.net/phien-toa-ty-phu-dau-ty-phu-giua-musk-va-altman-5074631.html</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -7894,12 +7882,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7917,12 +7905,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>AI Grok của xAI, công ty do Elon Musk thành lập và điều hành, bị đánh giá tụt hậu khá xa so với các đối thủ OpenAI, Anthropic hay Google.</t>
+          <t>Sau ba tuần tranh tụng, bên cạnh những thông tin chưa từng xuất hiện, phiên tòa giữa Elon Musk với Sam Altman và OpenAI còn phô trương sự giàu có.</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
@@ -7944,17 +7932,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chu-tich-fpt-telecom-lam-sep-gtel-5074476.html</t>
+          <t>https://vnexpress.net/ai-mythos-cua-anthropic-co-the-be-khoa-may-mac-5074524.html</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -7972,12 +7960,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7995,12 +7983,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom vừa được bổ nhiệm giữ chức Phó tổng giám đốc Tổng công ty Công nghệ - Viễn thông Toàn cầu (GTEL) thuộc Bộ Công an.</t>
+          <t>Các nhà nghiên cứu bảo mật cảnh báo Calude Mythos của Anthropic đã có thể vượt qua hệ thống bảo mật của macOS theo cách chưa từng đạt được trước đây.</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
@@ -8022,17 +8010,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
+          <t>https://vnexpress.net/loat-tinh-nang-moi-tren-android-17-5073388.html</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -8050,7 +8038,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -8073,12 +8061,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
+          <t>Google giới thiệu hệ điều hành Android 17 tập trung vào Gemini và hướng tới chấm dứt tình trạng cuộn màn hình tiêu cực.</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -8100,17 +8088,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+          <t>https://vnexpress.net/nhung-dan-loa-tien-ty-tai-plase-show-2026-5074425.html</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -8128,12 +8116,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -8151,12 +8139,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+          <t>Triển lãm thiết bị biểu diễn chuyên nghiệp Plase Show 2026 tăng quy mô trở lại, nổi bật với 14 dàn loa treo (line-array) giữa trời, gấp đôi năm ngoái.</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
@@ -8178,17 +8166,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/apples-siri-revamp-could-include-auto-deleting-chats/</t>
+          <t>https://vnexpress.net/cac-startup-viet-tim-duong-sang-thi-truong-nhat-ban-5074085.html</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -8206,12 +8194,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -8229,12 +8217,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Privacy will be a major theme when Apple unveils a new version of Siri.</t>
+          <t>Bên cạnh gọi vốn trong nước, nhiều startup Việt đang tìm cơ hội hợp tác, thử nghiệm sản phẩm và mở rộng sang thị trường Nhật Bản.</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -8243,10 +8231,10 @@
         <v>2.6</v>
       </c>
       <c r="T100" s="2" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U100" s="2" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="V100" s="2" t="inlineStr"/>
     </row>
@@ -8256,17 +8244,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
+          <t>https://vnexpress.net/cac-chuyen-gia-quoc-te-ban-ve-tuong-lai-ai-tai-tp-hcm-5073633.html</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -8284,7 +8272,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -8307,12 +8295,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
+          <t>Sự kiện GStar 2026, diễn ra cuối tháng 5 tại TP HCM, quy tụ nhiều chuyên gia từ Google, Qualcomm... cùng bàn về hướng phát triển định hình tương lai AI.</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
@@ -8321,10 +8309,10 @@
         <v>2.6</v>
       </c>
       <c r="T101" s="2" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U101" s="2" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="V101" s="2" t="inlineStr"/>
     </row>
@@ -8334,22 +8322,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
+          <t>https://vnexpress.net/sieu-hacker-ai-khien-loat-ngan-hang-my-voi-sua-loi-bao-mat-5073574.html</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>2 - Minor signal</t>
+          <t>3 - Market signal</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
@@ -8362,12 +8350,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -8377,7 +8365,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr"/>
@@ -8385,26 +8373,572 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
+          <t>Các ngân hàng Mỹ đang gấp rút khắc phục những điểm yếu hệ thống IT do Mythos, công cụ AI được mệnh danh "siêu hacker" của Anthropic, phát hiện.</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr"/>
       <c r="S102" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/grok-cua-elon-musk-mat-dan-vi-the-trong-cuoc-dua-ai-5073523.html</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_khcn</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>AI Grok của xAI, công ty do Elon Musk thành lập và điều hành, bị đánh giá tụt hậu khá xa so với các đối thủ OpenAI, Anthropic hay Google.</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U103" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chu-tich-fpt-telecom-lam-sep-gtel-5074476.html</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_kinhdoanh</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Chủ tịch FPT Telecom vừa được bổ nhiệm giữ chức Phó tổng giám đốc Tổng công ty Công nghệ - Viễn thông Toàn cầu (GTEL) thuộc Bộ Công an.</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U104" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_kinhdoanh</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U105" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>vnexpress_kinhdoanh</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/05/17/apples-siri-revamp-could-include-auto-deleting-chats/</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch_apps</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Privacy will be a major theme when Apple unveils a new version of Siri.</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says Codex is coming to your phone</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch_ai</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3 - Market signal</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says Codex is coming to your phone</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Quốc tế</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI says Codex is coming to your phone</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>scmp_tech</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2 - Minor signal</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Market Pulse</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Trung quốc</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T102" s="2" t="n">
+      <c r="T109" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="U102" s="2" t="n">
+      <c r="U109" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="V102" s="2" t="inlineStr"/>
+      <c r="V109" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
@@ -8418,7 +8952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10694,23 +11228,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
+          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>zalopay_news</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tin tức</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Introducing a Completely Private Way to Chat With AI</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_a7169d7312fe0349</t>
+          <t>DUPLICATE_OF_ecdd9a84cd8be1e9</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -10721,23 +11259,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
+          <t>https://blog.whatsapp.com/introducing-group-message-history-a-more-private-way-to-catch-up-in-group-chats</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Introducing Group Message History: A more private way to catch up in group chats</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>DUPLICATE_OF_ecdd9a84cd8be1e9</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -10748,23 +11286,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
+          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>zalopay_news</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>DUPLICATE_OF_a7169d7312fe0349</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -10775,7 +11313,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
+          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10802,7 +11340,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
+          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10829,7 +11367,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
+          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10856,7 +11394,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
+          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10883,7 +11421,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
+          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10910,27 +11448,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/rakuten-bank-shares-jump-as-mizuho-says-it-s-mulling-investment</t>
+          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rakuten Bank Shares Jump as Mizuho Considers Investment</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -10941,27 +11475,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/australia-plots-next-step-in-tokenized-bond-market-expansion</t>
+          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Australia Plots Next Step in Tokenized Bond Market Expansion</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -10972,7 +11502,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/e-commerce-giant-shein-buys-apparel-brand-everlane-reports-say</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/rakuten-bank-shares-jump-as-mizuho-says-it-s-mulling-investment</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10982,7 +11512,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>E-Commerce Giant Shein Buys Apparel Brand Everlane, Reports Say</t>
+          <t>Rakuten Bank Shares Jump as Mizuho Considers Investment</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11003,7 +11533,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/kioxia-shares-awash-in-buy-orders-after-ai-driven-profit-surge</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/australia-plots-next-step-in-tokenized-bond-market-expansion</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11013,7 +11543,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kioxia Shares Awash in Buy Orders After AI-Driven Profit Surge</t>
+          <t>Australia Plots Next Step in Tokenized Bond Market Expansion</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11034,7 +11564,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/e-commerce-giant-shein-buys-apparel-brand-everlane-reports-say</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -11044,12 +11574,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>China’s Energy Boom Could Give It the AI Edge</t>
+          <t>E-Commerce Giant Shein Buys Apparel Brand Everlane, Reports Say</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11065,7 +11595,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/kioxia-shares-awash-in-buy-orders-after-ai-driven-profit-surge</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -11075,12 +11605,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
+          <t>Kioxia Shares Awash in Buy Orders After AI-Driven Profit Surge</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11096,7 +11626,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -11106,12 +11636,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
+          <t>China’s Energy Boom Could Give It the AI Edge</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -11127,7 +11657,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11137,12 +11667,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
+          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11158,7 +11688,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11168,7 +11698,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
+          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11189,7 +11719,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11199,7 +11729,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
+          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11220,7 +11750,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/spacex-shareholders-approve-5-for-1-split-of-common-stock</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -11230,7 +11760,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SpaceX Holders Sign Off on 5-for-1 Stock Split Ahead of IPO</t>
+          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11251,22 +11781,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>luatvietnam_chinhsach</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
+          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -11282,22 +11812,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/spacex-shareholders-approve-5-for-1-split-of-common-stock</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
+          <t>SpaceX Holders Sign Off on 5-for-1 Stock Split Ahead of IPO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -11313,22 +11843,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
+          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>scmp_wechat</t>
+          <t>luatvietnam_chinhsach</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
+          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11344,22 +11874,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
+          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>China ramps up building a national computing power network as AI token demand surges</t>
+          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11375,22 +11905,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>scmp_wechat</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
+          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11406,7 +11936,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11416,12 +11946,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
+          <t>China ramps up building a national computing power network as AI token demand surges</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11437,7 +11967,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11447,12 +11977,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
+          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11468,7 +11998,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11478,12 +12008,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
+          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -11499,7 +12029,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11509,12 +12039,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
+          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -11530,7 +12060,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11540,17 +12070,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
+          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>T3_HEALTHCARE</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -11561,7 +12091,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11571,7 +12101,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
+          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -11592,7 +12122,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11602,17 +12132,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
+          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_HEALTHCARE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -11623,7 +12153,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11633,12 +12163,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
+          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11654,7 +12184,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11664,7 +12194,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>China ranks third in global index for AI competitiveness in life sciences</t>
+          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11685,22 +12215,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Osaurus brings both local and cloud AI models to your Mac</t>
+          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11716,22 +12246,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
+          <t>China ranks third in global index for AI competitiveness in life sciences</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11747,7 +12277,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
+          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11757,12 +12287,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
+          <t>Osaurus brings both local and cloud AI models to your Mac</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11778,7 +12308,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
+          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11788,12 +12318,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Indigo brings the open social web to one app</t>
+          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11809,22 +12339,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/if-youre-giving-a-commencement-speech-in-2026-maybe-dont-mention-ai/</t>
+          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>If you’re giving a commencement speech in 2026, maybe don’t mention AI</t>
+          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11840,22 +12370,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/techcrunch-mobility-the-ai-skills-arms-race-is-coming-for-automotive/</t>
+          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TechCrunch Mobility: The AI skills arms race is coming for automotive</t>
+          <t>Indigo brings the open social web to one app</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -11871,7 +12401,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
+          <t>https://techcrunch.com/2026/05/17/if-youre-giving-a-commencement-speech-in-2026-maybe-dont-mention-ai/</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11881,12 +12411,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>The haves and have nots of the AI gold rush</t>
+          <t>If you’re giving a commencement speech in 2026, maybe don’t mention AI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -11902,7 +12432,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
+          <t>https://techcrunch.com/2026/05/17/techcrunch-mobility-the-ai-skills-arms-race-is-coming-for-automotive/</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11912,12 +12442,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
+          <t>TechCrunch Mobility: The AI skills arms race is coming for automotive</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -11933,7 +12463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
+          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11943,12 +12473,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
+          <t>The haves and have nots of the AI gold rush</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -11964,7 +12494,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
+          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11974,12 +12504,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
+          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -11995,7 +12525,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
+          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12005,7 +12535,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>What happens when AI starts building itself?</t>
+          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -12026,7 +12556,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
+          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12036,7 +12566,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
+          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -12057,22 +12587,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
+          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
+          <t>What happens when AI starts building itself?</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -12088,22 +12618,22 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
+          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
+          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12119,7 +12649,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -12129,12 +12659,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
+          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12150,7 +12680,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
+          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12160,12 +12690,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
+          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12181,7 +12711,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
+          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12191,12 +12721,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
+          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12212,7 +12742,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
+          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12222,12 +12752,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
+          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12243,7 +12773,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
+          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12253,12 +12783,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
+          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12274,7 +12804,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
+          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12284,12 +12814,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
+          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12305,7 +12835,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
+          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12315,7 +12845,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
+          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -12336,22 +12866,22 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ban-dan-viet-nam-nen-di-theo-huong-toi-uu-nang-luong-5074612.html</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>'Bán dẫn Việt Nam nên đi theo hướng tối ưu năng lượng'</t>
+          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12367,22 +12897,22 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/iphone-gap-co-the-gap-loi-tieng-keu-ban-le-5075003.html</t>
+          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>iPhone gập 'có thể gặp lỗi tiếng kêu bản lề'</t>
+          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12398,7 +12928,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
+          <t>https://vnexpress.net/ban-dan-viet-nam-nen-di-theo-huong-toi-uu-nang-luong-5074612.html</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12408,12 +12938,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
+          <t>'Bán dẫn Việt Nam nên đi theo hướng tối ưu năng lượng'</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12429,7 +12959,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
+          <t>https://vnexpress.net/iphone-gap-co-the-gap-loi-tieng-keu-ban-le-5075003.html</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12439,12 +12969,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
+          <t>iPhone gập 'có thể gặp lỗi tiếng kêu bản lề'</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12460,22 +12990,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
+          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
+          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -12491,7 +13021,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
+          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12501,12 +13031,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
+          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -12522,22 +13052,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
+          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
+          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12553,7 +13083,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
+          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12563,12 +13093,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
+          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -12584,22 +13114,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
+          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
+          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12615,7 +13145,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
+          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12625,12 +13155,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
+          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -12646,22 +13176,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
+          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
+          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12677,7 +13207,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
+          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12687,12 +13217,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
+          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12708,7 +13238,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
+          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12718,12 +13248,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
+          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12739,7 +13269,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
+          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12749,7 +13279,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
+          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12770,7 +13300,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
+          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12780,7 +13310,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
+          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12801,7 +13331,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
+          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12811,12 +13341,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
+          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12832,22 +13362,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -12863,7 +13393,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
+          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12873,12 +13403,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
+          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12894,22 +13424,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -12925,7 +13455,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
+          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12935,12 +13465,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
+          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -12956,7 +13486,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/foxconn-bi-tan-cong-ma-hoa-du-lieu-co-the-lo-bi-mat-apple-5073614.html</t>
+          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12966,12 +13496,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Foxconn bị tấn công mã hóa dữ liệu, có thể lộ bí mật Apple</t>
+          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12987,7 +13517,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
+          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12997,7 +13527,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
+          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -13018,7 +13548,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
+          <t>https://vnexpress.net/foxconn-bi-tan-cong-ma-hoa-du-lieu-co-the-lo-bi-mat-apple-5073614.html</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13028,7 +13558,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
+          <t>Foxconn bị tấn công mã hóa dữ liệu, có thể lộ bí mật Apple</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13049,7 +13579,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
+          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13059,7 +13589,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
+          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13080,7 +13610,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
+          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13090,7 +13620,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
+          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13111,7 +13641,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
+          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13121,7 +13651,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
+          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13142,7 +13672,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
+          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13152,7 +13682,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
+          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13173,7 +13703,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
+          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13183,7 +13713,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Vai trò của sách trong thời AI</t>
+          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13204,7 +13734,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
+          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13214,12 +13744,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
+          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -13235,22 +13765,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-dau-tu-nen-lam-gi-khi-chung-khoan-len-cao-ky-luc-5074966.html</t>
+          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Nhà đầu tư nên làm gì khi chứng khoán lên cao kỷ lục?</t>
+          <t>Vai trò của sách trong thời AI</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -13266,22 +13796,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
+          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này được dự báo giảm tiếp</t>
+          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13297,7 +13827,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
+          <t>https://vnexpress.net/nha-dau-tu-nen-lam-gi-khi-chung-khoan-len-cao-ky-luc-5074966.html</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13307,12 +13837,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
+          <t>Nhà đầu tư nên làm gì khi chứng khoán lên cao kỷ lục?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13328,7 +13858,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
+          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13338,7 +13868,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
+          <t>Giá vàng tuần này được dự báo giảm tiếp</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -13359,7 +13889,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
+          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13369,12 +13899,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
+          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -13390,7 +13920,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
+          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13400,12 +13930,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
+          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -13421,7 +13951,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
+          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13431,12 +13961,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
+          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13452,7 +13982,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
+          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13462,12 +13992,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
+          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13483,7 +14013,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13493,12 +14023,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
+          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -13514,7 +14044,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
+          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13524,12 +14054,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
+          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -13545,7 +14075,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
+          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13555,12 +14085,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
+          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -13576,7 +14106,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
+          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13586,17 +14116,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
+          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>T3_SPORTS</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -13607,7 +14137,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
+          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13617,7 +14147,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
+          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -13638,7 +14168,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
+          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13648,17 +14178,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
+          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_SPORTS</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -13669,7 +14199,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
+          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13679,7 +14209,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
+          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -13700,7 +14230,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13710,7 +14240,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -13731,7 +14261,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13741,7 +14271,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -13762,7 +14292,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13772,7 +14302,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -13793,7 +14323,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13803,7 +14333,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -13824,7 +14354,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13834,7 +14364,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -13855,7 +14385,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
+          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13865,7 +14395,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
+          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -13886,7 +14416,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
+          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13896,7 +14426,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
+          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -13917,7 +14447,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
+          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13927,12 +14457,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Giá xăng, dầu cùng giảm</t>
+          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -13948,7 +14478,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13958,12 +14488,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -13979,7 +14509,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13989,7 +14519,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -14010,7 +14540,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
+          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14020,7 +14550,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
+          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -14041,7 +14571,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14051,12 +14581,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -14072,7 +14602,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14082,12 +14612,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -14103,7 +14633,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14113,7 +14643,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -14134,22 +14664,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14165,22 +14695,22 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
+          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
+          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -14196,7 +14726,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14206,12 +14736,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
+          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14221,6 +14751,68 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>vneconomy_techconnect</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>NO_KEYWORD</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>vneconomy_techconnect</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>NO_KEYWORD</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14294,12 +14886,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14324,12 +14916,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14354,12 +14946,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14384,12 +14976,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -14414,12 +15006,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14444,12 +15036,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14474,12 +15066,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -14504,12 +15096,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -14534,12 +15126,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -14564,12 +15156,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -14594,12 +15186,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14624,12 +15216,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14641,10 +15233,10 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -14654,12 +15246,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14684,12 +15276,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -14698,10 +15290,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -14714,12 +15306,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -14744,12 +15336,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -14774,12 +15366,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -14804,12 +15396,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -14834,12 +15426,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -14864,12 +15456,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -14894,12 +15486,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -14924,12 +15516,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -14954,12 +15546,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -14984,12 +15576,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15014,12 +15606,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15044,12 +15636,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15074,12 +15666,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15104,12 +15696,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15134,12 +15726,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15164,12 +15756,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15194,12 +15786,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15224,12 +15816,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15254,12 +15846,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15268,13 +15860,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -15284,12 +15876,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15314,12 +15906,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15344,12 +15936,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18T02:42:43.540294+00:00</t>
+          <t>2026-05-18T03:00:19.639243+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-18T02:51:04.566491+00:00</t>
+          <t>2026-05-18T03:07:50.089123+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">

--- a/output/raw_data.xlsx
+++ b/output/raw_data.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V109"/>
+  <dimension ref="A1:V108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -578,17 +578,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/car/thuongdoanhthumoituan-grabcar/</t>
+          <t>https://www.scmp.com/tech/policy/article/3353315/china-clears-tencents-ximalaya-acquisition-strict-bans-exclusive-deals-fee-hikes?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GrabCar | Cập nhật chương trình thưởng doanh thu mỗi tuần tại một số khu vực</t>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -606,22 +606,22 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>GrabCar | Cập nhật chương trình thưởng doanh thu mỗi tuần tại một số khu vực</t>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -629,28 +629,24 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>GrabCar | Cập nhật chương trình thưởng doanh thu mỗi tuần tại một số khu vực</t>
+          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Chủ Nhật Tháng Năm 17th, 2026 GrabCar | Cập nhật chương trình thưởng doanh thu mỗi tuần tại một số khu vực Quý Đối tác thân mến, Từ ngày 18/5/2026, Grab cập nhật chương trình thưởng % doanh thu mỗi tuần với thông tin chi tiết như sau: LƯU Ý LƯU Ý Tiền thưởng sẽ được tự động thanh toán vào Ví Tiền mặ</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
+          <t>Tencent Holdings has secured conditional approval to acquire online audio platform Ximalaya after a nearly year-long review by China’s antitrust watchdog, a move set to expand the Shenzhen-based tech giant’s footprint in China’s digital content ecosystem. The State Administration for Market Regulati</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="V2" s="2" t="inlineStr"/>
     </row>
@@ -660,17 +656,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/tin-tuc-su-kien/tham-gia-vong-song-khoe-nhan-qua-co-tri-gia-den-8707</t>
+          <t>https://banhang.shopee.vn/edu/article/25901</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -688,12 +684,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -703,7 +699,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>MoMo</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -711,32 +707,20 @@
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ Sự Kiện · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Làm nhiệm vụ đơn giản, nhận lượt quay và trúng quà có giá trị cao tại Vòng Sống Khỏe. Xem chi tiết ngay! Thời gian áp dụng: Từ 18/05/2026 đến hết ngày 30/09/202</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
+          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="V3" s="2" t="inlineStr"/>
     </row>
@@ -746,17 +730,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/policy/article/3353315/china-clears-tencents-ximalaya-acquisition-strict-bans-exclusive-deals-fee-hikes?utm_source=rss_feed</t>
+          <t>https://momo.vn/tin-tuc/cong-dong/thanh-cong-trao-195-suat-hoc-bong-cho-hoc-sinh-8714</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Thành công trao 195 suất học bổng cho học sinh nghèo hiếu học tại Cần Thơ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -774,22 +758,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Thành công trao 195 suất học bổng cho học sinh nghèo hiếu học tại Cần Thơ</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -797,24 +781,24 @@
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>China clears Tencent’s Ximalaya acquisition with strict bans on exclusive deals, fee hikes</t>
+          <t>Thành công trao 195 suất học bổng cho học sinh nghèo hiếu học tại Cần Thơ</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Tencent Holdings has secured conditional approval to acquire online audio platform Ximalaya after a nearly year-long review by China’s antitrust watchdog, a move set to expand the Shenzhen-based tech giant’s footprint in China’s digital content ecosystem. The State Administration for Market Regulati</t>
+          <t>Thành công trao 195 suất học bổng cho học sinh nghèo hiếu học tại Cần Thơ Cộng đồng · 14/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Những suất học bổng này không chỉ giúp giảm bớt gánh nặng về chi phí học tập cho các gia đình, mà còn là lời động viên, tiếp sức cho các em. Họ</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>3.84</v>
+        <v>3.52</v>
       </c>
       <c r="V4" s="2" t="inlineStr"/>
     </row>
@@ -824,17 +808,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/25901</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/sale-giua-thang-5-ve-may-bay-giam-den-1-trieu-8712</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+          <t>Sale giữa tháng 5: Vé máy bay giảm đến 1 triệu</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -852,12 +836,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
+          <t>Sale giữa tháng 5: Vé máy bay giảm đến 1 triệu</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -867,7 +851,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -875,20 +859,24 @@
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT CHÍNH SÁCH GÓI VOUCHER XTRA VÀ CONTENT XTRA DÀNH CHO TẤT CẢ NGƯỜI BÁN TỪ THÁNG 09/2025</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t>Sale giữa tháng 5: Vé máy bay giảm đến 1 triệu</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Sale giữa tháng 5: Vé máy bay giảm đến 1 triệu Khuyến mãi · 13/05/2026 · 5.6K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Giữa tháng lương chưa kịp về nhưng đã có nhu cầu đặt vé đi chơi, canh đúng ngày 15/5 để săn sale giữa tháng từ MoMo Travel nhé! Điểm danh ưu đãi sale giữ</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="V5" s="2" t="inlineStr"/>
     </row>
@@ -1580,12 +1568,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/grab-community?page=1</t>
+          <t>https://www.grab.com/vn/blog/thong-bao-trien-khai-dich-vu-grabcar-plus-grabbike-plus-tai-mot-so-tinh-thanh/</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1599,7 +1587,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1608,10 +1596,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1627,15 +1619,19 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Thứ Tư Tháng Năm 13th, 2026 Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành Bạn thân mến, Nhằm đáp ứng nhu cầu di chuyển đa dạng của hành khách, Grab chính thức triển khai dịch vụ GrabCar, GrabCar Plus và GrabBike Plus tại một số tỉnh thành từ ngày 14/05/2026. Thông ti</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="n">
         <v>3</v>
@@ -1654,12 +1650,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driven-by-tech?page=1</t>
+          <t>https://www.grab.com/vn/blog/thu-thach-cua-tin/</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
+          <t>Thử thách của Tín</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1673,7 +1669,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1682,10 +1678,14 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>Thử thách của Tín</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1701,12 +1701,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Driven by Tech</t>
+          <t>Thử thách của Tín</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
+          <t xml:space="preserve">Thứ Ba Tháng Năm 12th, 2026 Thử thách của Tín Các bạn sinh viên ơi! Grab chính thức khởi động Thử thách “Bản đồ bung sức mùa thi cùng Grab” với nhiều phần quà vô cùng hấp dẫn trong tháng 05 tới đây. Hãy cùng Grab khám phá thể lệ chi tiết của Thử thách này nhé! 🏁 THÔNG TIN TỔNG QUAN VỀ THỬ THÁCH Tên </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1728,17 +1728,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/pulse-of-vietnam?page=1</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/combo-du-lich-sieu-hoi-don-chao-le-hoi-phao-hoa-8718</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1756,10 +1756,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -1767,7 +1771,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1775,12 +1779,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Pulse of Vietnam</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Grab Blog Ưu đãi ngân hàng ACB Passenger Blog Ưu đãi khi sử dụng thẻ ACB thanh toán khi đặt Grab Muốn ăn ngon thì phải vào bếp, nhưng muốn ăn vừa ngon vừa rẻ thì nhớ thanh toán bằng thẻ ACB khi đặt Grab. Ưu [..] Read More Ưu đãi ngân hàng HD Bank Passenger Blog Ưu đãi khi sử dụng thẻ HD Bank thanh t</t>
+          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng Khuyến mãi · 15/05/2026 · 2.9K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Lễ hội Pháo hoa Quốc tế Đà Nẵng (DIFF) 2026 chính thức quay trở lại, hứa hẹn biến bầu trời sông Hàn thành một kiệt tác nghệ thuật đầy mê h</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1802,17 +1806,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/thong-bao-trien-khai-dich-vu-grabcar-plus-grabbike-plus-tai-mot-so-tinh-thanh/</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/155-315-hoan-den-8686d-khi-tu-chuyen-2k-tu-ngan-8717</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1830,12 +1834,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1845,7 +1849,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1853,20 +1857,24 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Thứ Tư Tháng Năm 13th, 2026 Thông báo triển khai dịch vụ GrabCar Plus, GrabBike Plus tại một số tỉnh thành Bạn thân mến, Nhằm đáp ứng nhu cầu di chuyển đa dạng của hành khách, Grab chính thức triển khai dịch vụ GrabCar, GrabCar Plus và GrabBike Plus tại một số tỉnh thành từ ngày 14/05/2026. Thông ti</t>
+          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN Khuyến mãi · 15/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn MoMo thưởng đến 8.686Đ cho bạn khi thực hiện giao dịch tự chuyển 2K từ app Ngân hàng đến SĐT MoMo của chính mình. Thời gian diễn r</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr"/>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
       <c r="S18" s="2" t="n">
         <v>3</v>
       </c>
@@ -1884,17 +1892,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/thu-thach-cua-tin/</t>
+          <t>https://momo.vn/tin-tuc/thong-bao/moi-lan-thanh-toan-hoa-don-them-mam-xanh-duoc-8709</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1912,7 +1920,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1927,7 +1935,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1935,12 +1943,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Thử thách của Tín</t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Ba Tháng Năm 12th, 2026 Thử thách của Tín Các bạn sinh viên ơi! Grab chính thức khởi động Thử thách “Bản đồ bung sức mùa thi cùng Grab” với nhiều phần quà vô cùng hấp dẫn trong tháng 05 tới đây. Hãy cùng Grab khám phá thể lệ chi tiết của Thử thách này nhé! 🏁 THÔNG TIN TỔNG QUAN VỀ THỬ THÁCH Tên </t>
+          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ Thông báo · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Thay vì chỉ là những giao dịch thanh toán thông thường, giờ đây với Green Hub - Góp hóa đơn trồng rừng trên MoMo, mỗi hóa đơn bạn chi trả đều mang lại giá trị đó</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -1962,17 +1970,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/bike/ugc-quantotbung/</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/ve-san-vang-doi-199-momo-xu-de-co-co-hoi-nhan-den-8706</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Vé Săn Vàng: Đổi 199 MoMo Xu để có cơ hội nhận đến 2 chỉ vàng PNJ</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1990,12 +1998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Vé Săn Vàng: Đổi 199 MoMo Xu để có cơ hội nhận đến 2 chỉ vàng PNJ</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2005,7 +2013,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>MoMo</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -2013,16 +2021,24 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO”</t>
+          <t>Vé Săn Vàng: Đổi 199 MoMo Xu để có cơ hội nhận đến 2 chỉ vàng PNJ</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thứ Sáu Tháng Năm 15th, 2026 Grab | Thử thách quay video: “LAN TỎA QUÁN TỐT BỤNG – CHÚT MÁT LÒNG GỬI TRAO” Quý Đối tác thân mến, Mùa nắng nóng cao điểm đã đến, những cung đường dường như dài hơn và oi ả hơn. Thế nhưng, giữa cái nắng gắt ấy, sự tử tế vẫn luôn hiện hữu qua những ly nước mát lạnh miễn </t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr"/>
+          <t>Vé Săn Vàng: Đổi 199 MoMo Xu để có cơ hội nhận đến 2 chỉ vàng PNJ Khuyến mãi · 12/05/2026 · 5.1K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Cơ hội săn vàng cực xịn đã đến, bạn chỉ cần dùng 199 Xu để đổi lấy 1 chiếc vé may mắn và có cơ hội rước về nhà đến 2 chỉ vàng PNJ. Xem</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n">
         <v>3</v>
       </c>
@@ -2040,12 +2056,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/khuyen-mai/combo-du-lich-sieu-hoi-don-chao-le-hoi-phao-hoa-8718</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/dat-ve-tau-thuy-tren-momo-nhanh-chong-an-toan-8708</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
+          <t>Đặt vé tàu thủy trên MoMo: Nhanh chóng, an toàn, chuẩn Châu Âu</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2068,12 +2084,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
+          <t>Đặt vé tàu thủy trên MoMo: Nhanh chóng, an toàn, chuẩn Châu Âu</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2091,12 +2107,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng</t>
+          <t>Đặt vé tàu thủy trên MoMo: Nhanh chóng, an toàn, chuẩn Châu Âu</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Combo du lịch siêu hời - Đón chào lễ hội pháo hoa tại Đà Nẵng Khuyến mãi · 15/05/2026 · 2.7K lượt xem Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Lễ hội Pháo hoa Quốc tế Đà Nẵng (DIFF) 2026 chính thức quay trở lại, hứa hẹn biến bầu trời sông Hàn thành một kiệt tác nghệ thuật đầy mê h</t>
+          <t>Đặt vé tàu thủy trên MoMo: Nhanh chóng, an toàn, chuẩn Châu Âu Khuyến mãi · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Bạn đang lên kế hoạch vi vu Phú Quốc, Phú Quý, hay Côn Đảo bằng đường thủy? Thay vì tốn thời gian ra bến tàu xếp hàng chờ đợi, giờ đây bạn hoàn toàn có t</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -2118,17 +2134,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/khuyen-mai/155-315-hoan-den-8686d-khi-tu-chuyen-2k-tu-ngan-8717</t>
+          <t>https://blog.whatsapp.com/new-feature-roundup-free-up-space-multiple-accounts-cross-platform-transfer-and-more</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2137,7 +2153,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -2146,14 +2162,10 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2161,7 +2173,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>MoMo</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
@@ -2169,24 +2181,16 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN</t>
+          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>[15.5 - 31.5] HOÀN ĐẾN 8.686Đ KHI TỰ CHUYỂN 2K TỪ NGÂN HÀNG ĐẾN SĐT MOMO CỦA BẢN THÂN Khuyến mãi · 15/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn MoMo thưởng đến 8.686Đ cho bạn khi thực hiện giao dịch tự chuyển 2K từ app Ngân hàng đến SĐT MoMo của chính mình. Thời gian diễn r</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Over time, our chats become a record of the moments that matter: conversations with family, laughs with friends, the photos and videos we couldn't stop sharing. To help you make the most of all of it, we're rolling out new ways to make WhatsApp even easier to use — whether you're staying organized, </t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="n">
         <v>3</v>
       </c>
@@ -2204,17 +2208,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://momo.vn/tin-tuc/thong-bao/moi-lan-thanh-toan-hoa-don-them-mam-xanh-duoc-8709</t>
+          <t>https://blog.whatsapp.com/whatsapps-latest-privacy-protection-strict-account-settings</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>momo_newsroom</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2223,7 +2227,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -2232,14 +2236,10 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Players Movement</t>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>MoMo</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
@@ -2255,12 +2255,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ</t>
+          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Mỗi lần thanh toán hoá đơn, thêm mầm xanh được tích luỹ Thông báo · 12/05/2026 Chia sẻ Sao chép liên kết Chia sẻ Facebook Chia sẻ LinkedIn Thay vì chỉ là những giao dịch thanh toán thông thường, giờ đây với Green Hub - Góp hóa đơn trồng rừng trên MoMo, mỗi hóa đơn bạn chi trả đều mang lại giá trị đó</t>
+          <t>At WhatsApp, we think you should be able to have a private conversation online, just like you would in-person. We will always defend that right to privacy for everyone, starting with default end-to-end encryption. But we also know that a few of our users – like journalists or public-facing figures –</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://blog.whatsapp.com/new-feature-roundup-free-up-space-multiple-accounts-cross-platform-transfer-and-more</t>
+          <t>https://blog.whatsapp.com/level-up-your-whatsapp-group-chats-with-new-member-tags-text-stickers-and-more</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -2329,12 +2329,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>New Feature Roundup: Free up space, multiple accounts, cross-platform transfer and more</t>
+          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Over time, our chats become a record of the moments that matter: conversations with family, laughs with friends, the photos and videos we couldn't stop sharing. To help you make the most of all of it, we're rolling out new ways to make WhatsApp even easier to use — whether you're staying organized, </t>
+          <t>It’s a new year and a great time for some upgrades to your group chats. Group chats on WhatsApp make it easier to stay connected with the people in your life no matter what device they own – whether it’s sharing New Year’s resolutions, preparing for that special celebration you have coming up, or pl</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://blog.whatsapp.com/whatsapps-latest-privacy-protection-strict-account-settings</t>
+          <t>https://blog.whatsapp.com/reintroducing-about-an-improved-way-to-share-what-youre-up-to</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -2403,12 +2403,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp's Latest Privacy Protection: Strict Account Settings</t>
+          <t>Reintroducing About: An improved way to share what you're up to</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>At WhatsApp, we think you should be able to have a private conversation online, just like you would in-person. We will always defend that right to privacy for everyone, starting with default end-to-end encryption. But we also know that a few of our users – like journalists or public-facing figures –</t>
+          <t>For those of you that have used WhatsApp from the very start, you’ll remember About was our first feature. Even before we brought the world private and secure messaging, we made it simple for you to quickly share what’s up in your life. Today we're reintroducing and improving About, making it more v</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://blog.whatsapp.com/level-up-your-whatsapp-group-chats-with-new-member-tags-text-stickers-and-more</t>
+          <t>https://zalopay.vn/tin-tuc/tin-tuc-su-kien</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>whatsapp_blog</t>
+          <t>zalopay_news</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
@@ -2477,12 +2477,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Level Up Your WhatsApp Group Chats With New Member Tags, Text Stickers, and More</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>It’s a new year and a great time for some upgrades to your group chats. Group chats on WhatsApp make it easier to stay connected with the people in your life no matter what device they own – whether it’s sharing New Year’s resolutions, preparing for that special celebration you have coming up, or pl</t>
+          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://blog.whatsapp.com/reintroducing-about-an-improved-way-to-share-what-youre-up-to</t>
+          <t>https://zalopay.vn/khuyen-mai/dac-biet</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Reintroducing About: An improved way to share what you're up to</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>whatsapp_blog</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Reintroducing About: An improved way to share what you're up to</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp</t>
+          <t>Zalo</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
@@ -2551,12 +2551,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Reintroducing About: An improved way to share what you're up to</t>
+          <t>Khuyến mãi – Ưu Đãi</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>For those of you that have used WhatsApp from the very start, you’ll remember About was our first feature. Even before we brought the world private and secure messaging, we made it simple for you to quickly share what’s up in your life. Today we're reintroducing and improving About, making it more v</t>
+          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -2578,17 +2578,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/tin-tuc/tin-tuc-su-kien</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353594/chinese-foundries-smic-hua-hong-forecast-second-quarter-growth-amid-ai-boom?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>zalopay_news</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -2606,18 +2606,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
@@ -2625,24 +2629,24 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Tin tức</t>
+          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
+          <t>China’s leading semiconductor foundries, Semiconductor Manufacturing International Corporation (SMIC) and Hua Hong Semiconductor, expect their second-quarter sales to rise amid a dynamic global market defined by surging artificial intelligence demand and a memory supply crunch, while Hua Hong said i</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="V28" s="2" t="inlineStr"/>
     </row>
@@ -2652,17 +2656,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/dac-biet</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353451/alibaba-ai-revenue-logs-triple-digit-growth-11th-quarter-amid-strategic-reshuffle?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2671,7 +2675,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -2680,18 +2684,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Zalo</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
@@ -2699,24 +2707,24 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Trang chủ Tin tức Tin tức Cập nhập thông tin mới nhất về ZaloPay Khuyến mãi - Ưu đãi Ưu đãi riêng cho người dùng ZaloPay Blog Chuyên trang cung cấp thông tin hữu ích Dịch vụ Chuyển tiền - Nhận tiền Miễn phí, an toàn, chuyển tiền Zalo chat Nạp tiền điện thoại Nạp ĐT - Mua thẻ ĐT - Data 3G/4G Thanh to</t>
+          <t>Alibaba Group Holding expects its annualised recurring revenue from AI models and applications to hit 30 billion yuan (US$4.42 billion) by the year’s end, as the company ramps up its AI commitment. AI products are projected to generate more than 50 per cent of Alibaba’s cloud-computing revenue withi</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="V29" s="2" t="inlineStr"/>
     </row>
@@ -2726,12 +2734,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353594/chinese-foundries-smic-hua-hong-forecast-second-quarter-growth-amid-ai-boom?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353214/kuaishou-stock-surges-reports-kling-ai-unit-spin?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2754,12 +2762,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2777,12 +2785,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Chinese foundries SMIC, Hua Hong forecast second-quarter growth amid AI boom</t>
+          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>China’s leading semiconductor foundries, Semiconductor Manufacturing International Corporation (SMIC) and Hua Hong Semiconductor, expect their second-quarter sales to rise amid a dynamic global market defined by surging artificial intelligence demand and a memory supply crunch, while Hua Hong said i</t>
+          <t>Kuaishou Technology’s shares jumped as much as 10 per cent on Tuesday morning after reports that the Chinese short-video platform was raising new funding for its Kling AI unit at a valuation of US$20 billion. Kuaishou – often seen as a rival to ByteDance-owned Douyin in China – plans to spin off its</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -2804,17 +2812,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353451/alibaba-ai-revenue-logs-triple-digit-growth-11th-quarter-amid-strategic-reshuffle?utm_source=rss_feed</t>
+          <t>https://banhang.shopee.vn/edu/article/25329</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2832,22 +2840,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
@@ -2855,24 +2863,20 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Alibaba CEO signals capex boost as China tech giant forges full-stack AI path</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Alibaba Group Holding expects its annualised recurring revenue from AI models and applications to hit 30 billion yuan (US$4.42 billion) by the year’s end, as the company ramps up its AI commitment. AI products are projected to generate more than 50 per cent of Alibaba’s cloud-computing revenue withi</t>
-        </is>
-      </c>
+          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="V31" s="2" t="inlineStr"/>
     </row>
@@ -2882,17 +2886,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353214/kuaishou-stock-surges-reports-kling-ai-unit-spin?utm_source=rss_feed</t>
+          <t>https://banhang.shopee.vn/edu/article/27540</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2901,7 +2905,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2910,22 +2914,22 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Shopee</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
@@ -2933,24 +2937,24 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Kuaishou shares soar as Kling AI eyes US$20 billion valuation in potential spin-off</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>Kuaishou Technology’s shares jumped as much as 10 per cent on Tuesday morning after reports that the Chinese short-video platform was raising new funding for its Kling AI unit at a valuation of US$20 billion. Kuaishou – often seen as a rival to ByteDance-owned Douyin in China – plans to spin off its</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr"/>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
       <c r="R32" s="2" t="inlineStr"/>
       <c r="S32" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>3.36</v>
+        <v>3.28</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
     </row>
@@ -2960,12 +2964,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/25329</t>
+          <t>https://banhang.shopee.vn/edu/article/17468</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2988,12 +2992,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3011,7 +3015,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mức thuế suất GTGT áp dụng trên các loại phí của Shopee Việt Nam từ tháng 05/2025 đến hết tháng 12/2026</t>
+          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr"/>
@@ -3034,12 +3038,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27540</t>
+          <t>https://banhang.shopee.vn/edu/article/12783</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>collection_ic Created with Sketch. Hướng dẫn yêu cầu hỗ trợ (raise ticket) API trên Shopee Open Platform</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3053,7 +3057,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -3062,12 +3066,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>collection_ic Created with Sketch. Hướng dẫn yêu cầu hỗ trợ (raise ticket) API trên Shopee Open Platform</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3085,15 +3089,11 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN KHÔNG THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>collection_ic Created with Sketch. Hướng dẫn yêu cầu hỗ trợ (raise ticket) API trên Shopee Open Platform</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="n">
         <v>3</v>
@@ -3112,17 +3112,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/17468</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353797/ai-agents-face-trust-issues-high-risk-industrial-sectors-experts?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -3140,22 +3140,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Shopee</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
@@ -3163,20 +3163,24 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Tính năng phân bổ đơn vị vận chuyển tự động cho Người bán trên Shopee</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr"/>
+          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>China’s industrial sectors are racing to integrate artificial intelligence to boost efficiency, bolstered by state support, but experts warn that critical vertical markets – such as healthcare and aerospace – may be too “high risk” for the shift towards autonomous agents. Hailed as the driver of a “</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="T35" s="2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="U35" s="2" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="V35" s="2" t="inlineStr"/>
     </row>
@@ -3186,12 +3190,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353797/ai-agents-face-trust-issues-high-risk-industrial-sectors-experts?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353764/trump-xi-weigh-ai-guardrails-nvidia-chip-exports-hang-balance?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3214,12 +3218,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3237,12 +3241,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>AI agents face trust issues in ‘high-risk’ industrial sectors: experts</t>
+          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>China’s industrial sectors are racing to integrate artificial intelligence to boost efficiency, bolstered by state support, but experts warn that critical vertical markets – such as healthcare and aerospace – may be too “high risk” for the shift towards autonomous agents. Hailed as the driver of a “</t>
+          <t>US President Donald Trump and Chinese officials discussed artificial intelligence “guardrails” and Nvidia’s H200 chips during his just-ended state visit to Beijing. Speaking to reporters on Air Force One during his return flight, Trump said the two sides “talked about possibly working together for g</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -3264,12 +3268,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353764/trump-xi-weigh-ai-guardrails-nvidia-chip-exports-hang-balance?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353747/chinas-tech-companies-are-looking-rewrite-e-commerce-playbook-ai-agents?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3292,7 +3296,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -3315,12 +3319,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Trump, Xi weigh AI ‘guardrails’ as Nvidia chip exports hang in the balance</t>
+          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>US President Donald Trump and Chinese officials discussed artificial intelligence “guardrails” and Nvidia’s H200 chips during his just-ended state visit to Beijing. Speaking to reporters on Air Force One during his return flight, Trump said the two sides “talked about possibly working together for g</t>
+          <t>For years, online shopping in China has followed a rigid, tedious ritual: typing precise keywords, squinting at endless rows of listings, and falling into a rabbit hole of product comparisons. But for a man surnamed Liu, a 30-something finance professional based in Hong Kong, that experience has rec</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
@@ -3342,12 +3346,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353747/chinas-tech-companies-are-looking-rewrite-e-commerce-playbook-ai-agents?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353715/panic-over-capacity-crunch-mature-node-chips-drives-orders-chinese-foundries?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3370,7 +3374,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -3393,12 +3397,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>China’s tech companies are looking to rewrite the e-commerce playbook with AI agents</t>
+          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>For years, online shopping in China has followed a rigid, tedious ritual: typing precise keywords, squinting at endless rows of listings, and falling into a rabbit hole of product comparisons. But for a man surnamed Liu, a 30-something finance professional based in Hong Kong, that experience has rec</t>
+          <t>The global AI boom is driving orders back to Chinese foundries as overseas rivals shift production towards high-margin AI chips and high-bandwidth memory, creating a shortage in mature-node semiconductors, according to the head of China’s top contract chipmaker. “AI demand has directly pushed power-</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -3420,12 +3424,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353715/panic-over-capacity-crunch-mature-node-chips-drives-orders-chinese-foundries?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353310/how-bytedance-plans-turn-openclaw-craze-profitable-ai-business?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3448,12 +3452,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -3471,12 +3475,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>‘Panic’ over capacity crunch in mature node chips drives orders to Chinese foundries</t>
+          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>The global AI boom is driving orders back to Chinese foundries as overseas rivals shift production towards high-margin AI chips and high-bandwidth memory, creating a shortage in mature-node semiconductors, according to the head of China’s top contract chipmaker. “AI demand has directly pushed power-</t>
+          <t>ByteDance’s Volcano Engine, the cloud unit that released an OpenClaw-based cloud agent tool ArkClaw, is betting that the next phase of artificial intelligence will hinge on cheaper tokens, higher inference efficiency and longer context windows. “Agent-related token consumption still accounts for a s</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
@@ -3498,12 +3502,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353310/how-bytedance-plans-turn-openclaw-craze-profitable-ai-business?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353188/chinese-chip-pioneer-calls-focus-pragmatic-breakthroughs-over-chasing-2nm-hype?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3526,12 +3530,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -3549,12 +3553,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>How ByteDance plans to turn OpenClaw craze into a profitable AI business</t>
+          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>ByteDance’s Volcano Engine, the cloud unit that released an OpenClaw-based cloud agent tool ArkClaw, is betting that the next phase of artificial intelligence will hinge on cheaper tokens, higher inference efficiency and longer context windows. “Agent-related token consumption still accounts for a s</t>
+          <t>The founder of China’s largest contract chipmaker has urged the country’s semiconductor industry to pursue breakthroughs in niche markets such as mature chips, citing their importance for “supply chain security”. Richard Chang Rugin, 78, former CEO of Semiconductor Manufacturing International Corp (</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -3576,12 +3580,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353188/chinese-chip-pioneer-calls-focus-pragmatic-breakthroughs-over-chasing-2nm-hype?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353132/alibaba-taps-chinas-chat-buy-trend-qwen-ai-and-taobao-integration?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3604,7 +3608,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -3627,12 +3631,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Chinese chip pioneer calls for focus on ‘pragmatic breakthroughs’ over chasing 2nm hype</t>
+          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>The founder of China’s largest contract chipmaker has urged the country’s semiconductor industry to pursue breakthroughs in niche markets such as mature chips, citing their importance for “supply chain security”. Richard Chang Rugin, 78, former CEO of Semiconductor Manufacturing International Corp (</t>
+          <t>Alibaba Group Holding is integrating its flagship AI assistant Qwen into its biggest e-commerce platforms, betting that the future of online shopping lies in fluid conversations rather than rigid search terms. Using the Qwen app, shoppers are able to find, compare and purchase products from Taobao a</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -3654,17 +3658,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353132/alibaba-taps-chinas-chat-buy-trend-qwen-ai-and-taobao-integration?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/12/google-adds-gemini-powered-dictation-to-gboard-which-could-be-bad-news-for-dictation-startups/</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -3682,12 +3686,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3697,7 +3701,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Trung quốc</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -3705,21 +3709,21 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Alibaba taps into China’s ‘chat to buy’ trend via Qwen AI and Taobao integration</t>
+          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding is integrating its flagship AI assistant Qwen into its biggest e-commerce platforms, betting that the future of online shopping lies in fluid conversations rather than rigid search terms. Using the Qwen app, shoppers are able to find, compare and purchase products from Taobao a</t>
+          <t>Google's transcription feature will initially launch with Samsung Galaxy and Google Pixel phones.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U42" s="2" t="n">
         <v>3.24</v>
@@ -3732,17 +3736,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/google-adds-gemini-powered-dictation-to-gboard-which-could-be-bad-news-for-dictation-startups/</t>
+          <t>https://vnexpress.net/altman-bi-to-noi-doi-musk-bi-che-mat-tri-nho-chon-loc-5074265.html</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -3760,12 +3764,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3783,12 +3787,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Google adds Gemini-powered dictation to Gboard, which could be bad news for dictation startups</t>
+          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Google's transcription feature will initially launch with Samsung Galaxy and Google Pixel phones.</t>
+          <t>Luật sư của Elon Musk công kích uy tín của Sam Altman, trong khi phía OpenAI đặt nghi vấn về các hành động của Musk.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
@@ -3810,12 +3814,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/altman-bi-to-noi-doi-musk-bi-che-mat-tri-nho-chon-loc-5074265.html</t>
+          <t>https://vnexpress.net/loat-thong-tin-duoc-ong-chu-chatgpt-he-lo-trong-phien-toa-5073321.html</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3838,12 +3842,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3861,12 +3865,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Altman bị tố nói dối, Musk bị chê 'mất trí nhớ chọn lọc'</t>
+          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Luật sư của Elon Musk công kích uy tín của Sam Altman, trong khi phía OpenAI đặt nghi vấn về các hành động của Musk.</t>
+          <t>Trong phiên tòa đang diễn ra giữa Elon Musk và OpenAI, Sam Altman nhận xét Musk "đáng sợ", nhưng bị luật sư chất vấn về tính trung thực.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -3888,17 +3892,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/loat-thong-tin-duoc-ong-chu-chatgpt-he-lo-trong-phien-toa-5073321.html</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-15/pershing-square-has-taken-new-stake-in-microsoft-ackman-says</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3916,12 +3920,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3939,24 +3943,24 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Loạt thông tin được ông chủ ChatGPT hé lộ trong phiên tòa</t>
+          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Trong phiên tòa đang diễn ra giữa Elon Musk và OpenAI, Sam Altman nhận xét Musk "đáng sợ", nhưng bị luật sư chất vấn về tính trung thực.</t>
+          <t>Bill Ackman’s Pershing Square has built a $2.1 billion stake in Microsoft Corp., taking advantage of a decline in the company’s share price to invest in a business that he said is stronger and more resilient than investors think.</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
     </row>
@@ -3966,17 +3970,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/pershing-square-has-taken-new-stake-in-microsoft-ackman-says</t>
+          <t>https://about.fb.com/news/2026/05/meta-at-the-cannes-film-festival-2026/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3994,12 +3998,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -4017,12 +4021,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Ackman Takes $2.1 Billion Microsoft Stake in Tech Bet</t>
+          <t>Meta at The Cannes Film Festival 2026</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Bill Ackman’s Pershing Square has built a $2.1 billion stake in Microsoft Corp., taking advantage of a decline in the company’s share price to invest in a business that he said is stronger and more resilient than investors think.</t>
+          <t>Meta is proud to be an Official Partner of the Festival de Cannes in a new multi-year strategic partnership. It’s a natural fit: for decades, Cannes has defined how we see the world through the frame—and today, our platforms are where that view is shared with the world. With more than 3.5 billion pe</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -4044,17 +4048,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/meta-at-the-cannes-film-festival-2026/</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353576/ex-meta-chinese-star-researcher-joins-race-self-improving-ai-us46b-start?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -4072,12 +4076,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -4095,12 +4099,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Meta at The Cannes Film Festival 2026</t>
+          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Meta is proud to be an Official Partner of the Festival de Cannes in a new multi-year strategic partnership. It’s a natural fit: for decades, Cannes has defined how we see the world through the frame—and today, our platforms are where that view is shared with the world. With more than 3.5 billion pe</t>
+          <t>A star Chinese researcher laid off by Facebook owner Meta Platforms has co-founded a start-up focused on self-improving artificial intelligence systems, joining a wave of US and Chinese firms developing models capable of autonomously refining their own code and reasoning. Tian Yuandong, former resea</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
@@ -4122,12 +4126,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353576/ex-meta-chinese-star-researcher-joins-race-self-improving-ai-us46b-start?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353291/jdcom-swings-back-profitability-first-quarter-though-profits-tumble-53?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4150,12 +4154,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -4173,12 +4177,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Ex-Meta Chinese star researcher joins race for self-improving AI with US$4.6b start-up</t>
+          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>A star Chinese researcher laid off by Facebook owner Meta Platforms has co-founded a start-up focused on self-improving artificial intelligence systems, joining a wave of US and Chinese firms developing models capable of autonomously refining their own code and reasoning. Tian Yuandong, former resea</t>
+          <t xml:space="preserve">Chinese online shopping giant JD.com reported a 53.2 per cent year-on-year decline in first-quarter profit to 5.1 billion yuan (US$750.2 million) due to protracted competition on the e-commerce and food delivery fronts. The company was able to swing back to profitability after posting a loss in the </t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -4200,17 +4204,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353291/jdcom-swings-back-profitability-first-quarter-though-profits-tumble-53?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/cerebras-raises-5-5b-kicking-off-2026s-ipo-season-with-a-bang/</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -4228,12 +4232,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -4251,12 +4255,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>JD.com swings back to profitability in first quarter though profits tumble 53%</t>
+          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chinese online shopping giant JD.com reported a 53.2 per cent year-on-year decline in first-quarter profit to 5.1 billion yuan (US$750.2 million) due to protracted competition on the e-commerce and food delivery fronts. The company was able to swing back to profitability after posting a loss in the </t>
+          <t>A year ago, it looked like this day would never happen for Cerebras.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -4278,17 +4282,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/cerebras-raises-5-5b-kicking-off-2026s-ipo-season-with-a-bang/</t>
+          <t>https://vnexpress.net/startup-my-duoc-dinh-gia-gan-100-ty-usd-nho-chip-ai-bang-cai-dia-5074683.html</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4306,12 +4310,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -4329,12 +4333,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Cerebras raises $5.5B, then stock pops $108%, in the first huge tech IPO of 2026</t>
+          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>A year ago, it looked like this day would never happen for Cerebras.</t>
+          <t>Cerebras, doanh nghiệp được đánh giá là đối thủ của Nvidia, thu hút sự chú ý với mẫu chip AI có kích thước bằng chiếc đĩa.</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -4356,12 +4360,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/startup-my-duoc-dinh-gia-gan-100-ty-usd-nho-chip-ai-bang-cai-dia-5074683.html</t>
+          <t>https://vnexpress.net/giam-doc-anthropic-ai-viet-90-ma-cua-cong-ty-5073942.html</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -4384,12 +4388,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -4407,12 +4411,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Startup Mỹ được định giá gần 100 tỷ USD nhờ chip AI 'bằng cái đĩa'</t>
+          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Cerebras, doanh nghiệp được đánh giá là đối thủ của Nvidia, thu hút sự chú ý với mẫu chip AI có kích thước bằng chiếc đĩa.</t>
+          <t>Krishna Rao, Giám đốc tài chính của Anthropic, cho biết AI Claude đang thay đổi cách nhân viên văn phòng làm việc mỗi ngày.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
@@ -4434,12 +4438,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/giam-doc-anthropic-ai-viet-90-ma-cua-cong-ty-5073942.html</t>
+          <t>https://vnexpress.net/sony-a7-r-vi-may-anh-cam-bien-xep-chong-gia-114-trieu-dong-5074084.html</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4462,12 +4466,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -4485,12 +4489,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Giám đốc Anthropic: 'AI viết 90% mã của công ty'</t>
+          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Krishna Rao, Giám đốc tài chính của Anthropic, cho biết AI Claude đang thay đổi cách nhân viên văn phòng làm việc mỗi ngày.</t>
+          <t>Sony A7 R VI trang bị cảm biến xếp chồng (full stack) 67 megapixel, chip AI thế hệ mới, khả năng quay video 8K và giá 114 triệu đồng.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -4512,12 +4516,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sony-a7-r-vi-may-anh-cam-bien-xep-chong-gia-114-trieu-dong-5074084.html</t>
+          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -4540,12 +4544,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -4563,12 +4567,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI - máy ảnh cảm biến xếp chồng giá 114 triệu đồng</t>
+          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Sony A7 R VI trang bị cảm biến xếp chồng (full stack) 67 megapixel, chip AI thế hệ mới, khả năng quay video 8K và giá 114 triệu đồng.</t>
+          <t>Tài liệu tòa án cho thấy Sam Altman có cổ phần hơn hai tỷ USD tại hàng loạt công ty đang bắt tay với OpenAI.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr"/>
@@ -4590,12 +4594,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sam-altman-lo-khoi-tai-san-hon-2-ty-usd-tu-doi-tac-cua-openai-5073854.html</t>
+          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4618,7 +4622,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -4641,12 +4645,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Sam Altman 'lộ' khối tài sản hơn 2 tỷ USD từ đối tác của OpenAI</t>
+          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Tài liệu tòa án cho thấy Sam Altman có cổ phần hơn hai tỷ USD tại hàng loạt công ty đang bắt tay với OpenAI.</t>
+          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -4668,17 +4672,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dien-thoai-trump-t1-bat-dau-duoc-giao-hang-5073733.html</t>
+          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -4696,12 +4700,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -4719,12 +4723,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Điện thoại Trump T1 bắt đầu được giao hàng</t>
+          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Sau nhiều tháng trì hoãn, công ty Trump Mobile thông báo đang giao điện thoại T1 cho khách hàng đã đặt cọc 100 USD.</t>
+          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr"/>
@@ -4746,12 +4750,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/shopee-bi-phat-200-trieu-dong-vi-canh-tranh-khong-lanh-manh-5074500.html</t>
+          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4774,7 +4778,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -4797,12 +4801,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Shopee bị phạt 200 triệu đồng vì cạnh tranh không lành mạnh</t>
+          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Quảng cáo chương trình miễn phí vận chuyển gây nhầm lẫn vào tháng 8/2025, Shopee bị Ủy ban Cạnh tranh Quốc gia xử phạt 200 triệu đồng.</t>
+          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr"/>
@@ -4824,17 +4828,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cong-ty-dien-cua-ong-pham-nhat-vuong-tang-von-len-gan-80-000-ty-dong-5074427.html</t>
+          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>grab_inside</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4843,7 +4847,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -4852,22 +4856,18 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>AI in action</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Market Pulse</t>
+          <t>Players Movement</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Grab</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
@@ -4875,24 +4875,24 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Công ty điện của ông Phạm Nhật Vượng tăng vốn lên gần 80.000 tỷ đồng</t>
+          <t>AI in action</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>VinEnergo, công ty năng lượng do ông Phạm Nhật Vượng sáng lập, hoàn tất tăng vốn từ hơn 28.300 tỷ đồng lên 79.923 tỷ đồng, vượt tập đoàn Vingroup.</t>
+          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V57" s="2" t="inlineStr"/>
     </row>
@@ -4902,12 +4902,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/ai-in-action/</t>
+          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -4949,7 +4949,7 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>AI in action</t>
+          <t>Product innovation</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/product-innovation/</t>
+          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Product innovation</t>
+          <t>Tracing our impact</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://www.grab.com/sg/inside-grab/tracing-our-impact/</t>
+          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>grab_inside</t>
+          <t>openai_news</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -5078,18 +5078,22 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Players Movement</t>
+          <t>Market Pulse</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Grab</t>
+          <t>Quốc tế</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr"/>
@@ -5097,24 +5101,24 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Tracing our impact</t>
+          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>AI in action All stories Perspectives Solutions Product innovation All stories Rides Food and deliveries Financial services Enterprise Autonomous Technology GrabX Tracing our impact All stories Environment Social impact Marketplace principles All stories Fares and pricing Matching Inside scoop All s</t>
+          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="T60" s="2" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V60" s="2" t="inlineStr"/>
     </row>
@@ -5124,12 +5128,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/building-codex-windows-sandbox/</t>
+          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5152,7 +5156,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -5175,12 +5179,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Building a safe, effective sandbox to enable Codex on Windows</t>
+          <t>Our response to the TanStack npm supply chain attack</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Engineering Security Building a safe, effective sandbox to enable Codex on Windows By David Wiesen, Member of Technical Staff Share When I joined the Codex engineering team in September 2025, Codex for Windows didn’t have a sandbox implementation meaning that Windows users were forced t</t>
+          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr"/>
@@ -5202,12 +5206,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/our-response-to-the-tanstack-npm-supply-chain-attack/</t>
+          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5230,7 +5234,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -5253,12 +5257,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Our response to the TanStack npm supply chain attack</t>
+          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>May 13, 2026 Company Security Our response to the TanStack npm supply chain attack Share We recently identified a security issue involving a common open-source library, TanStack npm, that is part of a broader attack known as Mini Shai-Hulud ⁠ (opens in a new window) . We found no evidence that OpenA</t>
+          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr"/>
@@ -5280,12 +5284,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/openai-launches-the-deployment-company/</t>
+          <t>https://openai.com/index/running-codex-safely/</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5308,12 +5312,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -5331,12 +5335,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence</t>
+          <t>Running Codex safely at OpenAI</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>May 11, 2026 Company OpenAI launches the OpenAI Deployment Company to help businesses build around intelligence OpenAI has agreed to acquire Tomoro, giving the OpenAI Deployment Company experienced Forward Deployed Engineers from day one. Learn more Share OpenAI is launching the OpenAI Deployment Co</t>
+          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr"/>
@@ -5358,17 +5362,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://openai.com/index/running-codex-safely/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/chipmaker-cxmt-reports-eightfold-jump-in-sales-on-path-to-ipo</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Chipmaker CXMT Reports Eightfold Jump in Sales on Path to IPO</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>openai_news</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -5377,7 +5381,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -5386,12 +5390,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Chipmaker CXMT Reports Eightfold Jump in Sales on Path to IPO</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -5409,12 +5413,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Running Codex safely at OpenAI</t>
+          <t>Chipmaker CXMT Reports Eightfold Jump in Sales on Path to IPO</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>May 8, 2026 Security Safety Running Codex safely at OpenAI A look at the controls, boundaries, and telemetry OpenAI uses to govern coding agents in real workflows. Share As AI systems become more capable, they increasingly act on behalf of users. Coding agents can autonomously review repositories, r</t>
+          <t>ChangXin Memory Technologies Inc. reported soaring revenue and profit in the first quarter and forecast higher earnings ahead, bolstering its financials ahead of a high-profile initial public offering later this year.</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -5904,17 +5908,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-15/snap-youtube-settle-school-social-media-suit-ahead-of-trial</t>
+          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -5932,12 +5936,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -5955,12 +5959,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Snap, YouTube, TikTok Settle School Suit Targeting Social Media</t>
+          <t>Introducing Instants: A New Way to Share in the Moment</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Snap Inc., Google’s YouTube and ByteDance Ltd.’s TikTok reached agreements to settle the first lawsuit headed to trial over claims that addiction to top social media platforms has disrupted learning and pushed public schools to spend massive sums fighting a mental health crisis, according to court f</t>
+          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr"/>
@@ -5982,12 +5986,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/instants-share-in-the-moment/</t>
+          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6010,12 +6014,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -6033,12 +6037,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Introducing Instants: A New Way to Share in the Moment</t>
+          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re introducing Instants, a new way to share photos in the moment with your Close Friends or mutual followers with just a tap. Photos you share on Instants disappear after they’ve been viewed and can’t be viewed after 24 hours. You also can’t edit your instants before sharing, so you can sh</t>
+          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -6060,12 +6064,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/new-supervision-tools-parents-insights-teens-algorithm/</t>
+          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6088,12 +6092,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -6111,12 +6115,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>New Supervision Tools Give Parents Insights Into Their Teen’s Algorithm and More</t>
+          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>Today, we’re making it easier for parents to manage and supervise their teen’s experiences across Instagram, Meta Horizon, Facebook, and Messenger by consolidating the parental tools in Family Center. We’re also giving parents new insights to better understand their teen’s algorithm on Instagram and</t>
+          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr"/>
@@ -6138,12 +6142,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/introducing-business-ai-on-whatsapp-for-small-businesses-in-india/</t>
+          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6166,12 +6170,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -6189,12 +6193,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Introducing Business AI on WhatsApp for Small Businesses in India</t>
+          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>To enable small businesses with AI-powered customer support directly into the WhatsApp Business app, we’ve launched Business AI in India. Available in all native languages in India, this feature enables eligible businesses to respond to customer queries 24/7, capture leads, book appointments, and dr</t>
+          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -6216,17 +6220,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/celebrating-african-cinema-with-the-made-by-africa-loved-by-the-world-2026-campaign/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -6244,12 +6248,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -6267,12 +6271,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Celebrating African Cinema With the ‘Made by Africa, Loved by the World’ 2026 Campaign</t>
+          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>In celebration of Africa Day on May 25, Facebook has launched the sixth edition of its pan-African campaign, ‘Made by Africa, loved by the world: Where stories spark community.’ This year’s campaign shifts the spotlight to African cinema. The 2026 campaign features a five-part vodcast series profili</t>
+          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr"/>
@@ -6294,12 +6298,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353833/ais-world-cup-debut-real-time-data-poised-reshape-football-strategy-level-field?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6322,12 +6326,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -6345,12 +6349,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>AI’s World Cup debut: real-time data poised to reshape football strategy, level the field</t>
+          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence is set to make its World Cup debut in 2026, as football’s most-watched tournament turns to real-time data models and live 3D simulations to reshape match strategy and event operations. Each team will have access to its own AI model, allowing analysts to compare playing patter</t>
+          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -6372,17 +6376,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353573/alibaba-tencent-signal-ai-spending-surge-despite-earnings-pressure-china-chips-ramp?utm_source=rss_feed</t>
+          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -6400,7 +6404,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -6423,12 +6427,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Alibaba, Tencent present a tale of two strategies for AI spending</t>
+          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding and Tencent Holdings are doubling down on a massive artificial intelligence spending spree, betting that a new wave of Chinese-made chips will break the supply bottlenecks stifling their ambitions. While both Chinese tech giants saw revenues trail expectations this past quarter</t>
+          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr"/>
@@ -6450,12 +6454,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/spotify-to-adopt-apples-new-video-podcast-tech-offering-creators-easier-cross-platform-distribution/</t>
+          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -6478,7 +6482,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -6501,12 +6505,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Spotify to adopt Apple’s new video podcast tech, offering creators easier cross-platform distribution</t>
+          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Spotify will let creators distribute and monetize video podcasts on Apple Podcasts using Apple’s HLS streaming technology, without changing their existing workflows.</t>
+          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -6528,12 +6532,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/how-to-turn-of-instagrams-new-instants-feature-and-retract-photos-you-accidentally-shared/</t>
+          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -6556,12 +6560,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -6579,12 +6583,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>How to turn off Instagram’s new Instants feature and retract photos you accidentally shared</t>
+          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>While the Meta-owned social network billed Instants as a new format to share real-life moments as they’re happening, many users are looking for a way  to turn off the feature, especially those who have accidentally sent images to others, not fully understanding how the feature works.</t>
+          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr"/>
@@ -6606,12 +6610,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/amazon-launches-an-ai-shopping-assistant-for-the-search-bar-powered-by-alexa/</t>
+          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -6634,7 +6638,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -6657,12 +6661,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Amazon launches an AI shopping assistant for the search bar, powered by Alexa+</t>
+          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Alexa for Shopping offers a voice- and touch-enabled shopping experience across mobile, desktop, and Echo Show smart displays. Alexa for Shopping provides more personalized recommendations and automates the shopping experience across Amazon and other online retailers.</t>
+          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -6684,12 +6688,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/whatsapp-adds-an-incognito-mode-in-meta-ai-chats/</t>
+          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -6712,7 +6716,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -6735,12 +6739,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp adds an incognito mode in Meta AI chats</t>
+          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>Meta said these incognito conversations are not saved, and messages will disappear by default once you close the chat.</t>
+          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr"/>
@@ -6762,12 +6766,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/poppy-debuts-a-proactive-ai-assistant-to-help-organize-your-digital-life/</t>
+          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6790,12 +6794,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -6813,12 +6817,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Poppy debuts a proactive AI assistant to help organize your digital life</t>
+          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Poppy is an AI-powered app that connects your calendar, email, messages, and other services to surface reminders, suggestions, and tasks based on what’s happening in your life.</t>
+          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -6840,12 +6844,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/googles-create-my-widget-feature-will-let-you-vibe-code-your-own-widgets/</t>
+          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6868,7 +6872,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -6891,12 +6895,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Google’s ‘Create My Widget’ feature will let you vibe-code your own widgets</t>
+          <t>Android adds a feature to stop you from doomscrolling</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>To create a widget, users will be able to describe what they want using natural language. For example, you could ask the feature to "suggest three high-protein meal prep recipes every week" in order to get a custom dashboard that you can add and resize on your home screen.</t>
+          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr"/>
@@ -6918,12 +6922,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/android-adds-a-feature-to-stop-you-from-doomscrolling/</t>
+          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6946,7 +6950,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -6969,12 +6973,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Android adds a feature to stop you from doomscrolling</t>
+          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Google’s new Android feature, Pause Point, forces you to wait before opening distracting apps in an effort to curb addictive scrolling habits.</t>
+          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -6996,12 +7000,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/threads-tests-a-meta-ai-integration-that-works-similarly-to-grok/</t>
+          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -7024,7 +7028,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -7047,12 +7051,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Threads tests a Meta AI integration that works similarly to Grok</t>
+          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>The feature is designed to help people get real-time context about trends and breaking stories, as well as receive recommendations, all within conversations.</t>
+          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr"/>
@@ -7074,12 +7078,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/tiktok-now-wants-to-be-the-place-you-book-the-trip-you-just-saw-on-tiktok/</t>
+          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -7102,7 +7106,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -7125,12 +7129,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>TikTok now wants to be the place you book the trip you just saw on TikTok</t>
+          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>TikTok is systematically converting its discovery engine into a transaction layer, which both deepens user retention and opens entirely new revenue streams for its new owners.</t>
+          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -7152,12 +7156,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/spotify-launches-a-wrapped-style-recap-of-your-entire-listening-history/</t>
+          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -7180,12 +7184,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -7203,12 +7207,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Spotify launches a Wrapped-style recap of your entire listening history</t>
+          <t>NYT’s Wordle to become a TV game show</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>As part of its 20th anniversary celebration, the streaming service is now releasing a limited-time feature that surfaces various facts about users, such as when they joined the app, the first song they streamed, their favorite artist, and a playlist of their most-streamed songs.</t>
+          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr"/>
@@ -7230,17 +7234,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/11/nyts-wordle-to-become-a-tv-game-show/</t>
+          <t>https://techcrunch.com/2026/05/17/why-trust-is-a-big-question-at-the-elon-musk-openai-trial/</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -7258,12 +7262,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7281,12 +7285,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>NYT’s Wordle to become a TV game show</t>
+          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>This will be the first time that The Times has collaborated with a TV broadcaster for an entertainment-based program, representing yet another pivot in the media company's attempt to build a sustainable digital subscription business as print revenue continues to decline.</t>
+          <t>A big theme in the trial’s final days was whether OpenAI CEO Sam Altman is trustworthy.</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -7308,12 +7312,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/why-trust-is-a-big-question-at-the-elon-musk-openai-trial/</t>
+          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7336,12 +7340,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -7359,12 +7363,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Why trust is a big question at the Elon Musk-OpenAI trial</t>
+          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>A big theme in the trial’s final days was whether OpenAI CEO Sam Altman is trustworthy.</t>
+          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr"/>
@@ -7386,12 +7390,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/openai-co-founder-greg-brockman-reportedly-takes-charge-of-product-strategy/</t>
+          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7414,12 +7418,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -7437,12 +7441,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>OpenAI co-founder Greg Brockman takes charge of product strategy</t>
+          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>OpenAI's latest shakeup comes as the company reportedly plans to combine ChatGPT and its programming product Codex.</t>
+          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr"/>
@@ -7464,12 +7468,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/podcast/the-openai-trial-wraps-up-and-the-musk-founder-machine-keeps-spinning/</t>
+          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -7492,7 +7496,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -7515,12 +7519,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>The OpenAI trial wraps up, and the Musk founder machine keeps spinning</t>
+          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>The Musk v. Altman trial came to a close this week, and the final arguments kept circling back to one question:&amp;#160;can we trust the people in charge of AI?&amp;#160;All of this is playing out as SpaceX charges toward what could be one of the largest IPOs in American history, with&amp;#160;a whole generati</t>
+          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr"/>
@@ -7542,12 +7546,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/openai-launches-chatgpt-for-personal-finance-will-let-you-connect-bank-accounts/</t>
+          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -7570,7 +7574,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -7593,12 +7597,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>OpenAI launches ChatGPT for personal finance, will let you connect bank accounts</t>
+          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Once users connect their accounts, they will see a dashboard of their portfolio performance, spending, subscriptions, and upcoming payments.</t>
+          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -7620,12 +7624,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/runway-started-by-helping-filmmakers-now-it-wants-to-beat-google-at-ai/</t>
+          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -7648,12 +7652,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -7671,12 +7675,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Runway started by helping filmmakers — now it wants to beat Google at AI</t>
+          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>AI video-generation startup Runway is betting that video generation is the path to world models. And that being an AI outsider is an advantage, not a liability.</t>
+          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr"/>
@@ -7698,12 +7702,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-is-reportedly-preparing-legal-action-against-apple-it-wouldnt-be-the-first-partner-to-feel-burned/</t>
+          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7726,7 +7730,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -7749,12 +7753,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is reportedly preparing legal action against Apple; it wouldn’t be the first partner to feel burned</t>
+          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>OpenAI is so frustrated with Apple over a ChatGPT integration that failed to deliver the subscribers and prominence it expected that the company is now actively exploring legal action against the iPhone maker.</t>
+          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr"/>
@@ -7776,17 +7780,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/clawdmeter-turns-your-claude-code-usage-stats-into-a-tiny-desktop-dashboard/</t>
+          <t>https://vnexpress.net/phien-toa-ty-phu-dau-ty-phu-giua-musk-va-altman-5074631.html</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -7804,12 +7808,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -7827,12 +7831,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Clawdmeter turns your Claude Code usage stats into a tiny desktop dashboard</t>
+          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>A new open source gadget called Clawdmeter turns Claude Code usage stats into a tiny desktop dashboard for AI coding power users.</t>
+          <t>Sau ba tuần tranh tụng, bên cạnh những thông tin chưa từng xuất hiện, phiên tòa giữa Elon Musk với Sam Altman và OpenAI còn phô trương sự giàu có.</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr"/>
@@ -7854,12 +7858,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phien-toa-ty-phu-dau-ty-phu-giua-musk-va-altman-5074631.html</t>
+          <t>https://vnexpress.net/ai-mythos-cua-anthropic-co-the-be-khoa-may-mac-5074524.html</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -7882,12 +7886,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -7905,12 +7909,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Phiên tòa 'tỷ phú đấu tỷ phú' giữa Musk và Altman</t>
+          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>Sau ba tuần tranh tụng, bên cạnh những thông tin chưa từng xuất hiện, phiên tòa giữa Elon Musk với Sam Altman và OpenAI còn phô trương sự giàu có.</t>
+          <t>Các nhà nghiên cứu bảo mật cảnh báo Calude Mythos của Anthropic đã có thể vượt qua hệ thống bảo mật của macOS theo cách chưa từng đạt được trước đây.</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr"/>
@@ -7932,12 +7936,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ai-mythos-cua-anthropic-co-the-be-khoa-may-mac-5074524.html</t>
+          <t>https://vnexpress.net/loat-tinh-nang-moi-tren-android-17-5073388.html</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -7960,12 +7964,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -7983,12 +7987,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>AI Mythos của Anthropic có thể bẻ khóa máy Mac</t>
+          <t>Loạt tính năng mới trên Android 17</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>Các nhà nghiên cứu bảo mật cảnh báo Calude Mythos của Anthropic đã có thể vượt qua hệ thống bảo mật của macOS theo cách chưa từng đạt được trước đây.</t>
+          <t>Google giới thiệu hệ điều hành Android 17 tập trung vào Gemini và hướng tới chấm dứt tình trạng cuộn màn hình tiêu cực.</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr"/>
@@ -8010,12 +8014,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/loat-tinh-nang-moi-tren-android-17-5073388.html</t>
+          <t>https://vnexpress.net/nhung-dan-loa-tien-ty-tai-plase-show-2026-5074425.html</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -8038,7 +8042,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -8061,12 +8065,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Loạt tính năng mới trên Android 17</t>
+          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Google giới thiệu hệ điều hành Android 17 tập trung vào Gemini và hướng tới chấm dứt tình trạng cuộn màn hình tiêu cực.</t>
+          <t>Triển lãm thiết bị biểu diễn chuyên nghiệp Plase Show 2026 tăng quy mô trở lại, nổi bật với 14 dàn loa treo (line-array) giữa trời, gấp đôi năm ngoái.</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -8088,12 +8092,12 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nhung-dan-loa-tien-ty-tai-plase-show-2026-5074425.html</t>
+          <t>https://vnexpress.net/cac-startup-viet-tim-duong-sang-thi-truong-nhat-ban-5074085.html</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -8116,7 +8120,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -8139,12 +8143,12 @@
       <c r="N99" s="2" t="inlineStr"/>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Những dàn loa tiền tỷ tại Plase Show 2026</t>
+          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>Triển lãm thiết bị biểu diễn chuyên nghiệp Plase Show 2026 tăng quy mô trở lại, nổi bật với 14 dàn loa treo (line-array) giữa trời, gấp đôi năm ngoái.</t>
+          <t>Bên cạnh gọi vốn trong nước, nhiều startup Việt đang tìm cơ hội hợp tác, thử nghiệm sản phẩm và mở rộng sang thị trường Nhật Bản.</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr"/>
@@ -8166,12 +8170,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cac-startup-viet-tim-duong-sang-thi-truong-nhat-ban-5074085.html</t>
+          <t>https://vnexpress.net/cac-chuyen-gia-quoc-te-ban-ve-tuong-lai-ai-tai-tp-hcm-5073633.html</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -8194,12 +8198,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -8217,12 +8221,12 @@
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Các startup Việt tìm đường sang thị trường Nhật Bản</t>
+          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Bên cạnh gọi vốn trong nước, nhiều startup Việt đang tìm cơ hội hợp tác, thử nghiệm sản phẩm và mở rộng sang thị trường Nhật Bản.</t>
+          <t>Sự kiện GStar 2026, diễn ra cuối tháng 5 tại TP HCM, quy tụ nhiều chuyên gia từ Google, Qualcomm... cùng bàn về hướng phát triển định hình tương lai AI.</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -8244,12 +8248,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cac-chuyen-gia-quoc-te-ban-ve-tuong-lai-ai-tai-tp-hcm-5073633.html</t>
+          <t>https://vnexpress.net/sieu-hacker-ai-khien-loat-ngan-hang-my-voi-sua-loi-bao-mat-5073574.html</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -8272,7 +8276,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -8295,12 +8299,12 @@
       <c r="N101" s="2" t="inlineStr"/>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Các chuyên gia quốc tế bàn về tương lai AI tại TP HCM</t>
+          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>Sự kiện GStar 2026, diễn ra cuối tháng 5 tại TP HCM, quy tụ nhiều chuyên gia từ Google, Qualcomm... cùng bàn về hướng phát triển định hình tương lai AI.</t>
+          <t>Các ngân hàng Mỹ đang gấp rút khắc phục những điểm yếu hệ thống IT do Mythos, công cụ AI được mệnh danh "siêu hacker" của Anthropic, phát hiện.</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr"/>
@@ -8322,12 +8326,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/sieu-hacker-ai-khien-loat-ngan-hang-my-voi-sua-loi-bao-mat-5073574.html</t>
+          <t>https://vnexpress.net/grok-cua-elon-musk-mat-dan-vi-the-trong-cuoc-dua-ai-5073523.html</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -8350,12 +8354,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -8373,12 +8377,12 @@
       <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>'Siêu hacker AI' khiến loạt ngân hàng Mỹ vội sửa lỗi bảo mật</t>
+          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>Các ngân hàng Mỹ đang gấp rút khắc phục những điểm yếu hệ thống IT do Mythos, công cụ AI được mệnh danh "siêu hacker" của Anthropic, phát hiện.</t>
+          <t>AI Grok của xAI, công ty do Elon Musk thành lập và điều hành, bị đánh giá tụt hậu khá xa so với các đối thủ OpenAI, Anthropic hay Google.</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
@@ -8400,17 +8404,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/grok-cua-elon-musk-mat-dan-vi-the-trong-cuoc-dua-ai-5073523.html</t>
+          <t>https://vnexpress.net/chu-tich-fpt-telecom-lam-sep-gtel-5074476.html</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -8428,12 +8432,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -8451,12 +8455,12 @@
       <c r="N103" s="2" t="inlineStr"/>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>Grok của Elon Musk mất dần vị thế trong cuộc đua AI</t>
+          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>AI Grok của xAI, công ty do Elon Musk thành lập và điều hành, bị đánh giá tụt hậu khá xa so với các đối thủ OpenAI, Anthropic hay Google.</t>
+          <t>Chủ tịch FPT Telecom vừa được bổ nhiệm giữ chức Phó tổng giám đốc Tổng công ty Công nghệ - Viễn thông Toàn cầu (GTEL) thuộc Bộ Công an.</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr"/>
@@ -8478,12 +8482,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chu-tich-fpt-telecom-lam-sep-gtel-5074476.html</t>
+          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -8506,7 +8510,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -8529,12 +8533,12 @@
       <c r="N104" s="2" t="inlineStr"/>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom làm sếp GTEL</t>
+          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>Chủ tịch FPT Telecom vừa được bổ nhiệm giữ chức Phó tổng giám đốc Tổng công ty Công nghệ - Viễn thông Toàn cầu (GTEL) thuộc Bộ Công an.</t>
+          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr"/>
@@ -8556,12 +8560,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/mo-hinh-kieng-ba-chan-giup-masan-but-toc-trong-mang-ban-le-5074018.html</t>
+          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -8584,12 +8588,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -8607,12 +8611,12 @@
       <c r="N105" s="2" t="inlineStr"/>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Mô hình 'kiềng ba chân' giúp Masan bứt tốc trong mảng bán lẻ</t>
+          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>Masan xây thương hiệu mạnh để kéo người dùng, vận hành chuỗi bán lẻ nhằm mở rộng độ phủ, ứng dụng công nghệ nắm bắt toàn cảnh vận hành, giúp doanh thu tăng trưởng hai chữ số.</t>
+          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr"/>
@@ -8634,17 +8638,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-tiep-tuc-lap-ky-luc-moi-5073931.html</t>
+          <t>https://techcrunch.com/2026/05/17/apples-siri-revamp-could-include-auto-deleting-chats/</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -8662,12 +8666,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -8685,12 +8689,12 @@
       <c r="N106" s="2" t="inlineStr"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Chứng khoán tiếp tục lập kỷ lục mới</t>
+          <t>Apple’s Siri revamp could include auto-deleting chats</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Nhờ sức nâng đỡ của cổ phiếu Vingroup, chứng khoán hôm nay tiếp tục ghi nhận kỷ lục mới, đóng cửa ở trên mốc 1.925 điểm.</t>
+          <t>Privacy will be a major theme when Apple unveils a new version of Siri.</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
@@ -8699,10 +8703,10 @@
         <v>2.6</v>
       </c>
       <c r="T106" s="2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U106" s="2" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="V106" s="2" t="inlineStr"/>
     </row>
@@ -8712,17 +8716,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/apples-siri-revamp-could-include-auto-deleting-chats/</t>
+          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -8740,12 +8744,12 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -8763,12 +8767,12 @@
       <c r="N107" s="2" t="inlineStr"/>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Apple’s Siri revamp could include auto-deleting chats</t>
+          <t>OpenAI says Codex is coming to your phone</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>Privacy will be a major theme when Apple unveils a new version of Siri.</t>
+          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr"/>
@@ -8790,22 +8794,22 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/openai-says-codex-is-coming-to-your-phone/</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>3 - Market signal</t>
+          <t>2 - Minor signal</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -8818,12 +8822,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -8833,7 +8837,7 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Quốc tế</t>
+          <t>Trung quốc</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr"/>
@@ -8841,104 +8845,26 @@
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>OpenAI says Codex is coming to your phone</t>
+          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>The update gives users enhanced flexibility over how they can manage their workflows.</t>
+          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="2" t="inlineStr"/>
       <c r="S108" s="2" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="T108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U108" s="2" t="n">
         <v>2.4</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>2.52</v>
-      </c>
       <c r="V108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353464/chinese-memory-module-makers-ramp-production-cxmt-ddr5-breakthrough-hits-market?utm_source=rss_feed</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>scmp_tech</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>2 - Minor signal</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Market Pulse</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>Trung quốc</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module makers ramp up production as CXMT DDR5 breakthrough hits market</t>
-        </is>
-      </c>
-      <c r="P109" s="2" t="inlineStr">
-        <is>
-          <t>Chinese memory module manufacturers are accelerating the release of consumer and enterprise storage products powered by domestic DDR5 chips, as breakthroughs by ChangXin Memory Technologies (CXMT), the nation’s leading memory chipmaker, filter through the supply chain. Powev, one of China’s major me</t>
-        </is>
-      </c>
-      <c r="Q109" s="2" t="inlineStr"/>
-      <c r="R109" s="2" t="inlineStr"/>
-      <c r="S109" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T109" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U109" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V109" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
@@ -8952,7 +8878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9779,27 +9705,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/vien-truong-vinatom-phat-trien-dien-hat-nhan-an-toan-la-so-mot-khong-co-ngoai-le.htm</t>
+          <t>https://vnexpress.net/nu-ty-phu-cong-nghe-trung-quoc-ngoi-giua-elon-musk-va-tim-cook-5074570.html</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Viện trưởng VINATOM: "Phát triển điện hạt nhân, an toàn là số một, không có ngoại lệ"</t>
+          <t>Nữ tỷ phú công nghệ Trung Quốc ngồi giữa Elon Musk và Tim Cook</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_9418fd7e597038c8</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -9810,7 +9736,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nu-ty-phu-cong-nghe-trung-quoc-ngoi-giua-elon-musk-va-tim-cook-5074570.html</t>
+          <t>https://vnexpress.net/ha-noi-mo-khong-gian-thuc-day-thuong-mai-hoa-cong-nghe-5074304.html</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9820,17 +9746,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nữ tỷ phú công nghệ Trung Quốc ngồi giữa Elon Musk và Tim Cook</t>
+          <t>Hà Nội mở không gian thúc đẩy thương mại hóa công nghệ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_9418fd7e597038c8</t>
+          <t>DUPLICATE_OF_33371aef61a2861a</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -9841,7 +9767,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-mo-khong-gian-thuc-day-thuong-mai-hoa-cong-nghe-5074304.html</t>
+          <t>https://vnexpress.net/ceo-xiaomi-va-elon-musk-gay-sot-khi-chup-selfie-5074051.html</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9851,17 +9777,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hà Nội mở không gian thúc đẩy thương mại hóa công nghệ</t>
+          <t>CEO Xiaomi và Elon Musk gây sốt khi chụp selfie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_33371aef61a2861a</t>
+          <t>DUPLICATE_OF_26113160399e295d</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -9872,7 +9798,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ceo-xiaomi-va-elon-musk-gay-sot-khi-chup-selfie-5074051.html</t>
+          <t>https://vnexpress.net/trai-nghiem-oppo-find-x9s-voi-camera-hasselblad-pin-lau-5073219.html</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9882,17 +9808,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEO Xiaomi và Elon Musk gây sốt khi chụp selfie</t>
+          <t>Trải nghiệm Oppo Find X9s với camera Hasselblad, pin lâu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_26113160399e295d</t>
+          <t>DUPLICATE_OF_1d2f664ed038de95</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -9903,7 +9829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trai-nghiem-oppo-find-x9s-voi-camera-hasselblad-pin-lau-5073219.html</t>
+          <t>https://vnexpress.net/tiktok-muon-thuc-day-mo-hinh-xa-thuong-mai-dien-tu-o-viet-nam-5073573.html</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9913,7 +9839,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Trải nghiệm Oppo Find X9s với camera Hasselblad, pin lâu</t>
+          <t>TikTok muốn thúc đẩy mô hình 'xã thương mại điện tử' ở Việt Nam</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -9923,7 +9849,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_1d2f664ed038de95</t>
+          <t>DUPLICATE_OF_fc44824132db1c02</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -9934,7 +9860,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tiktok-muon-thuc-day-mo-hinh-xa-thuong-mai-dien-tu-o-viet-nam-5073573.html</t>
+          <t>https://vnexpress.net/may-tinh-luong-tu-trung-quoc-nhanh-hon-sieu-may-tinh-cua-my-5074717.html</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9944,17 +9870,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TikTok muốn thúc đẩy mô hình 'xã thương mại điện tử' ở Việt Nam</t>
+          <t>Máy tính lượng tử Trung Quốc nhanh hơn siêu máy tính của Mỹ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_fc44824132db1c02</t>
+          <t>DUPLICATE_OF_0824a7656d0c5e85</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
@@ -9965,27 +9891,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/may-tinh-luong-tu-trung-quoc-nhanh-hon-sieu-may-tinh-cua-my-5074717.html</t>
+          <t>https://vnexpress.net/gia-vang-the-gioi-xuong-thap-nhat-gan-2-tuan-5074551.html</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Máy tính lượng tử Trung Quốc nhanh hơn siêu máy tính của Mỹ</t>
+          <t>Giá vàng thế giới xuống thấp nhất gần 2 tuần</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_0824a7656d0c5e85</t>
+          <t>DUPLICATE_OF_3ead10952ca31861</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -9996,17 +9922,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-the-gioi-xuong-thap-nhat-gan-2-tuan-5074551.html</t>
+          <t>https://vnexpress.net/chip-pc-cay-nha-la-vuon-trung-quoc-can-moc-doanh-so-mot-trieu-5073491.html</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Giá vàng thế giới xuống thấp nhất gần 2 tuần</t>
+          <t>Chip PC 'cây nhà lá vườn' Trung Quốc cán mốc doanh số một triệu</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -10016,7 +9942,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3ead10952ca31861</t>
+          <t>DUPLICATE_OF_1a2379fe5634145e</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -10027,17 +9953,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chip-pc-cay-nha-la-vuon-trung-quoc-can-moc-doanh-so-mot-trieu-5073491.html</t>
+          <t>https://vnexpress.net/ong-trump-trung-quoc-co-the-mua-750-may-bay-boeing-5074571.html</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chip PC 'cây nhà lá vườn' Trung Quốc cán mốc doanh số một triệu</t>
+          <t>Ông Trump: Trung Quốc có thể mua 750 máy bay Boeing</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10047,7 +9973,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_1a2379fe5634145e</t>
+          <t>DUPLICATE_OF_9207f47be79dbe06</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -10058,7 +9984,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ong-trump-trung-quoc-co-the-mua-750-may-bay-boeing-5074571.html</t>
+          <t>https://vnexpress.net/tp-hcm-chan-8-tan-thit-heo-gia-cam-khong-kiem-dich-5074708.html</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -10068,7 +9994,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ông Trump: Trung Quốc có thể mua 750 máy bay Boeing</t>
+          <t>TP HCM chặn 8 tấn thịt heo, gia cầm không kiểm dịch</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10078,7 +10004,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_9207f47be79dbe06</t>
+          <t>DUPLICATE_OF_22ab2ca1dc78a2b9</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -10089,7 +10015,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tp-hcm-chan-8-tan-thit-heo-gia-cam-khong-kiem-dich-5074708.html</t>
+          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10099,17 +10025,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TP HCM chặn 8 tấn thịt heo, gia cầm không kiểm dịch</t>
+          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_22ab2ca1dc78a2b9</t>
+          <t>DUPLICATE_OF_60723367cb83d78c</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -10120,7 +10046,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vietnam-airlines-co-the-lo-tro-lai-vi-gia-nhien-lieu-bay-neo-cao-5074266.html</t>
+          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -10130,7 +10056,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam Airlines có thể lỗ trở lại vì giá nhiên liệu bay neo cao</t>
+          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10140,7 +10066,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_60723367cb83d78c</t>
+          <t>DUPLICATE_OF_9207f47be79dbe06</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -10151,7 +10077,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-boeing-mat-gia-khi-trung-quoc-co-the-chi-mua-200-may-bay-5074242.html</t>
+          <t>https://vnexpress.net/vi-the-dac-biet-cua-elon-musk-tai-trung-quoc-5073851.html</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -10161,17 +10087,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cổ phiếu Boeing mất giá khi Trung Quốc có thể chỉ mua 200 máy bay</t>
+          <t>Vị thế đặc biệt của Elon Musk tại Trung Quốc</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_9207f47be79dbe06</t>
+          <t>DUPLICATE_OF_26113160399e295d</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -10182,7 +10108,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vi-the-dac-biet-cua-elon-musk-tai-trung-quoc-5073851.html</t>
+          <t>https://vnexpress.net/green-sm-hop-tac-75-doanh-nghiep-trien-khai-gan-18-500-xe-vinfast-5074490.html</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -10192,17 +10118,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vị thế đặc biệt của Elon Musk tại Trung Quốc</t>
+          <t>Green SM hợp tác 75 doanh nghiệp, triển khai gần 18.500 xe VinFast</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_26113160399e295d</t>
+          <t>DUPLICATE_OF_6f73162391c40d14</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -10213,7 +10139,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/green-sm-hop-tac-75-doanh-nghiep-trien-khai-gan-18-500-xe-vinfast-5074490.html</t>
+          <t>https://vnexpress.net/se-tao-dieu-kien-de-doanh-nghiep-chuyen-doi-xanh-de-tiep-can-von-5074672.html</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10223,17 +10149,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Green SM hợp tác 75 doanh nghiệp, triển khai gần 18.500 xe VinFast</t>
+          <t>Sẽ tạo điều kiện để doanh nghiệp chuyển đổi xanh dễ tiếp cận vốn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_6f73162391c40d14</t>
+          <t>DUPLICATE_OF_7e0d0d8afbcade01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
@@ -10244,7 +10170,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/se-tao-dieu-kien-de-doanh-nghiep-chuyen-doi-xanh-de-tiep-can-von-5074672.html</t>
+          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -10254,17 +10180,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sẽ tạo điều kiện để doanh nghiệp chuyển đổi xanh dễ tiếp cận vốn</t>
+          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7e0d0d8afbcade01</t>
+          <t>DUPLICATE_OF_1a2379fe5634145e</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -10275,7 +10201,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uy-ban-chung-khoan-day-manh-niem-yet-co-phieu-doanh-nghiep-nha-nuoc-5074010.html</t>
+          <t>https://vnexpress.net/nha-trang-trung-quoc-muon-mua-them-dau-my-5073987.html</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -10285,7 +10211,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Uỷ ban Chứng khoán: Đẩy mạnh niêm yết cổ phiếu doanh nghiệp nhà nước</t>
+          <t>Nhà Trắng: Trung Quốc muốn mua thêm dầu Mỹ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10295,7 +10221,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_1a2379fe5634145e</t>
+          <t>DUPLICATE_OF_9207f47be79dbe06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -10306,7 +10232,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-trang-trung-quoc-muon-mua-them-dau-my-5073987.html</t>
+          <t>https://vnexpress.net/han-quoc-sap-co-them-cong-ty-von-hoa-nghin-ty-usd-5073929.html</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -10316,7 +10242,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nhà Trắng: Trung Quốc muốn mua thêm dầu Mỹ</t>
+          <t>Hàn Quốc sắp có thêm công ty vốn hóa nghìn tỷ USD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10337,27 +10263,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/han-quoc-sap-co-them-cong-ty-von-hoa-nghin-ty-usd-5073929.html</t>
+          <t>https://vnexpress.net/ptit-muon-mo-quy-dau-tu-khoi-nghiep-cho-sinh-vien-5074258.html</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hàn Quốc sắp có thêm công ty vốn hóa nghìn tỷ USD</t>
+          <t>PTIT muốn mở quỹ đầu tư khởi nghiệp cho sinh viên</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_9207f47be79dbe06</t>
+          <t>DUPLICATE_OF_dce3e5e957055fb6</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -10368,27 +10294,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ptit-muon-mo-quy-dau-tu-khoi-nghiep-cho-sinh-vien-5074258.html</t>
+          <t>https://vnexpress.net/fed-sap-co-chu-tich-moi-5073625.html</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PTIT muốn mở quỹ đầu tư khởi nghiệp cho sinh viên</t>
+          <t>Fed sắp có chủ tịch mới</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_dce3e5e957055fb6</t>
+          <t>DUPLICATE_OF_cf55e528c69b8f8b</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -10399,27 +10325,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/fed-sap-co-chu-tich-moi-5073625.html</t>
+          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vneconomy_techconnect</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fed sắp có chủ tịch mới</t>
+          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_cf55e528c69b8f8b</t>
+          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -10430,7 +10356,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-giai-phap-nguon-nen-cho-lo-trinh-nang-luong-quoc-gia-ben-vung.htm</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -10440,12 +10366,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
+          <t>Điện hạt nhân quy mô nhỏ: Giải pháp “nguồn nền” cho lộ trình năng lượng quốc gia bền vững</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10461,7 +10387,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-giai-phap-nguon-nen-cho-lo-trinh-nang-luong-quoc-gia-ben-vung.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-tu-giai-phap-tiem-nang-den-thi-truong-ty-usd.htm</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10471,7 +10397,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ: Giải pháp “nguồn nền” cho lộ trình năng lượng quốc gia bền vững</t>
+          <t>Điện hạt nhân quy mô nhỏ: Từ giải pháp tiềm năng đến thị trường tỷ USD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10492,7 +10418,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-tu-giai-phap-tiem-nang-den-thi-truong-ty-usd.htm</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10502,7 +10428,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ: Từ giải pháp tiềm năng đến thị trường tỷ USD</t>
+          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10512,7 +10438,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_66f393fea931b3bb</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -10523,7 +10449,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
+          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10533,17 +10459,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
+          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_66f393fea931b3bb</t>
+          <t>DUPLICATE_OF_33371aef61a2861a</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -10554,7 +10480,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/xuat-khau-cong-nghe-ai-cua-trung-quoc-bung-no.htm</t>
+          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10564,7 +10490,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Xuất khẩu công nghệ AI của Trung Quốc bùng nổ</t>
+          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10574,7 +10500,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_33371aef61a2861a</t>
+          <t>DUPLICATE_OF_fc44824132db1c02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -10585,7 +10511,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10595,7 +10521,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
+          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10605,7 +10531,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_fc44824132db1c02</t>
+          <t>DUPLICATE_OF_bd1eda655234ed35</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -10616,7 +10542,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
+          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10626,17 +10552,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
+          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_bd1eda655234ed35</t>
+          <t>DUPLICATE_OF_20331d3bb6f2fe8b</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -10647,7 +10573,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
+          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10657,7 +10583,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
+          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -10667,7 +10593,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_20331d3bb6f2fe8b</t>
+          <t>DUPLICATE_OF_3150ccb709b5f656</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -10678,7 +10604,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/startup-viet-hop-tac-voi-cac-doanh-nghiep-nhat-ban-ung-dung-ai-iot-giai-quyet-thach-thuc-xa-hoi-va-moi-truong.htm</t>
+          <t>https://vneconomy.vn/techconnect/vien-truong-vinatom-phat-trien-dien-hat-nhan-an-toan-la-so-mot-khong-co-ngoai-le.htm</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10688,17 +10614,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Startup Việt hợp tác với các doanh nghiệp Nhật Bản, ứng dụng AI, IoT giải quyết thách thức xã hội và môi trường</t>
+          <t>Viện trưởng VINATOM: "Phát triển điện hạt nhân, an toàn là số một, không có ngoại lệ"</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3150ccb709b5f656</t>
+          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -10709,7 +10635,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/vien-truong-vinatom-phat-trien-dien-hat-nhan-an-toan-la-so-mot-khong-co-ngoai-le.htm</t>
+          <t>https://vneconomy.vn/techconnect/cmc-tai-cau-truc-khoi-cong-nghe-va-giai-phap-thuc-day-muc-tieu-chuyen-doi-ai.htm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10719,17 +10645,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Viện trưởng VINATOM: "Phát triển điện hạt nhân, an toàn là số một, không có ngoại lệ"</t>
+          <t>CMC tái cấu trúc Khối Công nghệ và Giải pháp, thúc đẩy mục tiêu chuyển đổi AI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_7cf8118d76f148e3</t>
+          <t>DUPLICATE_OF_33371aef61a2861a</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -10740,7 +10666,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cmc-tai-cau-truc-khoi-cong-nghe-va-giai-phap-thuc-day-muc-tieu-chuyen-doi-ai.htm</t>
+          <t>https://vneconomy.vn/techconnect/them-giai-phap-ai-make-in-vietnam-dat-chuan-quoc-te-ve-chong-gia-mao-khuon-mat.htm</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10750,17 +10676,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CMC tái cấu trúc Khối Công nghệ và Giải pháp, thúc đẩy mục tiêu chuyển đổi AI</t>
+          <t>Thêm giải pháp AI "Make in Vietnam" đạt chuẩn quốc tế về chống giả mạo khuôn mặt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_33371aef61a2861a</t>
+          <t>DUPLICATE_OF_fc44824132db1c02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -10771,27 +10697,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/them-giai-phap-ai-make-in-vietnam-dat-chuan-quoc-te-ve-chong-gia-mao-khuon-mat.htm</t>
+          <t>https://vneconomy.vn/techconnect/hacker-su-dung-ai-con-ac-mong-cua-thi-truong-crypto-130-ty-usd.htm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vneconomy_lifestyle</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thêm giải pháp AI "Make in Vietnam" đạt chuẩn quốc tế về chống giả mạo khuôn mặt</t>
+          <t>Hacker sử dụng AI: Cơn ác mộng của thị trường crypto 130 tỷ USD</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_fc44824132db1c02</t>
+          <t>DUPLICATE_OF_3150ccb709b5f656</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -11011,27 +10937,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/grabbike-18-5-2026/</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/lam-nhiem-vu-hoan-tien-mua-sam-san-hoan-tien-den-8715</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GrabBike | Thưởng mỗi tuần dành cho dịch vụ GrabBike từ ngày 18/5/2026 tại một số khu vực</t>
+          <t>Làm nhiệm vụ Hoàn tiền mua sắm, săn hoàn tiền đến 20K từ 15/05 – 25/05</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_0243da4a465c350b</t>
+          <t>DUPLICATE_OF_d09ee2a70e1838c8</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -11042,27 +10968,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/grabcar-kontum/</t>
+          <t>https://momo.vn/tin-tuc/cong-dong/hoan-thanh-ho-tro-chi-phi-hoc-tieng-anh-cho-10-em-8713</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GrabCar | Triển khai dịch vụ GrabCar tại Kon Tum</t>
+          <t>Hoàn thành hỗ trợ chi phí học tiếng Anh cho 10 em học sinh</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_313c80e7160af71f</t>
+          <t>DUPLICATE_OF_3af40e05acb3e3c8</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -11073,27 +10999,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.grab.com/vn/blog/driver/car/gfin-vc-voucher01thangtienlai/</t>
+          <t>https://momo.vn/tin-tuc/khuyen-mai/co-hoi-nhan-combo-5-the-qua-uu-dai-5000d-cho-don-8710</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>grab_vn_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GFIN x VIETCREDIT | Chương trình tặng voucher tương đương 01 tháng tiền lãi vay khi đăng ký vay qua thương hiệu Tin Vay</t>
+          <t>Cơ hội nhận combo 5 thẻ quà ưu đãi 5.000đ cho đơn hàng từ 0đ!</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_1566e1c9c20215f6</t>
+          <t>DUPLICATE_OF_6e2de3af4edb01b5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -11104,27 +11030,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/20471</t>
+          <t>https://momo.vn/tin-tuc/tin-tuc-su-kien/tham-gia-vong-song-khoe-nhan-qua-co-tri-gia-den-8707</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>momo_newsroom</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[11/05 - 17/05] ĐIỂM TIN BÁN HÀNG TRÊN SHOPEE TUẦN QUA CÓ GÌ MỚI !</t>
+          <t>Tham gia Vòng Sống Khỏe nhận quà có trị giá đến 3.990.000đ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_518231b28978900a</t>
+          <t>DUPLICATE_OF_ab2af2330968b663</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -11135,7 +11061,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/21087</t>
+          <t>https://banhang.shopee.vn/edu/article/20471</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -11145,17 +11071,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TỔNG HỢP CÁC MỨC PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL</t>
+          <t>[11/05 - 17/05] ĐIỂM TIN BÁN HÀNG TRÊN SHOPEE TUẦN QUA CÓ GÌ MỚI !</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
+          <t>DUPLICATE_OF_518231b28978900a</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -11166,27 +11092,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/50-nguoi-lai-xe-may-o-viet-nam-thuong-xuyen-dung-ung-dung-chi-duong-5072524.html</t>
+          <t>https://banhang.shopee.vn/edu/article/21087</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>50% người lái xe máy ở Việt Nam thường xuyên dùng ứng dụng chỉ đường</t>
+          <t>TỔNG HỢP CÁC MỨC PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_8576657079afb8be</t>
+          <t>DUPLICATE_OF_efd9f2bed01cac92</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -11197,27 +11123,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://banhang.shopee.vn/edu/article/27541</t>
+          <t>https://vnexpress.net/50-nguoi-lai-xe-may-o-viet-nam-thuong-xuyen-dung-ung-dung-chi-duong-5072524.html</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>shopee_seller_blog</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
+          <t>50% người lái xe máy ở Việt Nam thường xuyên dùng ứng dụng chỉ đường</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_8dd169053649c0d3</t>
+          <t>DUPLICATE_OF_8576657079afb8be</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -11228,27 +11154,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
+          <t>https://banhang.shopee.vn/edu/article/27541</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>shopee_seller_blog</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Introducing a Completely Private Way to Chat With AI</t>
+          <t>[QUAN TRỌNG] CẬP NHẬT VỀ PHÍ DÀNH CHO NGƯỜI BÁN THUỘC SHOPEE MALL TỪ NGÀY 23/05/2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_ecdd9a84cd8be1e9</t>
+          <t>DUPLICATE_OF_8dd169053649c0d3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -11259,20 +11185,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://blog.whatsapp.com/introducing-group-message-history-a-more-private-way-to-catch-up-in-group-chats</t>
+          <t>https://about.fb.com/news/2026/05/incognito-chat-whatsapp-meta-ai/</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>whatsapp_blog</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Introducing Group Message History: A more private way to catch up in group chats</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Introducing a Completely Private Way to Chat With AI</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>DUPLICATE_OF_ecdd9a84cd8be1e9</t>
@@ -11286,23 +11216,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
+          <t>https://blog.whatsapp.com/introducing-group-message-history-a-more-private-way-to-catch-up-in-group-chats</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>zalopay_news</t>
+          <t>whatsapp_blog</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tin tức</t>
+          <t>Introducing Group Message History: A more private way to catch up in group chats</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_a7169d7312fe0349</t>
+          <t>DUPLICATE_OF_ecdd9a84cd8be1e9</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -11313,23 +11243,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
+          <t>https://zalopay.vn/tin-tuc/thong-tin-bao-chi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>zalopay_promo</t>
+          <t>zalopay_news</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Khuyến mãi – Ưu Đãi</t>
+          <t>Tin tức</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
+          <t>DUPLICATE_OF_a7169d7312fe0349</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -11340,7 +11270,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
+          <t>https://zalopay.vn/khuyen-mai/mua-sam</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -11367,7 +11297,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
+          <t>https://zalopay.vn/khuyen-mai/an-uong</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11394,7 +11324,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
+          <t>https://zalopay.vn/khuyen-mai/du-lich</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11421,7 +11351,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
+          <t>https://zalopay.vn/khuyen-mai/hoa-don</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11448,7 +11378,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
+          <t>https://zalopay.vn/khuyen-mai/dien-thoai</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11475,7 +11405,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
+          <t>https://zalopay.vn/khuyen-mai/giai-tri</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11502,27 +11432,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/rakuten-bank-shares-jump-as-mizuho-says-it-s-mulling-investment</t>
+          <t>https://zalopay.vn/khuyen-mai/tai-chinh</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>bloomberg_tech</t>
+          <t>zalopay_promo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rakuten Bank Shares Jump as Mizuho Considers Investment</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
+          <t>Khuyến mãi – Ưu Đãi</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>DUPLICATE_OF_3032c2fa532d5c07</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -11533,7 +11459,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/australia-plots-next-step-in-tokenized-bond-market-expansion</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/samsung-shares-jump-after-leaders-resume-high-stakes-union-talks</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -11543,7 +11469,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Australia Plots Next Step in Tokenized Bond Market Expansion</t>
+          <t>Samsung Shares Jump After Leaders Resume High-Stakes Union Talks</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11564,7 +11490,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/e-commerce-giant-shein-buys-apparel-brand-everlane-reports-say</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/rakuten-bank-shares-jump-as-mizuho-says-it-s-mulling-investment</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -11574,7 +11500,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>E-Commerce Giant Shein Buys Apparel Brand Everlane, Reports Say</t>
+          <t>Rakuten Bank Shares Jump as Mizuho Considers Investment</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11595,7 +11521,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-18/kioxia-shares-awash-in-buy-orders-after-ai-driven-profit-surge</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/australia-plots-next-step-in-tokenized-bond-market-expansion</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -11605,7 +11531,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kioxia Shares Awash in Buy Orders After AI-Driven Profit Surge</t>
+          <t>Australia Plots Next Step in Tokenized Bond Market Expansion</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11626,7 +11552,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/e-commerce-giant-shein-buys-apparel-brand-everlane-reports-say</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -11636,12 +11562,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>China’s Energy Boom Could Give It the AI Edge</t>
+          <t>E-Commerce Giant Shein Buys Apparel Brand Everlane, Reports Say</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -11657,7 +11583,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-18/kioxia-shares-awash-in-buy-orders-after-ai-driven-profit-surge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -11667,12 +11593,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
+          <t>Kioxia Shares Awash in Buy Orders After AI-Driven Profit Surge</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11688,7 +11614,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-17/china-s-energy-boom-could-give-it-the-ai-edge-video</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -11698,12 +11624,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
+          <t>China’s Energy Boom Could Give It the AI Edge</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -11719,7 +11645,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-17/samsung-labor-union-to-meet-in-last-chance-to-avert-strike</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -11729,12 +11655,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
+          <t>Samsung, Labor Union to Meet in ‘Last Chance’ to Avert Strike</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11750,7 +11676,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/asml-partners-with-tata-electronics-to-advance-india-chip-plans</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -11760,7 +11686,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
+          <t>ASML Partners With Tata Electronics to Advance India Chip Plans</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11781,7 +11707,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
+          <t>https://www.bloomberg.com/news/videos/2026-05-16/stopping-poor-financial-decisions-masters-in-business-video</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -11791,7 +11717,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
+          <t>Stopping Poor Financial Decisions: Masters in Business with Sheila Bair</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11812,7 +11738,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-05-16/spacex-shareholders-approve-5-for-1-split-of-common-stock</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/china-data-centers-tap-spot-power-trading-first-time-report</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -11822,7 +11748,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SpaceX Holders Sign Off on 5-for-1 Stock Split Ahead of IPO</t>
+          <t>China Data Centers Tap Spot Power Trading First Time: Report</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11843,22 +11769,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
+          <t>https://www.bloomberg.com/news/articles/2026-05-16/europe-lacks-everything-needed-to-make-its-stock-market-a-winner</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>luatvietnam_chinhsach</t>
+          <t>bloomberg_tech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
+          <t>Europe Lacks Everything Needed to Make Its Stock Market a Winner</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -11874,22 +11800,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
+          <t>https://luatvietnam.vn/chinh-sach-moi-hang-thang/chinh-sach-moi-co-hieu-luc-thang-5-2026-559-108668-article.html</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>meta_newsroom</t>
+          <t>luatvietnam_chinhsach</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
+          <t>Chính sách mới có hiệu lực tháng 5/2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -11905,22 +11831,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
+          <t>https://about.fb.com/news/2026/05/from-scroll-to-chat-to-cart-trends-reshaping-how-india-shops/</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>scmp_wechat</t>
+          <t>meta_newsroom</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
+          <t>From Scroll to Chat to Cart: Trends Reshaping How India Shops</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -11936,22 +11862,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/news/china/diplomacy/article/3353201/us-trial-hears-witness-claims-harassment-over-chinese-secret-police-station</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>scmp_tech</t>
+          <t>scmp_wechat</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>China ramps up building a national computing power network as AI token demand surges</t>
+          <t>US trial hears witness claims of harassment over Chinese ‘secret police station’</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -11967,7 +11893,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353891/china-ramps-building-national-computing-power-network-ai-token-demand-surges?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11977,12 +11903,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
+          <t>China ramps up building a national computing power network as AI token demand surges</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11998,7 +11924,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353752/trump-poured-millions-nvidia-apple-first-quarter-ethics-filing-shows?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -12008,7 +11934,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
+          <t>Trump poured millions into Nvidia, Apple in first quarter, ethics filing shows</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12029,7 +11955,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/article/3353657/meet-zhou-qunfei-woman-seated-between-tim-cook-and-elon-musk-china-state-banquet?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -12039,12 +11965,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
+          <t>Meet Zhou Qunfei: the woman seated between Tim Cook and Elon Musk at China state banquet</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -12060,7 +11986,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/china-evs/article/3353525/geely-xiaomi-lead-pack-battery-evs-top-china-sales-rising-oil-costs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -12070,12 +11996,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
+          <t>Geely, Xiaomi lead the pack: battery EVs top China sales on rising oil costs</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -12091,7 +12017,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/banking-finance/article/3353341/hong-kong-biotech-firm-uses-ai-produce-nano-rockets-deliver-life-saving-drugs?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -12101,12 +12027,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
+          <t>Hong Kong-listed biotech firm uses AI to produce nano-rockets to deliver life-saving drugs</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -12122,7 +12048,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353309/loongsons-flagship-chip-hits-1-million-units-boosting-chinas-tech-self-reliance?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -12132,7 +12058,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
+          <t>Loongson’s flagship chip hits 1 million units, boosting China’s tech self-reliance</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12142,7 +12068,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>T3_HEALTHCARE</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -12153,7 +12079,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/business/china-business/article/3353263/chinas-hengrui-seals-us152-billion-deal-us-pharmaceutical-giant-bms?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -12163,7 +12089,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
+          <t>China’s Hengrui seals US$15.2 billion deal with US pharmaceutical giant BMS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12173,7 +12099,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_HEALTHCARE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -12184,7 +12110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353262/real-life-transformers-chinas-unitree-debuts-mecha-robot-shifts-2-legs-4?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -12194,12 +12120,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
+          <t>Real-life Transformers: China’s Unitree debuts ‘mecha’ robot that shifts from 2 legs to 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -12215,7 +12141,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/economy/global-economy/article/3353180/chinas-ai-ascent-leaves-trump-stark-choice-escalate-or-relax-chip-controls?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -12225,7 +12151,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
+          <t>China’s AI ascent leaves Trump a stark choice: escalate or relax chip controls?</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -12246,7 +12172,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
+          <t>https://www.scmp.com/tech/tech-trends/article/3353173/china-deepens-footprint-ai-conference-despite-neurips-dispute-us-tensions?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -12256,7 +12182,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>China ranks third in global index for AI competitiveness in life sciences</t>
+          <t>China deepens footprint at AI conference despite NeurIPS dispute, US tensions</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -12277,22 +12203,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
+          <t>https://www.scmp.com/tech/big-tech/article/3353081/china-ranks-third-global-index-ai-competitiveness-life-sciences?utm_source=rss_feed</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>techcrunch_apps</t>
+          <t>scmp_tech</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Osaurus brings both local and cloud AI models to your Mac</t>
+          <t>China ranks third in global index for AI competitiveness in life sciences</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -12308,7 +12234,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
+          <t>https://techcrunch.com/2026/05/15/osaurus-brings-both-local-and-cloud-ai-models-to-your-mac/</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -12318,12 +12244,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
+          <t>Osaurus brings both local and cloud AI models to your Mac</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -12339,7 +12265,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
+          <t>https://techcrunch.com/2026/05/14/two-weeks-left-startup-battlefield-200-applications-close-may-27/</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -12349,12 +12275,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
+          <t>Two weeks left: Startup Battlefield 200 applications close May 27</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12370,7 +12296,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
+          <t>https://techcrunch.com/2026/05/13/x-launches-a-history-tab-for-bookmarks-likes-videos-and-articles/</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -12380,12 +12306,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Indigo brings the open social web to one app</t>
+          <t>X launches a History tab for bookmarks, likes, videos, and articles</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12401,22 +12327,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/if-youre-giving-a-commencement-speech-in-2026-maybe-dont-mention-ai/</t>
+          <t>https://techcrunch.com/2026/05/12/indigo-brings-the-open-social-web-to-one-app/</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>techcrunch_ai</t>
+          <t>techcrunch_apps</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>If you’re giving a commencement speech in 2026, maybe don’t mention AI</t>
+          <t>Indigo brings the open social web to one app</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12432,7 +12358,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/17/techcrunch-mobility-the-ai-skills-arms-race-is-coming-for-automotive/</t>
+          <t>https://techcrunch.com/2026/05/17/if-youre-giving-a-commencement-speech-in-2026-maybe-dont-mention-ai/</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12442,7 +12368,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TechCrunch Mobility: The AI skills arms race is coming for automotive</t>
+          <t>If you’re giving a commencement speech in 2026, maybe don’t mention AI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -12463,7 +12389,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
+          <t>https://techcrunch.com/2026/05/17/techcrunch-mobility-the-ai-skills-arms-race-is-coming-for-automotive/</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12473,12 +12399,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The haves and have nots of the AI gold rush</t>
+          <t>TechCrunch Mobility: The AI skills arms race is coming for automotive</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12494,7 +12420,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
+          <t>https://techcrunch.com/2026/05/16/the-haves-and-have-nots-of-the-ai-gold-rush/</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12504,7 +12430,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
+          <t>The haves and have nots of the AI gold rush</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -12525,7 +12451,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
+          <t>https://techcrunch.com/2026/05/16/research-repository-arxiv-will-ban-authors-for-a-year-if-they-let-ai-do-all-the-work/</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12535,12 +12461,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
+          <t>Research repository ArXiv will ban authors for a year if they let AI do all the work</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12556,7 +12482,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
+          <t>https://techcrunch.com/2026/05/14/what-the-jury-will-actually-decide-in-the-case-of-elon-musk-vs-sam-altman/</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12566,7 +12492,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
+          <t>What the jury will actually decide in the case of Elon Musk vs. Sam Altman</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -12587,7 +12513,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
+          <t>https://techcrunch.com/2026/05/14/elon-musks-spacexai-has-been-bleeding-staff-since-its-merger/</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -12597,7 +12523,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>What happens when AI starts building itself?</t>
+          <t>Elon Musk’s SpaceXAI has been bleeding staff since its merger</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -12618,7 +12544,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
+          <t>https://techcrunch.com/2026/05/14/what-happens-when-ai-starts-building-itself/</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -12628,7 +12554,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
+          <t>What happens when AI starts building itself?</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -12649,22 +12575,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
+          <t>https://techcrunch.com/2026/05/14/khosla-ventures-is-betting-10m-on-ian-crosby-whose-last-startup-bench-imploded/</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>vneconomy_techtalk</t>
+          <t>techcrunch_ai</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
+          <t>Khosla Ventures is betting $10M on Ian Crosby, whose first startup, Bench, imploded</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12680,7 +12606,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
+          <t>https://vneconomy.vn/techconnect/canh-cua-moi-de-startup-viet-nam-vuon-ra-toan-cau.htm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12690,12 +12616,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
+          <t>“Cánh cửa mới” để startup Việt Nam vươn ra toàn cầu</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -12711,7 +12637,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/bao-ve-tre-em-tren-khong-gian-mang-khong-the-chi-dung-o-canh-bao-nguy-co.htm</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12721,12 +12647,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
+          <t>Bảo vệ trẻ em trên không gian mạng: Không thể chỉ dừng ở cảnh báo nguy cơ</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12742,7 +12668,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
+          <t>https://vneconomy.vn/techconnect/de-xuat-bo-sung-toi-danh-can-tro-bao-ve-du-lieu-ca-nhan.htm</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12752,12 +12678,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
+          <t>Đề xuất bổ sung tội danh cản trở bảo vệ dữ liệu cá nhân</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -12773,7 +12699,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
+          <t>https://vneconomy.vn/techconnect/truc-tiep-hoi-thao-quoc-te-dien-hat-nhan-quy-mo-nho-giai-phap-chien-luoc-cho-an-ninh-nang-luong-viet-nam.htm</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12783,12 +12709,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
+          <t>[Trực tiếp]: Hội thảo Quốc tế “Điện hạt nhân quy mô nhỏ: Giải pháp chiến lược cho an ninh năng lượng Việt Nam”</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -12804,7 +12730,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
+          <t>https://vneconomy.vn/techconnect/cac-sang-kien-khi-hau-dang-dich-chuyen-tu-phong-trao-sang-tac-dong-dai-han.htm</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12814,12 +12740,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
+          <t>Các sáng kiến khí hậu đang dịch chuyển từ phong trào sang tác động dài hạn</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12835,7 +12761,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
+          <t>https://vneconomy.vn/techconnect/tu-lao-cai-den-an-giang-ai-khong-con-la-san-choi-cua-thanh-pho-lon.htm</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12845,12 +12771,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
+          <t>Từ Lào Cai đến An Giang: AI không còn là sân chơi của thành phố lớn</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -12866,7 +12792,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
+          <t>https://vneconomy.vn/techconnect/chien-luoc-phat-trien-nang-luc-tu-stem-cau-chuyen-ngoi-truong-ngoai-thanh-den-cuoc-thi-vo-dich-quoc-gia.htm</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12876,12 +12802,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
+          <t>Chiến lược phát triển năng lực từ STEM: Câu chuyện ngôi trường ngoại thành đến cuộc thi vô địch quốc gia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12897,7 +12823,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
+          <t>https://vneconomy.vn/techconnect/hanh-trinh-truy-vet-toi-pham-mang-mo-hinh-huan-luyen-dieu-tra-so-sat-thuc-tien.htm</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12907,7 +12833,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
+          <t>“Hành trình truy vết tội phạm mạng”: Mô hình huấn luyện điều tra số sát thực tiễn</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -12928,22 +12854,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ban-dan-viet-nam-nen-di-theo-huong-toi-uu-nang-luong-5074612.html</t>
+          <t>https://vneconomy.vn/techconnect/dien-hat-nhan-quy-mo-nho-mo-ra-mot-cach-tiep-can-thi-truong-moi.htm</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>'Bán dẫn Việt Nam nên đi theo hướng tối ưu năng lượng'</t>
+          <t>Điện hạt nhân quy mô nhỏ mở ra một cách tiếp cận thị trường mới</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -12959,22 +12885,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/iphone-gap-co-the-gap-loi-tieng-keu-ban-le-5075003.html</t>
+          <t>https://vneconomy.vn/techconnect/viet-nam-truoc-bai-toan-an-ninh-nang-luong-trong-ky-nguyen-dien-hoa.htm</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vneconomy_techtalk</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>iPhone gập 'có thể gặp lỗi tiếng kêu bản lề'</t>
+          <t>Việt Nam trước bài toán an ninh năng lượng trong kỷ nguyên điện hóa</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -12990,7 +12916,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
+          <t>https://vnexpress.net/ban-dan-viet-nam-nen-di-theo-huong-toi-uu-nang-luong-5074612.html</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -13000,12 +12926,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
+          <t>'Bán dẫn Việt Nam nên đi theo hướng tối ưu năng lượng'</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -13021,7 +12947,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
+          <t>https://vnexpress.net/iphone-gap-co-the-gap-loi-tieng-keu-ban-le-5075003.html</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -13031,12 +12957,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
+          <t>iPhone gập 'có thể gặp lỗi tiếng kêu bản lề'</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -13052,22 +12978,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
+          <t>https://vnexpress.net/tau-nhien-lieu-kep-suc-cho-24-000-container-dau-tien-tren-the-gioi-5074925.html</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
+          <t>Tàu nhiên liệu kép sức chở 24.000 container đầu tiên trên thế giới</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13083,7 +13009,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
+          <t>https://vnexpress.net/kaspersky-chan-gan-nua-trieu-vu-ma-doc-danh-cap-mat-khau-tai-viet-nam-5074794.html</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -13093,12 +13019,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
+          <t>Kaspersky chặn gần nửa triệu vụ mã độc đánh cắp mật khẩu tại Việt Nam</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -13114,22 +13040,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
+          <t>https://vnexpress.net/trung-quoc-co-the-mua-them-hang-chuc-ty-usd-nong-san-my-5074335.html</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
+          <t>Trung Quốc có thể mua thêm 'hàng chục tỷ USD' nông sản Mỹ</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -13145,7 +13071,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
+          <t>https://vnexpress.net/trai-nghiem-spot-scrub-ai-robot-lau-nha-dau-tien-cua-dyson-5074297.html</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13155,12 +13081,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
+          <t>Trải nghiệm Spot+Scrub AI - robot lau nhà đầu tiên của Dyson</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -13176,22 +13102,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
+          <t>https://vnexpress.net/phan-lon-tre-em-tung-doi-mat-rui-ro-tren-moi-truong-so-5074901.html</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
+          <t>Phần lớn trẻ em từng đối mặt rủi ro trên môi trường số</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -13207,7 +13133,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
+          <t>https://vnexpress.net/van-hanh-nen-tang-truyen-so-lieu-rieng-cho-co-quan-dang-nha-nuoc-5074792.html</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13217,12 +13143,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
+          <t>Vận hành nền tảng truyền số liệu riêng cho cơ quan Đảng, Nhà nước</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -13238,22 +13164,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
+          <t>https://vnexpress.net/ngan-hang-nha-nuoc-go-kho-thanh-khoan-cho-nha-bang-quoc-doanh-5074479.html</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
+          <t>Ngân hàng Nhà nước gỡ khó thanh khoản cho nhà băng quốc doanh</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -13269,7 +13195,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
+          <t>https://vnexpress.net/canon-eos-r6-v-may-anh-full-frame-chuyen-quay-video-5074065.html</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13279,12 +13205,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
+          <t>Canon EOS R6 V - máy ảnh full-frame chuyên quay video</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -13300,7 +13226,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
+          <t>https://vnexpress.net/yeu-to-giup-lg-oled-doat-giai-man-hinh-choi-game-xuat-sac-5074711.html</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13310,12 +13236,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
+          <t>Yếu tố giúp LG OLED đoạt giải 'Màn hình chơi game xuất sắc'</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13331,7 +13257,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
+          <t>https://vnexpress.net/robot-hinh-nguoi-my-tu-dong-thay-phien-lam-viec-24-7-5074481.html</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13341,7 +13267,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
+          <t>Robot hình người Mỹ tự động thay phiên làm việc 24/7</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -13362,7 +13288,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
+          <t>https://vnexpress.net/nhung-bieu-cam-gay-sot-cua-musk-trong-chuyen-tham-trung-quoc-5074136.html</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13372,7 +13298,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
+          <t>Những biểu cảm gây sốt của Musk trong chuyến thăm Trung Quốc</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -13393,7 +13319,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
+          <t>https://vnexpress.net/lg-ra-mat-loat-tv-2026-voi-kich-thuoc-lon-5074076.html</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13403,12 +13329,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
+          <t>LG ra mắt loạt TV 2026 với kích thước lớn</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13424,22 +13350,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
+          <t>https://vnexpress.net/zenbook-duo-2026-laptop-hai-man-hinh-chay-chip-intel-manh-nhat-5073609.html</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
+          <t>Zenbook Duo 2026 - laptop hai màn hình chạy chip Intel mạnh nhất</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13455,7 +13381,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
+          <t>https://vnexpress.net/them-ai-lab-duoc-mo-tai-khu-cong-nghe-cao-hoa-lac-5074021.html</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13465,12 +13391,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
+          <t>Thêm AI Lab được mở tại khu công nghệ cao Hòa Lạc</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13486,22 +13412,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
+          <t>https://vnexpress.net/thu-truong-hoang-trung-doanh-nghiep-muon-dau-tu-phong-kiem-nghiem-phai-cho-6-thang-duyet-ho-so-5073902.html</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>vnexpress_khcn</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
+          <t>Thứ trưởng Hoàng Trung: Doanh nghiệp muốn đầu tư phòng kiểm nghiệm phải chờ 6 tháng duyệt hồ sơ</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13517,7 +13443,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
+          <t>https://vnexpress.net/tai-sao-dieu-hoa-co-mui-hoi-kho-chiu-5073641.html</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13527,12 +13453,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
+          <t>Tại sao điều hòa có mùi hôi khó chịu?</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13548,7 +13474,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/foxconn-bi-tan-cong-ma-hoa-du-lieu-co-the-lo-bi-mat-apple-5073614.html</t>
+          <t>https://vnexpress.net/galaxy-a57-a37-5g-smartphone-tam-trung-cho-gioi-tre-di-dau-ve-ai-5074011.html</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13558,12 +13484,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Foxconn bị tấn công mã hóa dữ liệu, có thể lộ bí mật Apple</t>
+          <t>Galaxy A57/A37 5G - smartphone tầm trung cho giới trẻ đi đầu về AI</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13579,7 +13505,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
+          <t>https://vnexpress.net/may-bay-nang-luong-mat-troi-tung-vong-quanh-the-gioi-roi-xuong-bien-5074039.html</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13589,7 +13515,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
+          <t>Máy bay năng lượng mặt trời từng vòng quanh thế giới rơi xuống biển</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13610,7 +13536,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
+          <t>https://vnexpress.net/foxconn-bi-tan-cong-ma-hoa-du-lieu-co-the-lo-bi-mat-apple-5073614.html</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13620,7 +13546,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
+          <t>Foxconn bị tấn công mã hóa dữ liệu, có thể lộ bí mật Apple</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13641,7 +13567,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
+          <t>https://vnexpress.net/bay-anh-phat-hien-soi-lua-quy-hiem-o-nghe-an-5073749.html</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13651,7 +13577,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
+          <t>Bẫy ảnh phát hiện sói lửa quý hiếm ở Nghệ An</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13672,7 +13598,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
+          <t>https://vnexpress.net/bao-tang-nghien-cuu-sam-va-duoc-lieu-trong-hang-nui-5068861.html</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13682,7 +13608,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
+          <t>Bảo tàng nghiên cứu sâm và dược liệu trong hang núi</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13703,7 +13629,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
+          <t>https://vnexpress.net/nha-mang-co-xoa-duoc-tai-khoan-gan-voi-sim-quay-dau-5073355.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13713,7 +13639,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
+          <t>Nhà mạng có xóa được tài khoản gắn với 'SIM quay đầu'?</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -13734,7 +13660,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
+          <t>https://vnexpress.net/oppo-find-x9-ultra-nhiep-anh-da-dung-voi-camera-quang-hoc-10x-5073877.html</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13744,7 +13670,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
+          <t>Oppo Find X9 Ultra - nhiếp ảnh đa dụng với camera quang học 10x</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13765,7 +13691,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
+          <t>https://vnexpress.net/trien-lam-sach-khoa-hoc-va-cong-nghe-2026-khai-mac-5073843.html</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13775,7 +13701,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Vai trò của sách trong thời AI</t>
+          <t>Triển lãm Sách Khoa học và Công nghệ 2026 khai mạc</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -13796,7 +13722,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
+          <t>https://vnexpress.net/voodoo-goi-y-cach-dua-game-viet-len-bang-xep-hang-toan-cau-5073773.html</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13806,12 +13732,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
+          <t>Voodoo gợi ý cách đưa game Việt lên bảng xếp hạng toàn cầu</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -13827,22 +13753,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nha-dau-tu-nen-lam-gi-khi-chung-khoan-len-cao-ky-luc-5074966.html</t>
+          <t>https://vnexpress.net/vai-tro-cua-sach-trong-thoi-ai-5073618.html</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nhà đầu tư nên làm gì khi chứng khoán lên cao kỷ lục?</t>
+          <t>Vai trò của sách trong thời AI</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13858,22 +13784,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
+          <t>https://vnexpress.net/vivo-x300-ultra-may-anh-trong-than-hinh-smartphone-5072795.html</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>vnexpress_kinhdoanh</t>
+          <t>vnexpress_khcn</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Giá vàng tuần này được dự báo giảm tiếp</t>
+          <t>Vivo X300 Ultra - 'máy ảnh' trong thân hình smartphone</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -13889,7 +13815,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
+          <t>https://vnexpress.net/nha-dau-tu-nen-lam-gi-khi-chung-khoan-len-cao-ky-luc-5074966.html</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13899,12 +13825,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
+          <t>Nhà đầu tư nên làm gì khi chứng khoán lên cao kỷ lục?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -13920,7 +13846,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
+          <t>https://vnexpress.net/gia-vang-duoc-du-bao-giam-tiep-tuan-sau-5074909.html</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13930,7 +13856,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
+          <t>Giá vàng tuần này được dự báo giảm tiếp</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -13951,7 +13877,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
+          <t>https://vnexpress.net/kim-ngach-xuat-nhap-khau-tang-manh-5074869.html</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13961,12 +13887,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
+          <t>Kim ngạch xuất, nhập khẩu tăng mạnh</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13982,7 +13908,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
+          <t>https://vnexpress.net/bhutan-co-the-da-ban-1-ty-usd-bitcoin-5074822.html</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13992,12 +13918,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
+          <t>Bhutan có thể đã bán 1 tỷ USD Bitcoin</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14013,7 +13939,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
+          <t>https://vnexpress.net/uae-gap-rut-xay-duong-ong-dan-dau-tranh-eo-bien-hormuz-5074710.html</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14023,12 +13949,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
+          <t>UAE gấp rút xây đường ống dẫn dầu, tránh eo biển Hormuz</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14044,7 +13970,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
+          <t>https://vnexpress.net/tp-hcm-ha-noi-tiep-tuc-khong-thuoc-top-dau-nang-luc-canh-tranh-cap-tinh-5074295.html</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14054,12 +13980,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
+          <t>TP HCM, Hà Nội tiếp tục không thuộc top đầu năng lực cạnh tranh cấp tỉnh</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14075,7 +14001,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
+          <t>https://vnexpress.net/doanh-nghiep-can-luat-choi-ro-rang-de-phat-trien-5074487.html</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14085,12 +14011,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
+          <t>'Doanh nghiệp cần luật chơi rõ ràng để phát triển'</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14106,7 +14032,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
+          <t>https://vnexpress.net/tinh-ban-giua-elon-musk-va-jensen-huang-5074616.html</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14116,12 +14042,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
+          <t>Tình bạn giữa Elon Musk và Jensen Huang</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -14137,7 +14063,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
+          <t>https://vnexpress.net/dragon-capital-co-phieu-nhom-vingroup-tang-manh-khong-vo-ly-5074576.html</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14147,12 +14073,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
+          <t>Dragon Capital: Cổ phiếu nhóm Vingroup tăng mạnh không vô lý</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14168,7 +14094,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
+          <t>https://vnexpress.net/ba-nguyen-thi-mai-thanh-tu-chuc-chu-tich-hdqt-ree-5074522.html</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14178,17 +14104,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
+          <t>Bà Nguyễn Thị Mai Thanh từ chức Chủ tịch HĐQT REE</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>T3_SPORTS</t>
+          <t>NO_KEYWORD</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
@@ -14199,7 +14125,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
+          <t>https://vnexpress.net/co-phieu-tru-tac-dong-den-vn-index-ra-sao-5072361.html</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14209,7 +14135,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
+          <t>Cổ phiếu trụ tác động đến VN-Index ra sao?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -14230,7 +14156,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
+          <t>https://vnexpress.net/trung-tam-dich-vu-so-mobifone-hop-tac-vtv-digital-phat-trien-he-sinh-thai-vtvgo-5074635.html</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14240,17 +14166,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
+          <t>Trung tâm Dịch vụ số MobiFone hợp tác VTV Digital phát triển hệ sinh thái VTVgo</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>NO_KEYWORD</t>
+          <t>T3_SPORTS</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -14261,7 +14187,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
+          <t>https://vnexpress.net/chuyen-gia-pin-luu-tru-giup-doanh-nghiep-giam-tien-dien-gio-cao-diem-5074379.html</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14271,7 +14197,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
+          <t>Chuyên gia: Pin lưu trữ giúp doanh nghiệp giảm tiền điện giờ cao điểm</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -14292,7 +14218,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
+          <t>https://vnexpress.net/acv-bo-nhiem-quyen-tong-giam-doc-5074468.html</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14302,7 +14228,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
+          <t>ACV bổ nhiệm Quyền Tổng giám đốc</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -14323,7 +14249,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
+          <t>https://vnexpress.net/nguoi-tieu-dung-dan-coi-mo-voi-xang-sinh-hoc-e10-5074369.html</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14333,7 +14259,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
+          <t>Người tiêu dùng dần cởi mở với xăng sinh học E10</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -14354,7 +14280,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
+          <t>https://vnexpress.net/chung-khoan-giam-diem-phien-cuoi-tuan-5074389.html</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14364,7 +14290,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
+          <t>Chứng khoán giảm điểm phiên cuối tuần</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -14385,7 +14311,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
+          <t>https://vnexpress.net/hang-hang-khong-giam-luong-lanh-dao-siet-chi-phi-van-hanh-5074317.html</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14395,7 +14321,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
+          <t>Hãng hàng không giảm lương lãnh đạo, siết chi phí vận hành</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -14416,7 +14342,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
+          <t>https://vnexpress.net/cuu-vuong-nganh-thep-chua-het-lo-5074229.html</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14426,7 +14352,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
+          <t>'Cựu vương' ngành thép chưa hết lỗ</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -14447,7 +14373,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
+          <t>https://vnexpress.net/vingroup-tuyen-20-000-lao-dong-cho-du-an-khu-do-thi-the-thao-5074359.html</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14457,7 +14383,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
+          <t>Vingroup tuyển 20.000 lao động cho dự án khu đô thị thể thao</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -14478,7 +14404,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
+          <t>https://vnexpress.net/grohe-spa-gioi-thieu-khong-gian-phong-tam-ket-hop-nghe-thuat-sap-dat-5074322.html</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14488,7 +14414,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
+          <t>Grohe Spa giới thiệu không gian phòng tắm kết hợp nghệ thuật sắp đặt</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -14509,7 +14435,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
+          <t>https://vnexpress.net/saigon-co-op-kich-cau-tieu-dung-voi-loat-uu-dai-thuc-pham-5074246.html</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14519,12 +14445,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Giá xăng, dầu cùng giảm</t>
+          <t>Saigon Co.op kích cầu tiêu dùng với loạt ưu đãi thực phẩm</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -14540,7 +14466,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
+          <t>https://vnexpress.net/cc1-lua-chon-don-vi-kiem-toan-moi-cho-bao-cao-tai-chinh-5074291.html</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14550,12 +14476,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
+          <t>CC1 lựa chọn đơn vị kiểm toán mới cho báo cáo tài chính</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -14571,7 +14497,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
+          <t>https://vnexpress.net/gia-xang-dau-moi-nhat-hom-nay-144-5-5073823.html</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14581,7 +14507,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
+          <t>Giá xăng, dầu cùng giảm</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -14602,7 +14528,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
+          <t>https://vnexpress.net/ke-hoach-cai-to-fed-cua-tan-chu-tich-5073630.html</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14612,7 +14538,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
+          <t>Kế hoạch cải tổ Fed của tân chủ tịch</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -14633,7 +14559,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
+          <t>https://vnexpress.net/highlands-coffee-lai-ky-luc-quy-dau-nam-5073741.html</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14643,12 +14569,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
+          <t>Highlands Coffee lãi kỷ lục quý đầu năm</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -14664,7 +14590,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
+          <t>https://vnexpress.net/vinfast-se-the-nao-khi-tach-mang-san-xuat-5073669.html</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14674,12 +14600,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
+          <t>VinFast sẽ thế nào khi tách mảng sản xuất</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14695,7 +14621,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
+          <t>https://vnexpress.net/ha-noi-co-the-cho-thue-via-he-45-000-dong-mot-m2-moi-thang-de-kinh-doanh-5073615.html</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14705,7 +14631,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
+          <t>Hà Nội có thể cho thuê vỉa hè 45.000 đồng một m2 mỗi tháng để kinh doanh</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -14726,22 +14652,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
+          <t>https://vnexpress.net/cu-hich-tai-cau-truc-kinh-te-toan-cau-tu-xung-dot-trung-dong-5073241.html</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
+          <t>Cú hích tái cấu trúc kinh tế toàn cầu từ xung đột Trung Đông</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14757,22 +14683,22 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
+          <t>https://vnexpress.net/de-xuat-phan-bo-dan-khoan-lo-cua-evn-vao-gia-dien-5073607.html</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>vneconomy_techconnect</t>
+          <t>vnexpress_kinhdoanh</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
+          <t>Đề xuất phân bổ dần khoản lỗ của EVN vào giá điện</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14788,7 +14714,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
+          <t>https://vneconomy.vn/techconnect/qualcomm-chinh-thuc-khai-truong-trung-tam-rd-tai-ha-noi.htm</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14798,12 +14724,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
+          <t>Qualcomm chính thức khai trương Trung tâm R&amp;D tại Hà Nội</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14813,6 +14739,68 @@
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/techconnect/bac-kinh-thuc-day-trung-tam-du-lieu-ai-dung-dien-xanh.htm</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>vneconomy_techconnect</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Bắc Kinh thúc đẩy trung tâm dữ liệu AI dùng “điện xanh”</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>NO_KEYWORD</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://vneconomy.vn/techconnect/cong-nghe-dieu-huong-phao-cuu-sinh-cho-thu-nhap-va-an-toan-cua-nguoi-lai-xe-2-banh-tai-viet-nam.htm</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>vneconomy_techconnect</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Công nghệ điều hướng: 'Phao cứu sinh' cho thu nhập và an toàn của người lái xe 2 bánh tại Việt Nam</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>NO_KEYWORD</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="b">
         <v>0</v>
       </c>
     </row>
@@ -14886,12 +14874,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -14916,12 +14904,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -14946,12 +14934,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -14976,12 +14964,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15006,12 +14994,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15036,12 +15024,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15066,12 +15054,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15096,12 +15084,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15126,12 +15114,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15140,13 +15128,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -15156,12 +15144,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15186,12 +15174,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15216,12 +15204,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15246,12 +15234,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -15276,12 +15264,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -15290,13 +15278,13 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="n">
         <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -15306,12 +15294,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -15336,12 +15324,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -15366,12 +15354,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -15396,12 +15384,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -15426,12 +15414,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -15440,10 +15428,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
         <v>3</v>
@@ -15456,12 +15444,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -15486,12 +15474,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -15516,12 +15504,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -15546,12 +15534,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -15576,12 +15564,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -15606,12 +15594,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -15636,12 +15624,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -15666,12 +15654,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -15696,12 +15684,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -15710,13 +15698,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -15726,12 +15714,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -15756,12 +15744,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -15786,12 +15774,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -15816,12 +15804,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -15846,12 +15834,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -15876,12 +15864,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -15906,12 +15894,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15936,12 +15924,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18T03:00:19.639243+00:00</t>
+          <t>2026-05-18T03:25:36.625157+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-18T03:07:50.089123+00:00</t>
+          <t>2026-05-18T03:34:29.254949+00:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
